--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CEAC012-9944-4010-A14B-8B10D21B072D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50304B1C-1B3A-4AD2-8020-2922B318D6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.63</v>
+        <v>7.55</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7951.8722290699998</v>
+        <v>7868.49742195</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>3.8805018001506791E-2</v>
+        <v>4.258909089785054E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.1089235029869067E-2</v>
+        <v>4.1524617652702114E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5386631716906952E-2</v>
+        <v>3.5761589403973511E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5386631716906952E-2</v>
+        <v>3.5761589403973511E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5386631716906952E-2</v>
+        <v>3.5761589403973511E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.3027522935779825E-2</v>
+        <v>3.3377483443708618E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0720838794233301E-2</v>
+        <v>5.1258278145695377E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1089235029869067E-2</v>
+        <v>4.1524617652702114E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.3756054598892012E-2</v>
+        <v>6.4431615442323981E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>4.8890373084562004E-2</v>
+        <v>4.9408416772875247E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.2081124124127863E-2</v>
+        <v>3.2421056565178227E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.5729035138675513E-2</v>
+        <v>2.6001660676568762E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11151952325870221</v>
+        <v>0.11270118708131097</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.10916070769179342</v>
+        <v>0.11031737744217004</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13078907332011216</v>
+        <v>0.13217491780562329</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.11476932396670758</v>
+        <v>0.11598542276370581</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.3633008786130697E-2</v>
+        <v>8.4519186362672472E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>9.9091003640554551E-2</v>
+        <v>0.10014097454005712</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0253001188895522E-2</v>
+        <v>3.0573562790897065E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4812612251162358E-2</v>
+        <v>1.4969567082962753E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6480556268272297E-3</v>
+        <v>2.6761144943962603E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.0294717438999153E-2</v>
+        <v>-2.0509760802591197E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4134490974956863E-2</v>
+        <v>7.4920022005155074E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1629797812610946E-2</v>
+        <v>7.2388789047711455E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4027542000312755E-2</v>
+        <v>9.5023860326143877E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0742620291710934E-2</v>
+        <v>8.159817123519926E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2155998132329794E-2</v>
+        <v>8.3026525264857778E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1083134099365092E-2</v>
+        <v>7.1836332871278899E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.63</v>
+        <v>7.55</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>3.8805018001506791E-2</v>
+        <v>4.258909089785054E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>7.63</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7951.8722290699998</v>
+        <v>7868.49742195</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>3.8805018001506791E-2</v>
+        <v>4.258909089785054E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.1089235029869067E-2</v>
+        <v>4.1524617652702114E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>3.5386631716906952E-2</v>
+        <v>3.5761589403973511E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,15 +21851,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21874,12 +21871,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50304B1C-1B3A-4AD2-8020-2922B318D6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963FB8A6-E6C8-46D1-9498-879262DE8077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.55</v>
+        <v>7.23</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7868.49742195</v>
+        <v>7534.9981934699999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>4.258909089785054E-2</v>
+        <v>5.8290687930822593E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.1524617652702114E-2</v>
+        <v>4.3362498378686158E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.5761589403973511E-2</v>
+        <v>3.7344398340248962E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.5761589403973511E-2</v>
+        <v>3.7344398340248962E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.5761589403973511E-2</v>
+        <v>3.7344398340248962E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.3377483443708618E-2</v>
+        <v>3.4854771784232373E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1258278145695377E-2</v>
+        <v>5.3526970954356851E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1524617652702114E-2</v>
+        <v>4.3362498378686158E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4431615442323981E-2</v>
+        <v>6.7283360524141897E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>4.9408416772875247E-2</v>
+        <v>5.1595234666003881E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.2421056565178227E-2</v>
+        <v>3.3856013425601052E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.6001660676568762E-2</v>
+        <v>2.7152494897385082E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11270118708131097</v>
+        <v>0.11768934473912832</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11031737744217004</v>
+        <v>0.11520002761941683</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13217491780562329</v>
+        <v>0.13802498332399113</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.11598542276370581</v>
+        <v>0.12111894078367617</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.4519186362672472E-2</v>
+        <v>8.8260007889097811E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10014097454005712</v>
+        <v>0.10457321684335147</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0573562790897065E-2</v>
+        <v>3.1926749525763874E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4969567082962753E-2</v>
+        <v>1.5632120536150592E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6761144943962603E-3</v>
+        <v>2.7945593959463021E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.0509760802591197E-2</v>
+        <v>-2.1417523383065497E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4920022005155074E-2</v>
+        <v>7.8235984251579641E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2388789047711455E-2</v>
+        <v>7.5592718853419297E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5023860326143877E-2</v>
+        <v>9.9229619012778186E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.159817123519926E-2</v>
+        <v>8.5209708551279989E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3026525264857778E-2</v>
+        <v>8.6701281569803071E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1836332871278899E-2</v>
+        <v>7.5015810951335499E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.55</v>
+        <v>7.23</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>4.258909089785054E-2</v>
+        <v>5.8290687930822593E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>7.55</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7868.49742195</v>
+        <v>7534.9981934699999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>4.258909089785054E-2</v>
+        <v>5.8290687930822593E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.1524617652702114E-2</v>
+        <v>4.3362498378686158E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>3.5761589403973511E-2</v>
+        <v>3.7344398340248962E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,12 +21851,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21871,15 +21874,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963FB8A6-E6C8-46D1-9498-879262DE8077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7DC544-65B5-4076-AEDC-55B293CF51B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.23</v>
+        <v>7.21</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7534.9981934699999</v>
+        <v>7514.1544916899993</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>5.8290687930822593E-2</v>
+        <v>5.9303448495270486E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.3362498378686158E-2</v>
+        <v>4.3482782701511923E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.7344398340248962E-2</v>
+        <v>3.7447988904299588E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.7344398340248962E-2</v>
+        <v>3.7447988904299588E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.7344398340248962E-2</v>
+        <v>3.7447988904299588E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.4854771784232373E-2</v>
+        <v>3.495145631067962E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.3526970954356851E-2</v>
+        <v>5.367545076282941E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3362498378686158E-2</v>
+        <v>4.3482782701511923E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7283360524141897E-2</v>
+        <v>6.7469999526982807E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1595234666003881E-2</v>
+        <v>5.173835598269183E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3856013425601052E-2</v>
+        <v>3.3949927471164439E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7152494897385082E-2</v>
+        <v>2.7227813884617775E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11768934473912832</v>
+        <v>0.11801580616697611</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11520002761941683</v>
+        <v>0.11551958386801439</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13802498332399113</v>
+        <v>0.13840785429021579</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12111894078367617</v>
+        <v>0.1214549156540886</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.8260007889097811E-2</v>
+        <v>8.8504834540662575E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10457321684335147</v>
+        <v>0.10486329511476161</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1926749525763874E-2</v>
+        <v>3.2015311937763226E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5632120536150592E-2</v>
+        <v>1.5675482867734923E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7945593959463021E-3</v>
+        <v>2.8023112944093988E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1417523383065497E-2</v>
+        <v>-2.1476933988843764E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8235984251579641E-2</v>
+        <v>7.8453005012332988E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5592718853419297E-2</v>
+        <v>7.5802407393928087E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9229619012778186E-2</v>
+        <v>9.9504874544020294E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5209708551279989E-2</v>
+        <v>8.5446073900936809E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6701281569803071E-2</v>
+        <v>8.6941784431300462E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5015810951335499E-2</v>
+        <v>7.5223899192531987E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.23</v>
+        <v>7.21</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>5.8290687930822593E-2</v>
+        <v>5.9303448495270486E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>7.23</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7534.9981934699999</v>
+        <v>7514.1544916899993</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>5.8290687930822593E-2</v>
+        <v>5.9303448495270486E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.3362498378686158E-2</v>
+        <v>4.3482782701511923E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>3.7344398340248962E-2</v>
+        <v>3.7447988904299588E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,15 +21851,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21874,12 +21871,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7DC544-65B5-4076-AEDC-55B293CF51B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32E2563-3DFE-44C6-907A-F63936F843CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.21</v>
+        <v>6.99</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7514.1544916899993</v>
+        <v>7284.8737721100006</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>5.9303448495270486E-2</v>
+        <v>7.0703084989331227E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.3482782701511923E-2</v>
+        <v>4.4851339524735467E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.7447988904299588E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.7447988904299588E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.7447988904299588E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.495145631067962E-2</v>
+        <v>3.6051502145922752E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.367545076282941E-2</v>
+        <v>5.5364806866952797E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.3482782701511923E-2</v>
+        <v>4.4851339524735467E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7469999526982807E-2</v>
+        <v>6.9593518825399991E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.173835598269183E-2</v>
+        <v>5.3366744869128485E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3949927471164439E-2</v>
+        <v>3.5018451654806236E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7227813884617775E-2</v>
+        <v>2.8084769400299591E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11801580616697611</v>
+        <v>0.12173018060999968</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11551958386801439</v>
+        <v>0.11915539337458995</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13840785429021579</v>
+        <v>0.14276403854541572</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.1214549156540886</v>
+        <v>0.1252775310251758</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.8504834540662575E-2</v>
+        <v>9.1290394426062543E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10486329511476161</v>
+        <v>0.10816371355900303</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2015311937763226E-2</v>
+        <v>3.3022946934373791E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5675482867734923E-2</v>
+        <v>1.6168845704773786E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8023112944093988E-3</v>
+        <v>2.8905099331461748E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1476933988843764E-2</v>
+        <v>-2.2152888992784482E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8453005012332988E-2</v>
+        <v>8.0922198303136017E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5802407393928087E-2</v>
+        <v>7.8188177011476609E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9504874544020294E-2</v>
+        <v>0.1026366445582813</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5446073900936809E-2</v>
+        <v>8.8135363780508486E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6941784431300462E-2</v>
+        <v>8.9678149606534502E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5223899192531987E-2</v>
+        <v>7.7591461112754737E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.21</v>
+        <v>6.99</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>5.9303448495270486E-2</v>
+        <v>7.0703084989331227E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>7.21</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7514.1544916899993</v>
+        <v>7284.8737721100006</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>5.9303448495270486E-2</v>
+        <v>7.0703084989331227E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.3482782701511923E-2</v>
+        <v>4.4851339524735467E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>3.7447988904299588E-2</v>
+        <v>3.8626609442060089E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,12 +21851,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21871,15 +21874,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32E2563-3DFE-44C6-907A-F63936F843CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D89F27-608C-4E8A-AC0D-C77C66FC2422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.99</v>
+        <v>6.74</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7284.8737721100006</v>
+        <v>7024.3274998600009</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>7.0703084989331227E-2</v>
+        <v>8.4267152703327367E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.4851339524735467E-2</v>
+        <v>4.6514964878026845E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.8626609442060089E-2</v>
+        <v>4.0059347181008904E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.8626609442060089E-2</v>
+        <v>4.0059347181008904E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.8626609442060089E-2</v>
+        <v>4.0059347181008904E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.6051502145922752E-2</v>
+        <v>3.7388724035608313E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.5364806866952797E-2</v>
+        <v>5.7418397626112769E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.4851339524735467E-2</v>
+        <v>4.6514964878026845E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9593518825399991E-2</v>
+        <v>7.2174880799635896E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3366744869128485E-2</v>
+        <v>5.5346223536381023E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5018451654806236E-2</v>
+        <v>3.6317355647937033E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8084769400299591E-2</v>
+        <v>2.9126489333545124E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12173018060999968</v>
+        <v>0.12624539502431717</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11915539337458995</v>
+        <v>0.12357510381133291</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14276403854541572</v>
+        <v>0.14805944056861362</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.1252775310251758</v>
+        <v>0.12992432371898796</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.1290394426062543E-2</v>
+        <v>9.4676536652548549E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10816371355900303</v>
+        <v>0.11217572073849127</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3022946934373791E-2</v>
+        <v>3.4247833690099823E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6168845704773786E-2</v>
+        <v>1.6768580337740174E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8905099331461748E-3</v>
+        <v>2.9977246932777093E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2152888992784482E-2</v>
+        <v>-2.297458368836254E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0922198303136017E-2</v>
+        <v>8.3923763522095074E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8188177011476609E-2</v>
+        <v>8.1088331945136718E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1026366445582813</v>
+        <v>0.10644364175999796</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8135363780508486E-2</v>
+        <v>9.1404479647738027E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9678149606534502E-2</v>
+        <v>9.3004490467311005E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7591461112754737E-2</v>
+        <v>8.0469482667382131E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.99</v>
+        <v>6.74</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>7.0703084989331227E-2</v>
+        <v>8.4267152703327367E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.99</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7284.8737721100006</v>
+        <v>7024.3274998600009</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>7.0703084989331227E-2</v>
+        <v>8.4267152703327367E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.4851339524735467E-2</v>
+        <v>4.6514964878026845E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>3.8626609442060089E-2</v>
+        <v>4.0059347181008904E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D89F27-608C-4E8A-AC0D-C77C66FC2422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80803A5-A306-4957-B602-29CD7258073B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.74</v>
+        <v>6.91</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7024.3274998600009</v>
+        <v>7201.4989649899999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>8.4267152703327367E-2</v>
+        <v>7.4970562689591916E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.6514964878026845E-2</v>
+        <v>4.537060250041982E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.0059347181008904E-2</v>
+        <v>3.9073806078147616E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.0059347181008904E-2</v>
+        <v>3.9073806078147616E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.0059347181008904E-2</v>
+        <v>3.9073806078147616E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.7388724035608313E-2</v>
+        <v>3.6468885672937781E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7418397626112769E-2</v>
+        <v>5.6005788712011582E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.6514964878026845E-2</v>
+        <v>4.537060250041982E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.2174880799635896E-2</v>
+        <v>7.0399232502105058E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5346223536381023E-2</v>
+        <v>5.3984594303213909E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.6317355647937033E-2</v>
+        <v>3.542387511824828E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9126489333545124E-2</v>
+        <v>2.8409918684239383E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12624539502431717</v>
+        <v>0.12313950252733687</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12357510381133291</v>
+        <v>0.1205349058883334</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14805944056861362</v>
+        <v>0.14441687835491401</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12992432371898796</v>
+        <v>0.1267279221224282</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.4676536652548549E-2</v>
+        <v>9.2347302031574124E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11217572073849127</v>
+        <v>0.10941597073479467</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4247833690099823E-2</v>
+        <v>3.3405267593527181E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6768580337740174E-2</v>
+        <v>1.6356039287462921E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9977246932777093E-3</v>
+        <v>2.9239745922853494E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.297458368836254E-2</v>
+        <v>-2.2409362381991829E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3923763522095074E-2</v>
+        <v>8.1859068905777252E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1088331945136718E-2</v>
+        <v>7.9093394690335966E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10644364175999796</v>
+        <v>0.10382491251264636</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1404479647738027E-2</v>
+        <v>8.9155744258430453E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3004490467311005E-2</v>
+        <v>9.0716391570141289E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0469482667382131E-2</v>
+        <v>7.8489770358633235E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.74</v>
+        <v>6.91</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>8.4267152703327367E-2</v>
+        <v>7.4970562689591916E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.74</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7024.3274998600009</v>
+        <v>7201.4989649899999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>8.4267152703327367E-2</v>
+        <v>7.4970562689591916E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.6514964878026845E-2</v>
+        <v>4.537060250041982E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>4.0059347181008904E-2</v>
+        <v>3.9073806078147616E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,15 +21851,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21874,12 +21871,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80803A5-A306-4957-B602-29CD7258073B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286DE096-CAD4-4532-B1A6-D036C13CABCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.91</v>
+        <v>6.52</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7201.4989649899999</v>
+        <v>6795.0467802799994</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>7.4970562689591916E-2</v>
+        <v>9.6784854223797762E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.537060250041982E-2</v>
+        <v>4.8084488232806893E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.9073806078147616E-2</v>
+        <v>4.141104294478528E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.9073806078147616E-2</v>
+        <v>4.141104294478528E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.9073806078147616E-2</v>
+        <v>4.141104294478528E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.6468885672937781E-2</v>
+        <v>3.865030674846627E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.6005788712011582E-2</v>
+        <v>5.9355828220858907E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.537060250041982E-2</v>
+        <v>4.8084488232806893E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.0399232502105058E-2</v>
+        <v>7.4610229538273926E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3984594303213909E-2</v>
+        <v>5.7213734146504311E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.542387511824828E-2</v>
+        <v>3.7542787893726323E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8409918684239383E-2</v>
+        <v>3.0109284985904015E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12313950252733687</v>
+        <v>0.1305052089668555</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.1205349058883334</v>
+        <v>0.12774481590312636</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14441687835491401</v>
+        <v>0.15305531126264663</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.1267279221224282</v>
+        <v>0.13430827329232806</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.2347302031574124E-2</v>
+        <v>9.7871143717511849E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10941597073479467</v>
+        <v>0.11596079107015816</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3405267593527181E-2</v>
+        <v>3.5403435440379272E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6356039287462921E-2</v>
+        <v>1.7334391330731409E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9239745922853494E-3</v>
+        <v>3.0988749129895344E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2409362381991829E-2</v>
+        <v>-2.3749799702387046E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1859068905777252E-2</v>
+        <v>8.6755546953822218E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9093394690335966E-2</v>
+        <v>8.3824441305248701E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10382491251264636</v>
+        <v>0.11003529838380158</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9155744258430453E-2</v>
+        <v>9.4488679881250676E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0716391570141289E-2</v>
+        <v>9.6142678795962624E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8489770358633235E-2</v>
+        <v>8.3184710610146567E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.91</v>
+        <v>6.52</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>7.4970562689591916E-2</v>
+        <v>9.6784854223797762E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.91</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7201.4989649899999</v>
+        <v>6795.0467802799994</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>7.4970562689591916E-2</v>
+        <v>9.6784854223797762E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.537060250041982E-2</v>
+        <v>4.8084488232806893E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>3.9073806078147616E-2</v>
+        <v>4.141104294478528E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,12 +21851,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21871,15 +21874,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286DE096-CAD4-4532-B1A6-D036C13CABCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152604D2-9190-45FC-BF69-EA2EE9719060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3252,10 +3252,10 @@
     <t>Historical Average or D&amp;A</t>
   </si>
   <si>
+    <t>维他奶</t>
+  </si>
+  <si>
     <t>0345.HK</t>
-  </si>
-  <si>
-    <t>维他奶</t>
   </si>
   <si>
     <t>CNS_01</t>
@@ -5342,7 +5342,7 @@
         <v>536</v>
       </c>
       <c r="C4" s="425" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E4" s="435" t="s">
         <v>540</v>
@@ -5356,7 +5356,7 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E5" s="438" t="s">
         <v>542</v>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.52</v>
+        <v>6.45</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6795.0467802799994</v>
+        <v>6722.09382405</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>9.6784854223797762E-2</v>
+        <v>0.10088941571874904</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5544,7 +5544,7 @@
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5559,7 +5559,7 @@
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.8084488232806893E-2</v>
+        <v>4.8606335391922627E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.141104294478528E-2</v>
+        <v>4.1860465116279069E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>0.49405992554973227</v>
+        <v>0.49405992554973238</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>0.56808106576265116</v>
+        <v>0.56808106576265138</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -10594,12 +10594,12 @@
         <v>239</v>
       </c>
       <c r="C86" s="73">
-        <f>-DCF!F4*Exchange_Rate</f>
-        <v>563558</v>
+        <f>DCF!F4*Exchange_Rate</f>
+        <v>-563558</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0.54074655831119844</v>
+        <v>-0.54074655831119844</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10646,11 +10646,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>1326682.9635863579</v>
+        <v>199566.96358635789</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>1.2729821003861608</v>
+        <v>0.19148898376376389</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.141104294478528E-2</v>
+        <v>4.1860465116279069E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.141104294478528E-2</v>
+        <v>4.1860465116279069E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.865030674846627E-2</v>
+        <v>3.906976744186047E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>5.9355828220858907E-2</v>
+        <v>6.0000000000000012E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8084488232806893E-2</v>
+        <v>4.8606335391922627E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4610229538273926E-2</v>
+        <v>7.5419952959619535E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7213734146504311E-2</v>
+        <v>5.7834658393055516E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.7542787893726323E-2</v>
+        <v>3.7950229002650479E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0109284985904015E-2</v>
+        <v>3.0436052419859558E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1305052089668555</v>
+        <v>0.13192154456804617</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12774481590312636</v>
+        <v>0.12913119375013701</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15305531126264663</v>
+        <v>0.1547163766561947</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13430827329232806</v>
+        <v>0.13576588245984167</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.7871143717511849E-2</v>
+        <v>9.8933311168709639E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11596079107015816</v>
+        <v>0.11721928027557073</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5403435440379272E-2</v>
+        <v>3.5787658770739972E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7334391330731409E-2</v>
+        <v>1.7522516507964152E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0988749129895344E-3</v>
+        <v>3.1325061135956222E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.3749799702387046E-2</v>
+        <v>-2.4007549466598999E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6755546953822218E-2</v>
+        <v>8.7697080021538115E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3824441305248701E-2</v>
+        <v>8.4734163924065353E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11003529838380158</v>
+        <v>0.11122947991664904</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4488679881250676E-2</v>
+        <v>9.551413842259758E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6142678795962624E-2</v>
+        <v>9.7186087713128103E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3184710610146567E-2</v>
+        <v>8.408749041521793E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.52</v>
+        <v>6.45</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>9.6784854223797762E-2</v>
+        <v>0.10088941571874904</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20160,7 +20160,7 @@
       </c>
       <c r="F53" s="252">
         <f>BS!D89/C36</f>
-        <v>0.16507960845834996</v>
+        <v>2.483218456427648E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.49405992554973227</v>
+        <v>0.49405992554973238</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.56808106576265116</v>
+        <v>0.56808106576265138</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.52</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6795.0467802799994</v>
+        <v>6722.09382405</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>9.6784854223797762E-2</v>
+        <v>0.10088941571874904</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.8084488232806893E-2</v>
+        <v>4.8606335391922627E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>4.141104294478528E-2</v>
+        <v>4.1860465116279069E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>0.49405992554973227</v>
+        <v>0.49405992554973238</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>0.56808106576265116</v>
+        <v>0.56808106576265138</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152604D2-9190-45FC-BF69-EA2EE9719060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD65855-81E6-4CAA-8237-3411ECF4F511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.45</v>
+        <v>6.37</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6722.09382405</v>
+        <v>6638.7190169300002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.10088941571874904</v>
+        <v>0.1056555578812557</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5544,7 +5544,7 @@
         <v>408</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5559,7 +5559,7 @@
         <v>409</v>
       </c>
       <c r="E23" s="448">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.8606335391922627E-2</v>
+        <v>4.9216776024788217E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.1860465116279069E-2</v>
+        <v>4.2386185243328101E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C140" s="337">
         <f>Scenarios!C62</f>
-        <v>0.49405992554973238</v>
+        <v>0.49405992554973227</v>
       </c>
       <c r="D140" s="337">
         <f>Scenarios!D62</f>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="F140" s="339">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C141" s="337">
         <f>Scenarios!C63</f>
-        <v>0.56808106576265138</v>
+        <v>0.56808106576265116</v>
       </c>
       <c r="D141" s="337">
         <f>Scenarios!D63</f>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="F141" s="339">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.1860465116279069E-2</v>
+        <v>4.2386185243328101E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.1860465116279069E-2</v>
+        <v>4.2386185243328101E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.906976744186047E-2</v>
+        <v>3.9560439560439566E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0000000000000012E-2</v>
+        <v>6.0753532182103623E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8606335391922627E-2</v>
+        <v>4.9216776024788217E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.5419952959619535E-2</v>
+        <v>7.6367142321749765E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7834658393055516E-2</v>
+        <v>5.8560996332057788E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.7950229002650479E-2</v>
+        <v>3.8426840983845467E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0436052419859558E-2</v>
+        <v>3.0818294836435504E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13192154456804617</v>
+        <v>0.13357833005712683</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12913119375013701</v>
+        <v>0.13075293558687343</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1547163766561947</v>
+        <v>0.15665943947134314</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13576588245984167</v>
+        <v>0.13747094848759478</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.8933311168709639E-2</v>
+        <v>0.10017580173283787</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11721928027557073</v>
+        <v>0.11869142194308181</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5787658770739972E-2</v>
+        <v>3.6237111314171559E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7522516507964152E-2</v>
+        <v>1.7742579509634031E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1325061135956222E-3</v>
+        <v>3.1718468497161324E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.4007549466598999E-2</v>
+        <v>-2.4309057152207776E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7697080021538115E-2</v>
+        <v>8.8798456222750524E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4734163924065353E-2</v>
+        <v>8.5798329248072444E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11122947991664904</v>
+        <v>0.11262639646191307</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.551413842259758E-2</v>
+        <v>9.6713688041719675E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7186087713128103E-2</v>
+        <v>9.8406635125537864E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.408749041521793E-2</v>
+        <v>8.5143534250887845E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.45</v>
+        <v>6.37</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10088941571874904</v>
+        <v>0.1056555578812557</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.49405992554973238</v>
+        <v>0.49405992554973227</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="F62" s="305">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="445">
         <f>(1-E62/C36)</f>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.56808106576265138</v>
+        <v>0.56808106576265116</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20271,7 +20271,7 @@
       </c>
       <c r="F63" s="305">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="445">
         <f>(1-E63/C36)</f>
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.45</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6722.09382405</v>
+        <v>6638.7190169300002</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.10088941571874904</v>
+        <v>0.1056555578812557</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20619,7 +20619,7 @@
       </c>
       <c r="E22" s="370">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="E23" s="372">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.8606335391922627E-2</v>
+        <v>4.9216776024788217E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>4.1860465116279069E-2</v>
+        <v>4.2386185243328101E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21647,7 +21647,7 @@
       </c>
       <c r="C140" s="413">
         <f>Scenarios!C62</f>
-        <v>0.49405992554973238</v>
+        <v>0.49405992554973227</v>
       </c>
       <c r="D140" s="413">
         <f>Scenarios!D62</f>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="F140" s="415">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21668,7 +21668,7 @@
       </c>
       <c r="C141" s="413">
         <f>Scenarios!C63</f>
-        <v>0.56808106576265138</v>
+        <v>0.56808106576265116</v>
       </c>
       <c r="D141" s="413">
         <f>Scenarios!D63</f>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="F141" s="415">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,15 +21851,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21874,12 +21871,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD65855-81E6-4CAA-8237-3411ECF4F511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A3112A-53EC-4FB5-9CCF-1948DFB0B13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,6 +5002,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5011,16 +5020,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.37</v>
+        <v>6.42</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6638.7190169300002</v>
+        <v>6690.8282713799999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.1056555578812557</v>
+        <v>0.10266720101005881</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="458" t="s">
+      <c r="B12" s="456" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="458"/>
-      <c r="D12" s="458"/>
-      <c r="E12" s="458"/>
-      <c r="F12" s="458"/>
+      <c r="C12" s="456"/>
+      <c r="D12" s="456"/>
+      <c r="E12" s="456"/>
+      <c r="F12" s="456"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="458" t="s">
+      <c r="B29" s="456" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="458"/>
-      <c r="D29" s="458"/>
-      <c r="E29" s="458"/>
-      <c r="F29" s="458"/>
+      <c r="C29" s="456"/>
+      <c r="D29" s="456"/>
+      <c r="E29" s="456"/>
+      <c r="F29" s="456"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="458" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="458"/>
+      <c r="D30" s="458"/>
+      <c r="E30" s="458"/>
+      <c r="F30" s="458"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="459" t="s">
+      <c r="B33" s="457" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="459"/>
-      <c r="D33" s="459"/>
-      <c r="E33" s="459"/>
-      <c r="F33" s="459"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="459" t="s">
+      <c r="B36" s="457" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="459"/>
-      <c r="D36" s="459"/>
-      <c r="E36" s="459"/>
-      <c r="F36" s="459"/>
+      <c r="C36" s="457"/>
+      <c r="D36" s="457"/>
+      <c r="E36" s="457"/>
+      <c r="F36" s="457"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="459" t="s">
+      <c r="B40" s="457" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="459"/>
-      <c r="D40" s="459"/>
-      <c r="E40" s="459"/>
-      <c r="F40" s="459"/>
+      <c r="C40" s="457"/>
+      <c r="D40" s="457"/>
+      <c r="E40" s="457"/>
+      <c r="F40" s="457"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="459" t="s">
+      <c r="B43" s="457" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="459"/>
-      <c r="D43" s="459"/>
-      <c r="E43" s="459"/>
-      <c r="F43" s="459"/>
+      <c r="C43" s="457"/>
+      <c r="D43" s="457"/>
+      <c r="E43" s="457"/>
+      <c r="F43" s="457"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="459" t="s">
+      <c r="B51" s="457" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="459"/>
-      <c r="D51" s="459"/>
-      <c r="E51" s="459"/>
-      <c r="F51" s="459"/>
+      <c r="C51" s="457"/>
+      <c r="D51" s="457"/>
+      <c r="E51" s="457"/>
+      <c r="F51" s="457"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="459" t="s">
+      <c r="B54" s="457" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="458" t="s">
+      <c r="B57" s="456" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="458"/>
-      <c r="D57" s="458"/>
-      <c r="E57" s="458"/>
-      <c r="F57" s="458"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="458" t="s">
+      <c r="B58" s="456" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="458"/>
-      <c r="D58" s="458"/>
-      <c r="E58" s="458"/>
-      <c r="F58" s="458"/>
+      <c r="C58" s="456"/>
+      <c r="D58" s="456"/>
+      <c r="E58" s="456"/>
+      <c r="F58" s="456"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.9216776024788217E-2</v>
+        <v>4.8833467800296099E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.2386185243328101E-2</v>
+        <v>4.2056074766355145E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="458" t="s">
+      <c r="B73" s="456" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="458"/>
-      <c r="D73" s="458"/>
-      <c r="E73" s="458"/>
-      <c r="F73" s="458"/>
+      <c r="C73" s="456"/>
+      <c r="D73" s="456"/>
+      <c r="E73" s="456"/>
+      <c r="F73" s="456"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="458" t="s">
+      <c r="B77" s="456" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="458"/>
-      <c r="D77" s="458"/>
-      <c r="E77" s="458"/>
-      <c r="F77" s="458"/>
+      <c r="C77" s="456"/>
+      <c r="D77" s="456"/>
+      <c r="E77" s="456"/>
+      <c r="F77" s="456"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="458" t="s">
+      <c r="B96" s="456" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="458"/>
-      <c r="D96" s="458"/>
-      <c r="E96" s="458"/>
-      <c r="F96" s="458"/>
+      <c r="C96" s="456"/>
+      <c r="D96" s="456"/>
+      <c r="E96" s="456"/>
+      <c r="F96" s="456"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="458" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="458"/>
+      <c r="D97" s="458"/>
+      <c r="E97" s="458"/>
+      <c r="F97" s="458"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="458" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="458"/>
+      <c r="D98" s="458"/>
+      <c r="E98" s="458"/>
+      <c r="F98" s="458"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="458" t="s">
+      <c r="B107" s="456" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="458"/>
-      <c r="D107" s="458"/>
-      <c r="E107" s="458"/>
-      <c r="F107" s="458"/>
+      <c r="C107" s="456"/>
+      <c r="D107" s="456"/>
+      <c r="E107" s="456"/>
+      <c r="F107" s="456"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="458" t="s">
+      <c r="B108" s="456" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="458"/>
-      <c r="D108" s="458"/>
-      <c r="E108" s="458"/>
-      <c r="F108" s="458"/>
+      <c r="C108" s="456"/>
+      <c r="D108" s="456"/>
+      <c r="E108" s="456"/>
+      <c r="F108" s="456"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="458" t="s">
+      <c r="B114" s="456" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="458"/>
-      <c r="D114" s="458"/>
-      <c r="E114" s="458"/>
-      <c r="F114" s="458"/>
+      <c r="C114" s="456"/>
+      <c r="D114" s="456"/>
+      <c r="E114" s="456"/>
+      <c r="F114" s="456"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="459" t="s">
+      <c r="B124" s="457" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="459"/>
-      <c r="D124" s="459"/>
-      <c r="E124" s="459"/>
-      <c r="F124" s="459"/>
+      <c r="C124" s="457"/>
+      <c r="D124" s="457"/>
+      <c r="E124" s="457"/>
+      <c r="F124" s="457"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="459" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="459"/>
+      <c r="D131" s="459"/>
+      <c r="E131" s="459"/>
+      <c r="F131" s="459"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="458" t="s">
+      <c r="B132" s="456" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="458"/>
-      <c r="D132" s="458"/>
-      <c r="E132" s="458"/>
-      <c r="F132" s="458"/>
+      <c r="C132" s="456"/>
+      <c r="D132" s="456"/>
+      <c r="E132" s="456"/>
+      <c r="F132" s="456"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="457" t="s">
+      <c r="B149" s="463" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="458"/>
-      <c r="D149" s="458"/>
-      <c r="E149" s="458"/>
-      <c r="F149" s="458"/>
+      <c r="C149" s="456"/>
+      <c r="D149" s="456"/>
+      <c r="E149" s="456"/>
+      <c r="F149" s="456"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="459" t="s">
+      <c r="B158" s="457" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="459"/>
-      <c r="D158" s="459"/>
-      <c r="E158" s="459"/>
-      <c r="F158" s="459"/>
+      <c r="C158" s="457"/>
+      <c r="D158" s="457"/>
+      <c r="E158" s="457"/>
+      <c r="F158" s="457"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="456" t="s">
+      <c r="B161" s="462" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="456"/>
-      <c r="D161" s="456"/>
-      <c r="E161" s="456"/>
-      <c r="F161" s="456"/>
+      <c r="C161" s="462"/>
+      <c r="D161" s="462"/>
+      <c r="E161" s="462"/>
+      <c r="F161" s="462"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="456" t="s">
+      <c r="B162" s="462" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="456"/>
-      <c r="D162" s="456"/>
-      <c r="E162" s="456"/>
-      <c r="F162" s="456"/>
+      <c r="C162" s="462"/>
+      <c r="D162" s="462"/>
+      <c r="E162" s="462"/>
+      <c r="F162" s="462"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,6 +6773,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6789,18 +6801,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.2386185243328101E-2</v>
+        <v>4.2056074766355145E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.2386185243328101E-2</v>
+        <v>4.2056074766355145E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.9560439560439566E-2</v>
+        <v>3.9252336448598144E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0753532182103623E-2</v>
+        <v>6.0280373831775709E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9216776024788217E-2</v>
+        <v>4.8833467800296099E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6367142321749765E-2</v>
+        <v>7.5772382646346725E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.8560996332057788E-2</v>
+        <v>5.8104913806107182E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8426840983845467E-2</v>
+        <v>3.8127566521354454E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0818294836435504E-2</v>
+        <v>3.0578276963877594E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13357833005712683</v>
+        <v>0.13253800038378472</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.13075293558687343</v>
+        <v>0.12973461054336197</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15665943947134314</v>
+        <v>0.1554393503788872</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13747094848759478</v>
+        <v>0.13640030247133628</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.10017580173283787</v>
+        <v>9.9395616361086792E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11869142194308181</v>
+        <v>0.11776703392171825</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6237111314171559E-2</v>
+        <v>3.5954890821070534E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7742579509634031E-2</v>
+        <v>1.7604397426225667E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1718468497161324E-3</v>
+        <v>3.1471439926311156E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.4309057152207776E-2</v>
+        <v>-2.4119734277190583E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8798456222750524E-2</v>
+        <v>8.8106879460891088E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5798329248072444E-2</v>
+        <v>8.5130117961093696E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11262639646191307</v>
+        <v>0.11174924384149319</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6713688041719675E-2</v>
+        <v>9.5960466172235886E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8406635125537864E-2</v>
+        <v>9.764022830991842E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5143534250887845E-2</v>
+        <v>8.4480422613419884E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.37</v>
+        <v>6.42</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1056555578812557</v>
+        <v>0.10266720101005881</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.37</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6638.7190169300002</v>
+        <v>6690.8282713799999</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.1056555578812557</v>
+        <v>0.10266720101005881</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="470" t="s">
+      <c r="B12" s="467" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="470"/>
-      <c r="D12" s="470"/>
-      <c r="E12" s="470"/>
-      <c r="F12" s="470"/>
+      <c r="C12" s="467"/>
+      <c r="D12" s="467"/>
+      <c r="E12" s="467"/>
+      <c r="F12" s="467"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="470" t="s">
+      <c r="B29" s="467" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
+      <c r="C29" s="467"/>
+      <c r="D29" s="467"/>
+      <c r="E29" s="467"/>
+      <c r="F29" s="467"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
+      <c r="B30" s="468" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="468"/>
+      <c r="D30" s="468"/>
+      <c r="E30" s="468"/>
+      <c r="F30" s="468"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="472"/>
-      <c r="D54" s="472"/>
-      <c r="E54" s="472"/>
-      <c r="F54" s="472"/>
+      <c r="C54" s="469"/>
+      <c r="D54" s="469"/>
+      <c r="E54" s="469"/>
+      <c r="F54" s="469"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="470" t="s">
+      <c r="B57" s="467" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="470"/>
-      <c r="D57" s="470"/>
-      <c r="E57" s="470"/>
-      <c r="F57" s="470"/>
+      <c r="C57" s="467"/>
+      <c r="D57" s="467"/>
+      <c r="E57" s="467"/>
+      <c r="F57" s="467"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="470" t="s">
+      <c r="B58" s="467" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="470"/>
-      <c r="D58" s="470"/>
-      <c r="E58" s="470"/>
-      <c r="F58" s="470"/>
+      <c r="C58" s="467"/>
+      <c r="D58" s="467"/>
+      <c r="E58" s="467"/>
+      <c r="F58" s="467"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.9216776024788217E-2</v>
+        <v>4.8833467800296099E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>4.2386185243328101E-2</v>
+        <v>4.2056074766355145E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="470" t="s">
+      <c r="B73" s="467" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="470"/>
-      <c r="D73" s="470"/>
-      <c r="E73" s="470"/>
-      <c r="F73" s="470"/>
+      <c r="C73" s="467"/>
+      <c r="D73" s="467"/>
+      <c r="E73" s="467"/>
+      <c r="F73" s="467"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
+      <c r="B74" s="468" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="C74" s="468"/>
+      <c r="D74" s="468"/>
+      <c r="E74" s="468"/>
+      <c r="F74" s="468"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="470" t="s">
+      <c r="B77" s="467" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="470"/>
-      <c r="D77" s="470"/>
-      <c r="E77" s="470"/>
-      <c r="F77" s="470"/>
+      <c r="C77" s="467"/>
+      <c r="D77" s="467"/>
+      <c r="E77" s="467"/>
+      <c r="F77" s="467"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="470" t="s">
+      <c r="B96" s="467" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="470"/>
-      <c r="D96" s="470"/>
-      <c r="E96" s="470"/>
-      <c r="F96" s="470"/>
+      <c r="C96" s="467"/>
+      <c r="D96" s="467"/>
+      <c r="E96" s="467"/>
+      <c r="F96" s="467"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="473" t="s">
+      <c r="B97" s="468" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="C97" s="468"/>
+      <c r="D97" s="468"/>
+      <c r="E97" s="468"/>
+      <c r="F97" s="468"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="473" t="s">
+      <c r="B98" s="468" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="C98" s="468"/>
+      <c r="D98" s="468"/>
+      <c r="E98" s="468"/>
+      <c r="F98" s="468"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="470" t="s">
+      <c r="B107" s="467" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="470"/>
-      <c r="D107" s="470"/>
-      <c r="E107" s="470"/>
-      <c r="F107" s="470"/>
+      <c r="C107" s="467"/>
+      <c r="D107" s="467"/>
+      <c r="E107" s="467"/>
+      <c r="F107" s="467"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="470" t="s">
+      <c r="B108" s="467" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="470"/>
-      <c r="D108" s="470"/>
-      <c r="E108" s="470"/>
-      <c r="F108" s="470"/>
+      <c r="C108" s="467"/>
+      <c r="D108" s="467"/>
+      <c r="E108" s="467"/>
+      <c r="F108" s="467"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="470" t="s">
+      <c r="B114" s="467" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="470"/>
-      <c r="D114" s="470"/>
-      <c r="E114" s="470"/>
-      <c r="F114" s="470"/>
+      <c r="C114" s="467"/>
+      <c r="D114" s="467"/>
+      <c r="E114" s="467"/>
+      <c r="F114" s="467"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="468" t="s">
+      <c r="B127" s="471" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="468"/>
-      <c r="D127" s="468"/>
-      <c r="E127" s="468"/>
-      <c r="F127" s="468"/>
+      <c r="C127" s="471"/>
+      <c r="D127" s="471"/>
+      <c r="E127" s="471"/>
+      <c r="F127" s="471"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="469" t="s">
+      <c r="B131" s="472" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="469"/>
-      <c r="D131" s="469"/>
-      <c r="E131" s="469"/>
-      <c r="F131" s="469"/>
+      <c r="C131" s="472"/>
+      <c r="D131" s="472"/>
+      <c r="E131" s="472"/>
+      <c r="F131" s="472"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="470" t="s">
+      <c r="B132" s="467" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="470"/>
-      <c r="D132" s="470"/>
-      <c r="E132" s="470"/>
-      <c r="F132" s="470"/>
+      <c r="C132" s="467"/>
+      <c r="D132" s="467"/>
+      <c r="E132" s="467"/>
+      <c r="F132" s="467"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="471" t="s">
+      <c r="B149" s="473" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="470"/>
-      <c r="D149" s="470"/>
-      <c r="E149" s="470"/>
-      <c r="F149" s="470"/>
+      <c r="C149" s="467"/>
+      <c r="D149" s="467"/>
+      <c r="E149" s="467"/>
+      <c r="F149" s="467"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="472" t="s">
+      <c r="B152" s="469" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="472"/>
-      <c r="D152" s="472"/>
-      <c r="E152" s="472"/>
-      <c r="F152" s="472"/>
+      <c r="C152" s="469"/>
+      <c r="D152" s="469"/>
+      <c r="E152" s="469"/>
+      <c r="F152" s="469"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="470" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="470"/>
+      <c r="D161" s="470"/>
+      <c r="E161" s="470"/>
+      <c r="F161" s="470"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="470" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="470"/>
+      <c r="D162" s="470"/>
+      <c r="E162" s="470"/>
+      <c r="F162" s="470"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,12 +21851,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21871,15 +21874,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A3112A-53EC-4FB5-9CCF-1948DFB0B13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5238AD5F-00CE-409A-9FF3-D41869833E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4969,30 +4969,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5002,25 +5002,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5390,7 +5390,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.42</v>
+        <v>6.53</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5408,14 +5408,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6690.8282713799999</v>
+        <v>6805.4686311699998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>531</v>
       </c>
       <c r="E10" s="307">
         <f>Scenarios!F34</f>
-        <v>0.10266720101005881</v>
+        <v>9.6203404893799888E-2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5423,13 +5423,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="456" t="s">
+      <c r="B12" s="458" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="456"/>
-      <c r="D12" s="456"/>
-      <c r="E12" s="456"/>
-      <c r="F12" s="456"/>
+      <c r="C12" s="458"/>
+      <c r="D12" s="458"/>
+      <c r="E12" s="458"/>
+      <c r="F12" s="458"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5607,22 +5607,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="456" t="s">
+      <c r="B29" s="458" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="456"/>
-      <c r="D29" s="456"/>
-      <c r="E29" s="456"/>
-      <c r="F29" s="456"/>
+      <c r="C29" s="458"/>
+      <c r="D29" s="458"/>
+      <c r="E29" s="458"/>
+      <c r="F29" s="458"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="458" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="458"/>
-      <c r="D30" s="458"/>
-      <c r="E30" s="458"/>
-      <c r="F30" s="458"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5634,13 +5634,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="457" t="s">
+      <c r="B33" s="459" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="457"/>
-      <c r="D33" s="457"/>
-      <c r="E33" s="457"/>
-      <c r="F33" s="457"/>
+      <c r="C33" s="459"/>
+      <c r="D33" s="459"/>
+      <c r="E33" s="459"/>
+      <c r="F33" s="459"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5660,13 +5660,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="457" t="s">
+      <c r="B36" s="459" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="457"/>
-      <c r="D36" s="457"/>
-      <c r="E36" s="457"/>
-      <c r="F36" s="457"/>
+      <c r="C36" s="459"/>
+      <c r="D36" s="459"/>
+      <c r="E36" s="459"/>
+      <c r="F36" s="459"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5695,13 +5695,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="457" t="s">
+      <c r="B40" s="459" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="457"/>
-      <c r="D40" s="457"/>
-      <c r="E40" s="457"/>
-      <c r="F40" s="457"/>
+      <c r="C40" s="459"/>
+      <c r="D40" s="459"/>
+      <c r="E40" s="459"/>
+      <c r="F40" s="459"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="457" t="s">
+      <c r="B43" s="459" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="457"/>
-      <c r="D43" s="457"/>
-      <c r="E43" s="457"/>
-      <c r="F43" s="457"/>
+      <c r="C43" s="459"/>
+      <c r="D43" s="459"/>
+      <c r="E43" s="459"/>
+      <c r="F43" s="459"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5787,13 +5787,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="457" t="s">
+      <c r="B51" s="459" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="457"/>
-      <c r="D51" s="457"/>
-      <c r="E51" s="457"/>
-      <c r="F51" s="457"/>
+      <c r="C51" s="459"/>
+      <c r="D51" s="459"/>
+      <c r="E51" s="459"/>
+      <c r="F51" s="459"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5809,7 +5809,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="457" t="s">
+      <c r="B54" s="459" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="460"/>
@@ -5831,22 +5831,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="456" t="s">
+      <c r="B57" s="458" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="456"/>
-      <c r="D57" s="456"/>
-      <c r="E57" s="456"/>
-      <c r="F57" s="456"/>
+      <c r="C57" s="458"/>
+      <c r="D57" s="458"/>
+      <c r="E57" s="458"/>
+      <c r="F57" s="458"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="456" t="s">
+      <c r="B58" s="458" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="456"/>
-      <c r="D58" s="456"/>
-      <c r="E58" s="456"/>
-      <c r="F58" s="456"/>
+      <c r="C58" s="458"/>
+      <c r="D58" s="458"/>
+      <c r="E58" s="458"/>
+      <c r="F58" s="458"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>4.8833467800296099E-2</v>
+        <v>4.8010851956799536E-2</v>
       </c>
       <c r="F62" s="260"/>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>4.2056074766355145E-2</v>
+        <v>4.1347626339969371E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5981,13 +5981,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="456" t="s">
+      <c r="B73" s="458" t="s">
         <v>481</v>
       </c>
-      <c r="C73" s="456"/>
-      <c r="D73" s="456"/>
-      <c r="E73" s="456"/>
-      <c r="F73" s="456"/>
+      <c r="C73" s="458"/>
+      <c r="D73" s="458"/>
+      <c r="E73" s="458"/>
+      <c r="F73" s="458"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="456" t="s">
+      <c r="B77" s="458" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="456"/>
-      <c r="D77" s="456"/>
-      <c r="E77" s="456"/>
-      <c r="F77" s="456"/>
+      <c r="C77" s="458"/>
+      <c r="D77" s="458"/>
+      <c r="E77" s="458"/>
+      <c r="F77" s="458"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6181,31 +6181,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="456" t="s">
+      <c r="B96" s="458" t="s">
         <v>488</v>
       </c>
-      <c r="C96" s="456"/>
-      <c r="D96" s="456"/>
-      <c r="E96" s="456"/>
-      <c r="F96" s="456"/>
+      <c r="C96" s="458"/>
+      <c r="D96" s="458"/>
+      <c r="E96" s="458"/>
+      <c r="F96" s="458"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="458" t="s">
+      <c r="B97" s="462" t="s">
         <v>487</v>
       </c>
-      <c r="C97" s="458"/>
-      <c r="D97" s="458"/>
-      <c r="E97" s="458"/>
-      <c r="F97" s="458"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="458" t="s">
+      <c r="B98" s="462" t="s">
         <v>486</v>
       </c>
-      <c r="C98" s="458"/>
-      <c r="D98" s="458"/>
-      <c r="E98" s="458"/>
-      <c r="F98" s="458"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6255,22 +6255,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="456" t="s">
+      <c r="B107" s="458" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="456"/>
-      <c r="D107" s="456"/>
-      <c r="E107" s="456"/>
-      <c r="F107" s="456"/>
+      <c r="C107" s="458"/>
+      <c r="D107" s="458"/>
+      <c r="E107" s="458"/>
+      <c r="F107" s="458"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="456" t="s">
+      <c r="B108" s="458" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="456"/>
-      <c r="D108" s="456"/>
-      <c r="E108" s="456"/>
-      <c r="F108" s="456"/>
+      <c r="C108" s="458"/>
+      <c r="D108" s="458"/>
+      <c r="E108" s="458"/>
+      <c r="F108" s="458"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6304,13 +6304,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="456" t="s">
+      <c r="B114" s="458" t="s">
         <v>494</v>
       </c>
-      <c r="C114" s="456"/>
-      <c r="D114" s="456"/>
-      <c r="E114" s="456"/>
-      <c r="F114" s="456"/>
+      <c r="C114" s="458"/>
+      <c r="D114" s="458"/>
+      <c r="E114" s="458"/>
+      <c r="F114" s="458"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6445,13 +6445,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="457" t="s">
+      <c r="B124" s="459" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="457"/>
-      <c r="D124" s="457"/>
-      <c r="E124" s="457"/>
-      <c r="F124" s="457"/>
+      <c r="C124" s="459"/>
+      <c r="D124" s="459"/>
+      <c r="E124" s="459"/>
+      <c r="F124" s="459"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6486,22 +6486,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="459" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="459"/>
-      <c r="D131" s="459"/>
-      <c r="E131" s="459"/>
-      <c r="F131" s="459"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="456" t="s">
+      <c r="B132" s="458" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="456"/>
-      <c r="D132" s="456"/>
-      <c r="E132" s="456"/>
-      <c r="F132" s="456"/>
+      <c r="C132" s="458"/>
+      <c r="D132" s="458"/>
+      <c r="E132" s="458"/>
+      <c r="F132" s="458"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6677,13 +6677,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="463" t="s">
+      <c r="B149" s="457" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="456"/>
-      <c r="D149" s="456"/>
-      <c r="E149" s="456"/>
-      <c r="F149" s="456"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="458"/>
+      <c r="E149" s="458"/>
+      <c r="F149" s="458"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6720,13 +6720,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="457" t="s">
+      <c r="B158" s="459" t="s">
         <v>441</v>
       </c>
-      <c r="C158" s="457"/>
-      <c r="D158" s="457"/>
-      <c r="E158" s="457"/>
-      <c r="F158" s="457"/>
+      <c r="C158" s="459"/>
+      <c r="D158" s="459"/>
+      <c r="E158" s="459"/>
+      <c r="F158" s="459"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6734,22 +6734,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="462" t="s">
+      <c r="B161" s="456" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="462"/>
-      <c r="D161" s="462"/>
-      <c r="E161" s="462"/>
-      <c r="F161" s="462"/>
+      <c r="C161" s="456"/>
+      <c r="D161" s="456"/>
+      <c r="E161" s="456"/>
+      <c r="F161" s="456"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="462" t="s">
+      <c r="B162" s="456" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="462"/>
-      <c r="D162" s="462"/>
-      <c r="E162" s="462"/>
-      <c r="F162" s="462"/>
+      <c r="C162" s="456"/>
+      <c r="D162" s="456"/>
+      <c r="E162" s="456"/>
+      <c r="F162" s="456"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6773,18 +6773,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6801,6 +6789,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14233,20 +14233,20 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>4.2056074766355145E-2</v>
+        <v>4.1347626339969371E-2</v>
       </c>
       <c r="E92" s="238"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>4.2056074766355145E-2</v>
+        <v>4.1347626339969371E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.9252336448598144E-2</v>
+        <v>3.8591117917304754E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>6.0280373831775709E-2</v>
+        <v>5.9264931087289439E-2</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
@@ -15432,50 +15432,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8833467800296099E-2</v>
+        <v>4.8010851956799536E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="235"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.5772382646346725E-2</v>
+        <v>7.449597191264104E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.8104913806107182E-2</v>
+        <v>5.7126117402022676E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8127566521354454E-2</v>
+        <v>3.7485295109815561E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0578276963877594E-2</v>
+        <v>3.0063175820535092E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13253800038378472</v>
+        <v>0.13030535412923397</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12973461054336197</v>
+        <v>0.12754918831368817</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1554393503788872</v>
+        <v>0.15282092334340824</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13640030247133628</v>
+        <v>0.13410259446645922</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.9395616361086792E-2</v>
+        <v>9.772126447751564E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11776703392171825</v>
+        <v>0.11578320946055608</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15489,43 +15489,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5954890821070534E-2</v>
+        <v>3.5349218847055566E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7604397426225667E-2</v>
+        <v>1.7307845555339783E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1471439926311156E-3</v>
+        <v>3.0941293158792899E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.4119734277190583E-2</v>
+        <v>-2.3713429411878029E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8106879460891088E-2</v>
+        <v>8.6622690067216054E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5130117961093696E-2</v>
+        <v>8.3696073094980325E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11174924384149319</v>
+        <v>0.10986679103558748</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5960466172235886E-2</v>
+        <v>9.4343980524617829E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.764022830991842E-2</v>
+        <v>9.599544651603005E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4480422613419884E-2</v>
+        <v>8.3057322079350016E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19954,7 +19954,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.42</v>
+        <v>6.53</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="F34" s="334">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10266720101005881</v>
+        <v>9.6203404893799888E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C8" s="360">
         <f>Market_Price</f>
-        <v>6.42</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20475,14 +20475,14 @@
       </c>
       <c r="C10" s="361">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6690.8282713799999</v>
+        <v>6805.4686311699998</v>
       </c>
       <c r="D10" s="347" t="s">
         <v>532</v>
       </c>
       <c r="E10" s="364">
         <f>Scenarios!F34</f>
-        <v>0.10266720101005881</v>
+        <v>9.6203404893799888E-2</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20490,13 +20490,13 @@
       <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="467" t="s">
+      <c r="B12" s="470" t="s">
         <v>501</v>
       </c>
-      <c r="C12" s="467"/>
-      <c r="D12" s="467"/>
-      <c r="E12" s="467"/>
-      <c r="F12" s="467"/>
+      <c r="C12" s="470"/>
+      <c r="D12" s="470"/>
+      <c r="E12" s="470"/>
+      <c r="F12" s="470"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="351" t="s">
@@ -20681,22 +20681,22 @@
       <c r="F27" s="349"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="467" t="s">
+      <c r="B29" s="470" t="s">
         <v>502</v>
       </c>
-      <c r="C29" s="467"/>
-      <c r="D29" s="467"/>
-      <c r="E29" s="467"/>
-      <c r="F29" s="467"/>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="468" t="s">
+      <c r="B30" s="473" t="s">
         <v>503</v>
       </c>
-      <c r="C30" s="468"/>
-      <c r="D30" s="468"/>
-      <c r="E30" s="468"/>
-      <c r="F30" s="468"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="373" t="s">
@@ -20886,10 +20886,10 @@
       <c r="B54" s="466" t="s">
         <v>510</v>
       </c>
-      <c r="C54" s="469"/>
-      <c r="D54" s="469"/>
-      <c r="E54" s="469"/>
-      <c r="F54" s="469"/>
+      <c r="C54" s="472"/>
+      <c r="D54" s="472"/>
+      <c r="E54" s="472"/>
+      <c r="F54" s="472"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="376" t="s">
@@ -20905,22 +20905,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="467" t="s">
+      <c r="B57" s="470" t="s">
         <v>511</v>
       </c>
-      <c r="C57" s="467"/>
-      <c r="D57" s="467"/>
-      <c r="E57" s="467"/>
-      <c r="F57" s="467"/>
+      <c r="C57" s="470"/>
+      <c r="D57" s="470"/>
+      <c r="E57" s="470"/>
+      <c r="F57" s="470"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="467" t="s">
+      <c r="B58" s="470" t="s">
         <v>512</v>
       </c>
-      <c r="C58" s="467"/>
-      <c r="D58" s="467"/>
-      <c r="E58" s="467"/>
-      <c r="F58" s="467"/>
+      <c r="C58" s="470"/>
+      <c r="D58" s="470"/>
+      <c r="E58" s="470"/>
+      <c r="F58" s="470"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="376" t="s">
@@ -20954,7 +20954,7 @@
       </c>
       <c r="C62" s="382">
         <f>Normalized_FCF!C124</f>
-        <v>4.8833467800296099E-2</v>
+        <v>4.8010851956799536E-2</v>
       </c>
       <c r="F62" s="383"/>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C63" s="382">
         <f>Normalized_FCF!C92</f>
-        <v>4.2056074766355145E-2</v>
+        <v>4.1347626339969371E-2</v>
       </c>
       <c r="E63" s="376" t="s">
         <v>373</v>
@@ -21055,22 +21055,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="390"/>
-      <c r="B73" s="467" t="s">
+      <c r="B73" s="470" t="s">
         <v>513</v>
       </c>
-      <c r="C73" s="467"/>
-      <c r="D73" s="467"/>
-      <c r="E73" s="467"/>
-      <c r="F73" s="467"/>
+      <c r="C73" s="470"/>
+      <c r="D73" s="470"/>
+      <c r="E73" s="470"/>
+      <c r="F73" s="470"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="468" t="s">
+      <c r="B74" s="473" t="s">
         <v>482</v>
       </c>
-      <c r="C74" s="468"/>
-      <c r="D74" s="468"/>
-      <c r="E74" s="468"/>
-      <c r="F74" s="468"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="373" t="s">
@@ -21078,13 +21078,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="467" t="s">
+      <c r="B77" s="470" t="s">
         <v>514</v>
       </c>
-      <c r="C77" s="467"/>
-      <c r="D77" s="467"/>
-      <c r="E77" s="467"/>
-      <c r="F77" s="467"/>
+      <c r="C77" s="470"/>
+      <c r="D77" s="470"/>
+      <c r="E77" s="470"/>
+      <c r="F77" s="470"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="347" t="s">
@@ -21233,33 +21233,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="389"/>
-      <c r="B96" s="467" t="s">
+      <c r="B96" s="470" t="s">
         <v>517</v>
       </c>
-      <c r="C96" s="467"/>
-      <c r="D96" s="467"/>
-      <c r="E96" s="467"/>
-      <c r="F96" s="467"/>
+      <c r="C96" s="470"/>
+      <c r="D96" s="470"/>
+      <c r="E96" s="470"/>
+      <c r="F96" s="470"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="389"/>
-      <c r="B97" s="468" t="s">
+      <c r="B97" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C97" s="468"/>
-      <c r="D97" s="468"/>
-      <c r="E97" s="468"/>
-      <c r="F97" s="468"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="389"/>
-      <c r="B98" s="468" t="s">
+      <c r="B98" s="473" t="s">
         <v>519</v>
       </c>
-      <c r="C98" s="468"/>
-      <c r="D98" s="468"/>
-      <c r="E98" s="468"/>
-      <c r="F98" s="468"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="389"/>
@@ -21322,23 +21322,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="389"/>
-      <c r="B107" s="467" t="s">
+      <c r="B107" s="470" t="s">
         <v>520</v>
       </c>
-      <c r="C107" s="467"/>
-      <c r="D107" s="467"/>
-      <c r="E107" s="467"/>
-      <c r="F107" s="467"/>
+      <c r="C107" s="470"/>
+      <c r="D107" s="470"/>
+      <c r="E107" s="470"/>
+      <c r="F107" s="470"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="389"/>
-      <c r="B108" s="467" t="s">
+      <c r="B108" s="470" t="s">
         <v>539</v>
       </c>
-      <c r="C108" s="467"/>
-      <c r="D108" s="467"/>
-      <c r="E108" s="467"/>
-      <c r="F108" s="467"/>
+      <c r="C108" s="470"/>
+      <c r="D108" s="470"/>
+      <c r="E108" s="470"/>
+      <c r="F108" s="470"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="389"/>
@@ -21382,13 +21382,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="389"/>
-      <c r="B114" s="467" t="s">
+      <c r="B114" s="470" t="s">
         <v>521</v>
       </c>
-      <c r="C114" s="467"/>
-      <c r="D114" s="467"/>
-      <c r="E114" s="467"/>
-      <c r="F114" s="467"/>
+      <c r="C114" s="470"/>
+      <c r="D114" s="470"/>
+      <c r="E114" s="470"/>
+      <c r="F114" s="470"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="389"/>
@@ -21552,13 +21552,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="471" t="s">
+      <c r="B127" s="468" t="s">
         <v>523</v>
       </c>
-      <c r="C127" s="471"/>
-      <c r="D127" s="471"/>
-      <c r="E127" s="471"/>
-      <c r="F127" s="471"/>
+      <c r="C127" s="468"/>
+      <c r="D127" s="468"/>
+      <c r="E127" s="468"/>
+      <c r="F127" s="468"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="349" t="s">
@@ -21571,22 +21571,22 @@
       <c r="F129" s="349"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="472" t="s">
+      <c r="B131" s="469" t="s">
         <v>524</v>
       </c>
-      <c r="C131" s="472"/>
-      <c r="D131" s="472"/>
-      <c r="E131" s="472"/>
-      <c r="F131" s="472"/>
+      <c r="C131" s="469"/>
+      <c r="D131" s="469"/>
+      <c r="E131" s="469"/>
+      <c r="F131" s="469"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="467" t="s">
+      <c r="B132" s="470" t="s">
         <v>525</v>
       </c>
-      <c r="C132" s="467"/>
-      <c r="D132" s="467"/>
-      <c r="E132" s="467"/>
-      <c r="F132" s="467"/>
+      <c r="C132" s="470"/>
+      <c r="D132" s="470"/>
+      <c r="E132" s="470"/>
+      <c r="F132" s="470"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="373" t="s">
@@ -21755,13 +21755,13 @@
       <c r="F147" s="349"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="473" t="s">
+      <c r="B149" s="471" t="s">
         <v>526</v>
       </c>
-      <c r="C149" s="467"/>
-      <c r="D149" s="467"/>
-      <c r="E149" s="467"/>
-      <c r="F149" s="467"/>
+      <c r="C149" s="470"/>
+      <c r="D149" s="470"/>
+      <c r="E149" s="470"/>
+      <c r="F149" s="470"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="373" t="s">
@@ -21769,13 +21769,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="469" t="s">
+      <c r="B152" s="472" t="s">
         <v>527</v>
       </c>
-      <c r="C152" s="469"/>
-      <c r="D152" s="469"/>
-      <c r="E152" s="469"/>
-      <c r="F152" s="469"/>
+      <c r="C152" s="472"/>
+      <c r="D152" s="472"/>
+      <c r="E152" s="472"/>
+      <c r="F152" s="472"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="416" t="s">
@@ -21812,22 +21812,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="470" t="s">
+      <c r="B161" s="467" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="470"/>
-      <c r="D161" s="470"/>
-      <c r="E161" s="470"/>
-      <c r="F161" s="470"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="470" t="s">
+      <c r="B162" s="467" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="470"/>
-      <c r="D162" s="470"/>
-      <c r="E162" s="470"/>
-      <c r="F162" s="470"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="347" t="s">
@@ -21851,15 +21851,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21874,12 +21871,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE48B498-FFC2-40C8-81FE-FB489B5C44A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F17E48-BBE1-4D2F-A9EA-3CEE932CF8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E10" s="306">
         <f>Scenarios!F34</f>
-        <v>0.24433009042746481</v>
+        <v>0.19401097353978844</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C18" s="254">
         <f>C125</f>
-        <v>12.192767818192898</v>
+        <v>10.738252335306031</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>344</v>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C22" s="257">
         <f>E140</f>
-        <v>5.8526420444189942</v>
+        <v>5.1823584117522348</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C23" s="258">
         <f>E141</f>
-        <v>7.311645678868441</v>
+        <v>6.471492331352561</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C24" s="258">
         <f>E144</f>
-        <v>9.0476237328011386</v>
+        <v>8.0050846436410321</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>407</v>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="C25" s="258">
         <f>E145</f>
-        <v>10.217353238803947</v>
+        <v>9.0383189215069883</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>408</v>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C34" s="288">
         <f>Normalized_FCF!C8</f>
-        <v>767207.54639827425</v>
+        <v>914466.27600619278</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="C52" s="288">
         <f>Normalized_FCF!C12</f>
-        <v>-184073.41200989831</v>
+        <v>-220888.09441187794</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C61" s="288">
         <f>Normalized_FCF!C19</f>
-        <v>517879.86501135764</v>
+        <v>628323.91221729654</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="C62" s="88">
         <f>Normalized_FCF!C124</f>
-        <v>7.5519355908056987E-2</v>
+        <v>9.1624757705612153E-2</v>
       </c>
       <c r="F62" s="259"/>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="F63" s="260">
         <f>Normalized_FCF!C90</f>
-        <v>0.28576180044141009</v>
+        <v>0.23553183280221826</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="C66" s="88">
         <f>Normalized_FCF!C119</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D66" s="88">
         <f>Normalized_FCF!G119</f>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C67" s="265">
         <f>Normalized_FCF!C116</f>
-        <v>0.1173640985241442</v>
+        <v>0.14083691822897304</v>
       </c>
       <c r="D67" s="265">
         <f>Normalized_FCF!G116</f>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C81" s="341">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0.73455742536120039</v>
+        <v>0.61626985574718296</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C112" s="215">
         <f>DCF!C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6356,11 +6356,11 @@
       </c>
       <c r="C118" s="205">
         <f>DCF!C90</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D118" s="206" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>23.81 HKD</v>
+        <v>16.25 HKD</v>
       </c>
       <c r="E118" s="207">
         <f>DCF!F90</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="F118" s="207">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.19318833606723049</v>
+        <v>-0.11981746812183972</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6378,11 +6378,11 @@
       </c>
       <c r="C119" s="197">
         <f>DCF!C91</f>
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="D119" s="206" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>14.02 HKD</v>
+        <v>10.75 HKD</v>
       </c>
       <c r="E119" s="198">
         <f>DCF!F91</f>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="F119" s="207">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-3.5981606745978272E-2</v>
+        <v>1.1484216740361894E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6400,11 +6400,11 @@
       </c>
       <c r="C120" s="197">
         <f>DCF!C92</f>
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="D120" s="206" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>10.12 HKD</v>
+        <v>9.86 HKD</v>
       </c>
       <c r="E120" s="198">
         <f>DCF!F92</f>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="F120" s="207">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>7.5950185261146122E-2</v>
+        <v>4.1278169698530445E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6422,11 +6422,11 @@
       </c>
       <c r="C121" s="197">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D121" s="206" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>7.83 HKD</v>
+        <v>9.04 HKD</v>
       </c>
       <c r="E121" s="198">
         <f>DCF!F93</f>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F121" s="207">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.17336935374366599</v>
+        <v>7.2406300117129577E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="D122" s="206" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>7.17 HKD</v>
+        <v>8.65 HKD</v>
       </c>
       <c r="E122" s="198">
         <f>DCF!F94</f>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="F122" s="207">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.20880750223117184</v>
+        <v>8.8494095501752745E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C125" s="196">
         <f>Scenarios!C36</f>
-        <v>12.192767818192898</v>
+        <v>10.738252335306031</v>
       </c>
       <c r="D125" s="193" t="str">
         <f>Market_currency</f>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="D140" s="336">
         <f>Scenarios!D62</f>
-        <v>5.6187870129921205</v>
+        <v>4.9485033803253611</v>
       </c>
       <c r="E140" s="337">
         <f>Scenarios!E62</f>
-        <v>5.8526420444189942</v>
+        <v>5.1823584117522348</v>
       </c>
       <c r="F140" s="338">
         <f>E22</f>
@@ -6602,11 +6602,11 @@
       </c>
       <c r="D141" s="336">
         <f>Scenarios!D63</f>
-        <v>7.0427539744074528</v>
+        <v>6.2026006268915728</v>
       </c>
       <c r="E141" s="337">
         <f>Scenarios!E63</f>
-        <v>7.311645678868441</v>
+        <v>6.471492331352561</v>
       </c>
       <c r="F141" s="338">
         <f>Scenarios!F63</f>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="D144" s="336">
         <f>Scenarios!D66</f>
-        <v>8.739293053306179</v>
+        <v>7.6967539641460725</v>
       </c>
       <c r="E144" s="337">
         <f>Scenarios!E66</f>
-        <v>9.0476237328011386</v>
+        <v>8.0050846436410321</v>
       </c>
       <c r="F144" s="338">
         <f>E24</f>
@@ -6670,11 +6670,11 @@
       </c>
       <c r="D145" s="336">
         <f>Scenarios!D67</f>
-        <v>9.8834916847712346</v>
+        <v>8.7044573674742765</v>
       </c>
       <c r="E145" s="337">
         <f>Scenarios!E67</f>
-        <v>10.217353238803947</v>
+        <v>9.0383189215069883</v>
       </c>
       <c r="F145" s="338">
         <f>Scenarios!F67</f>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="C50" s="91">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.73455742536120039</v>
+        <v>0.61626985574718296</v>
       </c>
       <c r="D50" s="91">
         <f>G31/Normalized_FCF!G8</f>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="C54" s="88">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.17518529827978366</v>
+        <v>0.20881057294212796</v>
       </c>
       <c r="D54" s="88">
         <f>Normalized_FCF!G8/G35</f>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="C5" s="269">
         <f>C26</f>
-        <v>-4811959.4536017254</v>
+        <v>-4664700.7239938071</v>
       </c>
       <c r="E5" s="237"/>
       <c r="G5" s="273">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="C6" s="270">
         <f>C8-C7</f>
-        <v>1461625.5463982741</v>
+        <v>1608884.2760061929</v>
       </c>
       <c r="E6" s="237"/>
       <c r="G6" s="270">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="C8" s="271">
         <f>C11-(C9+C10)</f>
-        <v>767207.54639827425</v>
+        <v>914466.27600619278</v>
       </c>
       <c r="D8" s="56"/>
       <c r="E8" s="243"/>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="C11" s="270">
         <f>C4*C77</f>
-        <v>736293.64803959324</v>
+        <v>883552.37764751178</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="270">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="C12" s="269">
         <f>-C11*C41</f>
-        <v>-184073.41200989831</v>
+        <v>-220888.09441187794</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="269">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="C14" s="272">
         <f>SUM(C11:C13)</f>
-        <v>517879.86501135764</v>
+        <v>628323.91221729654</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="245"/>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C19" s="270">
         <f>C14+C17</f>
-        <v>517879.86501135764</v>
+        <v>628323.91221729654</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
@@ -11706,7 +11706,7 @@
       </c>
       <c r="C23" s="277">
         <f>-C$4*C29</f>
-        <v>-2803035.155581587</v>
+        <v>-2655776.4259736692</v>
       </c>
       <c r="D23" s="55"/>
       <c r="E23" s="236"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="C26" s="270">
         <f>C6-C4</f>
-        <v>-4811959.4536017254</v>
+        <v>-4664700.7239938071</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="242"/>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="C29" s="456">
         <f>C32-C30-C31</f>
-        <v>0.44679958199045477</v>
+        <v>0.42332676228562605</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="235"/>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="C32" s="67">
         <f>ABS(C5/$C$4)</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="E32" s="237"/>
       <c r="G32" s="29">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
-        <v>22.689399209968165</v>
+        <v>27.044429499897465</v>
       </c>
       <c r="E53" s="237"/>
       <c r="G53" s="40">
@@ -13255,7 +13255,7 @@
       </c>
       <c r="C71" s="73">
         <f t="shared" ref="C71:C75" si="23">ABS(C5/C$4)</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="D71" s="26"/>
       <c r="E71" s="234"/>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="C72" s="74">
         <f t="shared" si="23"/>
-        <v>0.23298091065926008</v>
+        <v>0.25645373036408892</v>
       </c>
       <c r="D72" s="26"/>
       <c r="E72" s="234"/>
@@ -13426,7 +13426,7 @@
       </c>
       <c r="C74" s="74">
         <f>SUM(C75:C77)</f>
-        <v>0.12229172736135308</v>
+        <v>0.14576454706618192</v>
       </c>
       <c r="D74" s="26"/>
       <c r="E74" s="234"/>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="C77" s="74">
         <f>C116</f>
-        <v>0.1173640985241442</v>
+        <v>0.14083691822897304</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="C78" s="73">
         <f>ABS(C12/C$4)</f>
-        <v>2.9341024631036054E-2</v>
+        <v>3.520922955724326E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="C80" s="74">
         <f>ABS(C14/C$4)</f>
-        <v>8.2549270474753689E-2</v>
+        <v>0.1001538852533753</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="C85" s="74">
         <f>ABS(C19/C$4)</f>
-        <v>8.2549270474753689E-2</v>
+        <v>0.1001538852533753</v>
       </c>
       <c r="D85" s="71"/>
       <c r="E85" s="234"/>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.28576180044141009</v>
+        <v>0.23553183280221826</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="151">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="C96" s="73">
         <f>C11/G11-1</f>
-        <v>0.24944620027896547</v>
+        <v>0.4993354403347583</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="C116" s="22">
         <f>C119/C117/C118</f>
-        <v>0.1173640985241442</v>
+        <v>0.14083691822897304</v>
       </c>
       <c r="E116" s="237"/>
       <c r="G116" s="22">
@@ -15267,7 +15267,7 @@
         <v>551</v>
       </c>
       <c r="C119" s="455">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D119" s="99"/>
       <c r="E119" s="240"/>
@@ -15388,7 +15388,7 @@
       </c>
       <c r="C123" s="158">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.49691736187501495</v>
+        <v>0.60289090570292803</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C124" s="73">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5519355908056987E-2</v>
+        <v>9.1624757705612153E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
@@ -16294,7 +16294,7 @@
       </c>
       <c r="C4" s="278">
         <f>Normalized_FCF!C19</f>
-        <v>517879.86501135764</v>
+        <v>628323.91221729654</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="C6" s="286">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>10061665.948792094</v>
+        <v>12207436.008793194</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="C8" s="286">
         <f>C6+C7</f>
-        <v>10284138.341905594</v>
+        <v>12429908.401906693</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="C10" s="286">
         <f>C8*Exchange_Rate</f>
-        <v>10284138.341905594</v>
+        <v>12429908.401906693</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="C11" s="107">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16600,14 +16600,14 @@
       </c>
       <c r="C17" s="309">
         <f>Normalized_FCF!C32</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="E17" s="311" t="s">
         <v>399</v>
       </c>
       <c r="F17" s="314">
         <f>Scenarios!C40</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="H17" s="105" t="s">
         <v>411</v>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="I18" s="128">
         <f>(M52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>12.434603944721822</v>
+        <v>14.9918591479965</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="E21" s="302">
         <f>$C$17</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="F21" s="280">
         <f>I5*(1+D21)</f>
@@ -16711,7 +16711,7 @@
       </c>
       <c r="G21" s="280">
         <f>C21*(1-E21)+F21+$I$6</f>
-        <v>836030.62907136942</v>
+        <v>1002432.9935283166</v>
       </c>
       <c r="H21" s="302">
         <f t="shared" ref="H21:H50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16719,15 +16719,15 @@
       </c>
       <c r="I21" s="280">
         <f>(G21*(1-$I$10)+C21*(H21-$I$9))</f>
-        <v>588218.35255280603</v>
+        <v>713020.12589551625</v>
       </c>
       <c r="J21" s="302">
         <f>I21/C21</f>
-        <v>8.2974441989468697E-2</v>
+        <v>0.10057905676809022</v>
       </c>
       <c r="K21" s="302">
         <f>I21/C4-1</f>
-        <v>0.13582008549397018</v>
+        <v>0.13479705615426063</v>
       </c>
       <c r="L21" s="118">
         <f t="shared" ref="L21:L50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="M21" s="280">
         <f t="shared" ref="M21:M50" si="4">I21*L21</f>
-        <v>548455.34037557663</v>
+        <v>664820.63020560949</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -16756,7 +16756,7 @@
       </c>
       <c r="E22" s="302">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="F22" s="280">
         <f t="shared" ref="F22:F50" si="7">IF(A22="",0,F21*(1+D22))</f>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="G22" s="280">
         <f t="shared" ref="G22:G50" si="8">IF(A22="", 0,C22*(1-E22)+F22+$I$6)</f>
-        <v>948733.41763727576</v>
+        <v>1136768.0894736261</v>
       </c>
       <c r="H22" s="302">
         <f t="shared" si="2"/>
@@ -16772,15 +16772,15 @@
       </c>
       <c r="I22" s="280">
         <f>IF(A22="", 0,G22*(1-$I$10)+C22*(H22-$I$9))</f>
-        <v>667700.84347464202</v>
+        <v>808726.84735190473</v>
       </c>
       <c r="J22" s="302">
         <f>IF(A22="", 0,I22/C22)</f>
-        <v>8.3350699967092517E-2</v>
+        <v>0.10095531474571405</v>
       </c>
       <c r="K22" s="302">
         <f>IF(A22="", 0,I22/I21-1)</f>
-        <v>0.13512412623116954</v>
+        <v>0.13422723704493733</v>
       </c>
       <c r="L22" s="118">
         <f t="shared" si="3"/>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="M22" s="280">
         <f t="shared" si="4"/>
-        <v>580480.0830029326</v>
+        <v>703084.07135532168</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -16809,7 +16809,7 @@
       </c>
       <c r="E23" s="302">
         <f t="shared" si="6"/>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="F23" s="280">
         <f t="shared" si="7"/>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="G23" s="280">
         <f t="shared" si="8"/>
-        <v>1076087.5687167498</v>
+        <v>1288566.7478918259</v>
       </c>
       <c r="H23" s="302">
         <f t="shared" si="2"/>
@@ -16825,15 +16825,15 @@
       </c>
       <c r="I23" s="280">
         <f t="shared" ref="I23:I50" si="9">IF(A23="", 0,G23*(1-$I$10)+C23*(H23-$I$9))</f>
-        <v>757516.05821631663</v>
+        <v>916875.44259762368</v>
       </c>
       <c r="J23" s="302">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,I23/C23)</f>
-        <v>8.3683671628706505E-2</v>
+        <v>0.10128828640732807</v>
       </c>
       <c r="K23" s="302">
         <f t="shared" ref="K23:K50" si="11">IF(A23="", 0,I23/I22-1)</f>
-        <v>0.13451415498336949</v>
+        <v>0.1337269754303827</v>
       </c>
       <c r="L23" s="118">
         <f t="shared" si="3"/>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="M23" s="280">
         <f t="shared" si="4"/>
-        <v>614044.63482773746</v>
+        <v>743221.7973808375</v>
       </c>
       <c r="O23" s="278"/>
       <c r="P23" s="278"/>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="E24" s="302">
         <f t="shared" si="6"/>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="F24" s="280">
         <f t="shared" si="7"/>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="G24" s="280">
         <f t="shared" si="8"/>
-        <v>1219997.7594365557</v>
+        <v>1460099.2319043912</v>
       </c>
       <c r="H24" s="302">
         <f t="shared" si="2"/>
@@ -16886,15 +16886,15 @@
       </c>
       <c r="I24" s="280">
         <f t="shared" si="9"/>
-        <v>859007.25087440899</v>
+        <v>1039083.3552252856</v>
       </c>
       <c r="J24" s="302">
         <f t="shared" si="10"/>
-        <v>8.3978336815975524E-2</v>
+        <v>0.10158295159459706</v>
       </c>
       <c r="K24" s="302">
         <f t="shared" si="11"/>
-        <v>0.13397893227117641</v>
+        <v>0.13328736592773338</v>
       </c>
       <c r="L24" s="118">
         <f t="shared" si="3"/>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="M24" s="280">
         <f t="shared" si="4"/>
-        <v>649243.52388699481</v>
+        <v>785346.26858163613</v>
       </c>
       <c r="O24" s="278"/>
       <c r="P24" s="278"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="E25" s="302">
         <f t="shared" si="6"/>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="F25" s="280">
         <f t="shared" si="7"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="G25" s="280">
         <f t="shared" si="8"/>
-        <v>1382616.2749499364</v>
+        <v>1653930.9388385906</v>
       </c>
       <c r="H25" s="302">
         <f t="shared" si="2"/>
@@ -16947,15 +16947,15 @@
       </c>
       <c r="I25" s="280">
         <f t="shared" si="9"/>
-        <v>973692.29857805371</v>
+        <v>1177178.2964945443</v>
       </c>
       <c r="J25" s="302">
         <f t="shared" si="10"/>
-        <v>8.4239102468426016E-2</v>
+        <v>0.10184371724704755</v>
       </c>
       <c r="K25" s="302">
         <f t="shared" si="11"/>
-        <v>0.13350882380434315</v>
+        <v>0.13290073464733543</v>
       </c>
       <c r="L25" s="118">
         <f t="shared" si="3"/>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="M25" s="280">
         <f t="shared" si="4"/>
-        <v>686175.5367121069</v>
+        <v>829575.16515494569</v>
       </c>
       <c r="O25" s="278"/>
       <c r="P25" s="278"/>
@@ -18373,7 +18373,7 @@
       </c>
       <c r="E51" s="304">
         <f>F17</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="F51" s="280">
         <f>VLOOKUP(C15,B21:F50,5,FALSE)*(1+Terminal_Growth)</f>
@@ -18381,7 +18381,7 @@
       </c>
       <c r="G51" s="280">
         <f>C51*(1-E51)+F51+$I$6</f>
-        <v>1410886.8784161082</v>
+        <v>1687627.8355825359</v>
       </c>
       <c r="H51" s="302">
         <f>F18</f>
@@ -18389,12 +18389,12 @@
       </c>
       <c r="I51" s="280">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/Equity_Cost</f>
-        <v>13705239.35206889</v>
+        <v>16568076.839997454</v>
       </c>
       <c r="J51" s="457"/>
       <c r="K51" s="418">
         <f>(G51*(1-$I$10)+C51*(H51-$I$9))/VLOOKUP(C15,B21:I50,8,FALSE)-1</f>
-        <v>2.0476237180941936E-2</v>
+        <v>2.0393915243562599E-2</v>
       </c>
       <c r="L51" s="118">
         <f>1/(1+Equity_Cost)^C15</f>
@@ -18402,7 +18402,7 @@
       </c>
       <c r="M51" s="280">
         <f>I51*L51</f>
-        <v>9658287.3068908155</v>
+        <v>11675771.734638346</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="13.15">
@@ -18416,7 +18416,7 @@
       <c r="L52" s="467"/>
       <c r="M52" s="320">
         <f>SUM(M21:M51)</f>
-        <v>12736686.425696164</v>
+        <v>15401819.667316698</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -18441,7 +18441,7 @@
     <row r="55" spans="1:22" ht="13.15">
       <c r="A55" s="124">
         <f>M52</f>
-        <v>12736686.425696164</v>
+        <v>15401819.667316698</v>
       </c>
       <c r="B55" s="122">
         <f>C94</f>
@@ -18449,19 +18449,19 @@
       </c>
       <c r="C55" s="122">
         <f>C93</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D55" s="122">
         <f>C92</f>
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E55" s="122">
         <f>C91</f>
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="F55" s="122">
         <f>C90</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="G55" s="122"/>
       <c r="H55" s="122"/>
@@ -18477,19 +18477,19 @@
       </c>
       <c r="B56" s="117">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>7282340.1462942101</v>
+        <v>8834114.0753672756</v>
       </c>
       <c r="C56" s="117">
-        <v>7434382.9281908553</v>
+        <v>8925653.2056063283</v>
       </c>
       <c r="D56" s="117">
-        <v>7890511.2738807919</v>
+        <v>9108731.4660844337</v>
       </c>
       <c r="E56" s="117">
-        <v>8498682.4014673736</v>
+        <v>9291809.726562541</v>
       </c>
       <c r="F56" s="117">
-        <v>9562981.8747438937</v>
+        <v>10207201.028953075</v>
       </c>
       <c r="G56" s="298"/>
       <c r="H56" s="298"/>
@@ -18504,19 +18504,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="117">
-        <v>7272932.4114737231</v>
+        <v>8822786.0024098568</v>
       </c>
       <c r="C57" s="117">
-        <v>7569387.1669113301</v>
+        <v>9000416.5340092592</v>
       </c>
       <c r="D57" s="117">
-        <v>8492774.9928094093</v>
+        <v>9360798.6674312316</v>
       </c>
       <c r="E57" s="117">
-        <v>9803347.0663724635</v>
+        <v>9728008.8944840897</v>
       </c>
       <c r="F57" s="117">
-        <v>12315166.03577991</v>
+        <v>11666481.434211653</v>
       </c>
       <c r="G57" s="298"/>
       <c r="H57" s="298"/>
@@ -18531,19 +18531,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="117">
-        <v>7264160.6307553211</v>
+        <v>8812223.696622055</v>
       </c>
       <c r="C58" s="117">
-        <v>7697782.8065335965</v>
+        <v>9070823.0250926744</v>
       </c>
       <c r="D58" s="117">
-        <v>9099250.3461361267</v>
+        <v>9602877.1918015834</v>
       </c>
       <c r="E58" s="117">
-        <v>11214452.904404996</v>
+        <v>10155057.030910779</v>
       </c>
       <c r="F58" s="117">
-        <v>15651146.837035688</v>
+        <v>13231211.006283779</v>
       </c>
       <c r="G58" s="298"/>
       <c r="H58" s="298"/>
@@ -18558,19 +18558,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="117">
-        <v>7255981.8142346647</v>
+        <v>8802375.3928572033</v>
       </c>
       <c r="C59" s="117">
-        <v>7819893.3449156145</v>
+        <v>9137126.5738052577</v>
       </c>
       <c r="D59" s="117">
-        <v>9709966.7858497389</v>
+        <v>9835362.8608938549</v>
       </c>
       <c r="E59" s="117">
-        <v>12740683.927358605</v>
+        <v>10573146.11552432</v>
       </c>
       <c r="F59" s="117">
-        <v>19694759.929466929</v>
+        <v>14909009.615032442</v>
       </c>
       <c r="G59" s="298"/>
       <c r="H59" s="298"/>
@@ -18585,19 +18585,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="117">
-        <v>7248355.8780848701</v>
+        <v>8793192.8252442889</v>
       </c>
       <c r="C60" s="117">
-        <v>7936026.4443558557</v>
+        <v>9199566.2793527786</v>
       </c>
       <c r="D60" s="117">
-        <v>10324953.969897024</v>
+        <v>10058635.811164284</v>
       </c>
       <c r="E60" s="117">
-        <v>14391432.632837567</v>
+        <v>10982464.100460658</v>
       </c>
       <c r="F60" s="117">
-        <v>24596109.132413905</v>
+        <v>16708047.750287421</v>
       </c>
       <c r="G60" s="298"/>
       <c r="H60" s="298"/>
@@ -18612,19 +18612,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="117">
-        <v>7241245.4481083713</v>
+        <v>8784630.9906401746</v>
       </c>
       <c r="C61" s="117">
-        <v>8046474.7067605583</v>
+        <v>9258367.3074208349</v>
       </c>
       <c r="D61" s="117">
-        <v>10944241.763622954</v>
+        <v>10273061.115386706</v>
       </c>
       <c r="E61" s="117">
-        <v>16176857.806129495</v>
+        <v>11383194.994803924</v>
       </c>
       <c r="F61" s="117">
-        <v>30537138.469319317</v>
+        <v>18637086.310234483</v>
       </c>
       <c r="G61" s="298"/>
       <c r="H61" s="298"/>
@@ -18639,19 +18639,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="117">
-        <v>7234615.6765685128</v>
+        <v>8776647.9280722328</v>
       </c>
       <c r="C62" s="117">
-        <v>8151516.4108657334</v>
+        <v>9313741.7021515928</v>
       </c>
       <c r="D62" s="117">
-        <v>11567860.241221095</v>
+        <v>10478989.379581664</v>
       </c>
       <c r="E62" s="117">
-        <v>18107947.037848506</v>
+        <v>11775518.94730782</v>
       </c>
       <c r="F62" s="117">
-        <v>37738386.150416784</v>
+        <v>20705519.264956281</v>
       </c>
       <c r="G62" s="298"/>
       <c r="H62" s="298"/>
@@ -18666,19 +18666,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="117">
-        <v>7228434.071403143</v>
+        <v>8769204.5130904708</v>
       </c>
       <c r="C63" s="117">
-        <v>8251416.2133713532</v>
+        <v>9365889.1508024707</v>
       </c>
       <c r="D63" s="117">
-        <v>12195839.687194047</v>
+        <v>10676757.316291042</v>
       </c>
       <c r="E63" s="117">
-        <v>20196584.342085391</v>
+        <v>12159612.327381562</v>
       </c>
       <c r="F63" s="117">
-        <v>46467171.218413725</v>
+        <v>22923419.402886413</v>
       </c>
       <c r="G63" s="298"/>
       <c r="H63" s="298"/>
@@ -18693,19 +18693,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="117">
-        <v>7222670.3369832169</v>
+        <v>8762264.2660212275</v>
       </c>
       <c r="C64" s="117">
-        <v>8346425.8157543177</v>
+        <v>9414997.70384432</v>
       </c>
       <c r="D64" s="117">
-        <v>12828210.597824151</v>
+        <v>10866688.295135476</v>
       </c>
       <c r="E64" s="117">
-        <v>22455623.291190077</v>
+        <v>12535647.804376837</v>
       </c>
       <c r="F64" s="117">
-        <v>57047516.755379692</v>
+        <v>25301587.382951353</v>
       </c>
       <c r="G64" s="298"/>
       <c r="H64" s="298"/>
@@ -18720,19 +18720,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="117">
-        <v>7217296.2256359681</v>
+        <v>8755793.1731827743</v>
       </c>
       <c r="C65" s="117">
-        <v>8436784.5984402169</v>
+        <v>9461244.4530958571</v>
       </c>
       <c r="D65" s="117">
-        <v>13465003.68265447</v>
+        <v>11049092.871554844</v>
       </c>
       <c r="E65" s="117">
-        <v>24898966.117261354</v>
+        <v>12903794.425211374</v>
       </c>
       <c r="F65" s="117">
-        <v>69872178.012308165</v>
+        <v>27851604.331272725</v>
       </c>
       <c r="G65" s="298"/>
       <c r="H65" s="298"/>
@@ -18747,19 +18747,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="117">
-        <v>7195408.0236646254</v>
+        <v>8729437.0785894059</v>
       </c>
       <c r="C66" s="280">
-        <v>8826405.6232918277</v>
+        <v>9655059.6669822503</v>
       </c>
       <c r="D66" s="117">
-        <v>16716391.670853011</v>
+        <v>11858254.484474305</v>
       </c>
       <c r="E66" s="117">
-        <v>40451609.88045691</v>
+        <v>14631867.201378077</v>
       </c>
       <c r="F66" s="117">
-        <v>188339608.58854318</v>
+        <v>43646854.909473136</v>
       </c>
       <c r="G66" s="298"/>
       <c r="H66" s="298"/>
@@ -18783,19 +18783,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="117">
-        <v>7179983.080120055</v>
+        <v>8710863.5442401562</v>
       </c>
       <c r="C67" s="280">
-        <v>9129555.0413656943</v>
+        <v>9798611.3304492645</v>
       </c>
       <c r="D67" s="117">
-        <v>20083065.71007333</v>
+        <v>12519305.368966207</v>
       </c>
       <c r="E67" s="117">
-        <v>63471734.287715033</v>
+        <v>16186121.293586787</v>
       </c>
       <c r="F67" s="117">
-        <v>498316434.19513571</v>
+        <v>66035572.462525703</v>
       </c>
       <c r="G67" s="298"/>
       <c r="H67" s="298"/>
@@ -18819,19 +18819,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="117">
-        <v>7169112.8915287443</v>
+        <v>8697774.4965817239</v>
       </c>
       <c r="C68" s="280">
-        <v>9365424.1649930049</v>
+        <v>9904934.666326426</v>
       </c>
       <c r="D68" s="117">
-        <v>23569113.554101955</v>
+        <v>13059356.03982152</v>
       </c>
       <c r="E68" s="117">
-        <v>97544791.948797733</v>
+        <v>17584040.302823294</v>
       </c>
       <c r="F68" s="117">
-        <v>1309388573.9872437</v>
+        <v>97770091.088153809</v>
       </c>
       <c r="G68" s="298"/>
       <c r="H68" s="298"/>
@@ -18855,19 +18855,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="117">
-        <v>7161452.5069270628</v>
+        <v>8688550.4487842917</v>
       </c>
       <c r="C69" s="280">
-        <v>9548945.0301630683</v>
+        <v>9983684.3755183741</v>
       </c>
       <c r="D69" s="117">
-        <v>27178767.898206804</v>
+        <v>13500554.643338174</v>
       </c>
       <c r="E69" s="117">
-        <v>147977762.58945242</v>
+        <v>18841349.237173751</v>
       </c>
       <c r="F69" s="117">
-        <v>3431605338.610302</v>
+        <v>142751661.38193899</v>
       </c>
       <c r="G69" s="298"/>
       <c r="H69" s="298"/>
@@ -18940,19 +18940,19 @@
       </c>
       <c r="C72" s="123">
         <f>C55</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D72" s="123">
         <f>D55</f>
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E72" s="123">
         <f>E55</f>
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="F72" s="123">
         <f>F55</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="G72" s="123"/>
       <c r="H72" s="123"/>
@@ -18968,23 +18968,23 @@
       </c>
       <c r="B73" s="118">
         <f>C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="C73" s="118">
         <f>C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="D73" s="118">
         <f>C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="E73" s="118">
         <f>C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="F73" s="118">
         <f>C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="G73" s="299"/>
       <c r="H73" s="299"/>
@@ -19000,23 +19000,23 @@
       </c>
       <c r="B74" s="118">
         <f t="shared" ref="B74:F87" si="12">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>7.201036186968234</v>
+        <v>8.6899981242015016</v>
       </c>
       <c r="C74" s="118">
         <f t="shared" si="12"/>
-        <v>7.3469246510245885</v>
+        <v>8.7778319756020107</v>
       </c>
       <c r="D74" s="118">
         <f t="shared" si="12"/>
-        <v>7.7845900431936546</v>
+        <v>8.9534996784030305</v>
       </c>
       <c r="E74" s="118">
         <f t="shared" si="12"/>
-        <v>8.3681438994190724</v>
+        <v>9.1291673812040521</v>
       </c>
       <c r="F74" s="118">
         <f t="shared" si="12"/>
-        <v>9.3893631478135582</v>
+        <v>10.007505895209151</v>
       </c>
       <c r="G74" s="299"/>
       <c r="H74" s="299"/>
@@ -19032,23 +19032,23 @@
       </c>
       <c r="B75" s="118">
         <f t="shared" si="12"/>
-        <v>7.1920092541136169</v>
+        <v>8.6791285837743892</v>
       </c>
       <c r="C75" s="118">
         <f t="shared" si="12"/>
-        <v>7.4764642502238194</v>
+        <v>8.8495690683622499</v>
       </c>
       <c r="D75" s="118">
         <f t="shared" si="12"/>
-        <v>8.3624756081334706</v>
+        <v>9.1953638194345064</v>
       </c>
       <c r="E75" s="118">
         <f t="shared" si="12"/>
-        <v>9.6199989476974412</v>
+        <v>9.5477102797021391</v>
       </c>
       <c r="F75" s="118">
         <f t="shared" si="12"/>
-        <v>12.030145663399921</v>
+        <v>11.407718218970942</v>
       </c>
       <c r="G75" s="299"/>
       <c r="H75" s="299"/>
@@ -19064,23 +19064,23 @@
       </c>
       <c r="B76" s="118">
         <f t="shared" si="12"/>
-        <v>7.1835925335032513</v>
+        <v>8.6689938141453826</v>
       </c>
       <c r="C76" s="118">
         <f t="shared" si="12"/>
-        <v>7.5996627501615475</v>
+        <v>8.9171256778614048</v>
       </c>
       <c r="D76" s="118">
         <f t="shared" si="12"/>
-        <v>8.944402330870064</v>
+        <v>9.4276436005649682</v>
       </c>
       <c r="E76" s="118">
         <f t="shared" si="12"/>
-        <v>10.973986692222283</v>
+        <v>9.9574725579520145</v>
       </c>
       <c r="F76" s="118">
         <f t="shared" si="12"/>
-        <v>15.231094167140965</v>
+        <v>12.909111386640918</v>
       </c>
       <c r="G76" s="299"/>
       <c r="H76" s="299"/>
@@ -19096,23 +19096,23 @@
       </c>
       <c r="B77" s="118">
         <f t="shared" si="12"/>
-        <v>7.1757447753583854</v>
+        <v>8.6595441454936264</v>
       </c>
       <c r="C77" s="118">
         <f t="shared" si="12"/>
-        <v>7.716830554298129</v>
+        <v>8.9807454220051284</v>
       </c>
       <c r="D77" s="118">
         <f t="shared" si="12"/>
-        <v>9.5303984712481693</v>
+        <v>9.6507188216040127</v>
       </c>
       <c r="E77" s="118">
         <f t="shared" si="12"/>
-        <v>12.438439637349394</v>
+        <v>10.358638424770074</v>
       </c>
       <c r="F77" s="118">
         <f t="shared" si="12"/>
-        <v>19.111031747433138</v>
+        <v>14.518996834492171</v>
       </c>
       <c r="G77" s="299"/>
       <c r="H77" s="299"/>
@@ -19128,23 +19128,23 @@
       </c>
       <c r="B78" s="118">
         <f t="shared" si="12"/>
-        <v>7.1684275183468582</v>
+        <v>8.6507332656318496</v>
       </c>
       <c r="C78" s="118">
         <f t="shared" si="12"/>
-        <v>7.828262871518934</v>
+        <v>9.0406577218514386</v>
       </c>
       <c r="D78" s="118">
         <f t="shared" si="12"/>
-        <v>10.120492486733827</v>
+        <v>9.8649542320191301</v>
       </c>
       <c r="E78" s="118">
         <f t="shared" si="12"/>
-        <v>14.022370095482211</v>
+        <v>10.751388224452093</v>
       </c>
       <c r="F78" s="118">
         <f t="shared" si="12"/>
-        <v>23.813986390211543</v>
+        <v>16.245214331022655</v>
       </c>
       <c r="G78" s="299"/>
       <c r="H78" s="299"/>
@@ -19160,23 +19160,23 @@
       </c>
       <c r="B79" s="118">
         <f t="shared" si="12"/>
-        <v>7.1616049010866929</v>
+        <v>8.6425179930334561</v>
       </c>
       <c r="C79" s="118">
         <f t="shared" si="12"/>
-        <v>7.934240459924732</v>
+        <v>9.0970786289328061</v>
       </c>
       <c r="D79" s="118">
         <f t="shared" si="12"/>
-        <v>10.714713033796297</v>
+        <v>10.070700127336217</v>
       </c>
       <c r="E79" s="118">
         <f t="shared" si="12"/>
-        <v>15.735525649266886</v>
+        <v>11.135898517847076</v>
       </c>
       <c r="F79" s="118">
         <f t="shared" si="12"/>
-        <v>29.514537472367174</v>
+        <v>18.096170154808256</v>
       </c>
       <c r="G79" s="299"/>
       <c r="H79" s="299"/>
@@ -19193,23 +19193,23 @@
       </c>
       <c r="B80" s="118">
         <f t="shared" si="12"/>
-        <v>7.1552434863919006</v>
+        <v>8.6348580652027849</v>
       </c>
       <c r="C80" s="118">
         <f t="shared" si="12"/>
-        <v>8.0350303342127667</v>
+        <v>9.1502116043660759</v>
       </c>
       <c r="D80" s="118">
         <f t="shared" si="12"/>
-        <v>11.313088969299764</v>
+        <v>10.26829292190647</v>
       </c>
       <c r="E80" s="118">
         <f t="shared" si="12"/>
-        <v>17.588449138675028</v>
+        <v>11.512342161730276</v>
       </c>
       <c r="F80" s="118">
         <f t="shared" si="12"/>
-        <v>36.424296359828546</v>
+        <v>20.080878031128481</v>
       </c>
       <c r="G80" s="299"/>
       <c r="H80" s="299"/>
@@ -19225,23 +19225,23 @@
       </c>
       <c r="B81" s="118">
         <f t="shared" si="12"/>
-        <v>7.1493120973990871</v>
+        <v>8.6277159413513456</v>
       </c>
       <c r="C81" s="118">
         <f t="shared" si="12"/>
-        <v>8.1308864384307569</v>
+        <v>9.2002482525596463</v>
       </c>
       <c r="D81" s="118">
         <f t="shared" si="12"/>
-        <v>11.915649351904657</v>
+        <v>10.458055698976271</v>
       </c>
       <c r="E81" s="118">
         <f t="shared" si="12"/>
-        <v>19.592543542137449</v>
+        <v>11.880888386511026</v>
       </c>
       <c r="F81" s="118">
         <f t="shared" si="12"/>
-        <v>44.799761677963545</v>
+        <v>22.209003026716605</v>
       </c>
       <c r="G81" s="299"/>
       <c r="H81" s="299"/>
@@ -19258,23 +19258,23 @@
       </c>
       <c r="B82" s="118">
         <f t="shared" si="12"/>
-        <v>7.143781664771752</v>
+        <v>8.621056618412938</v>
       </c>
       <c r="C82" s="118">
         <f t="shared" si="12"/>
-        <v>8.2220502857989164</v>
+        <v>9.2473690121638459</v>
       </c>
       <c r="D82" s="118">
         <f t="shared" si="12"/>
-        <v>12.522423443478811</v>
+        <v>10.640298738959386</v>
       </c>
       <c r="E82" s="118">
         <f t="shared" si="12"/>
-        <v>21.760142151010548</v>
+        <v>12.241702872310368</v>
       </c>
       <c r="F82" s="118">
         <f t="shared" si="12"/>
-        <v>54.951840851460496</v>
+        <v>24.490908616391511</v>
       </c>
       <c r="G82" s="299"/>
       <c r="H82" s="299"/>
@@ -19291,23 +19291,23 @@
       </c>
       <c r="B83" s="118">
         <f t="shared" si="12"/>
-        <v>7.1386250842334471</v>
+        <v>8.6148474594960103</v>
       </c>
       <c r="C83" s="118">
         <f t="shared" si="12"/>
-        <v>8.3087515672119885</v>
+        <v>9.2917438067561502</v>
       </c>
       <c r="D83" s="118">
         <f t="shared" si="12"/>
-        <v>13.133440710518522</v>
+        <v>10.815320026775344</v>
       </c>
       <c r="E83" s="118">
         <f t="shared" si="12"/>
-        <v>24.104584469232272</v>
+        <v>12.59494782344259</v>
       </c>
       <c r="F83" s="118">
         <f t="shared" si="12"/>
-        <v>67.257391364790152</v>
+        <v>26.937707150774852</v>
       </c>
       <c r="G83" s="299"/>
       <c r="H83" s="299"/>
@@ -19324,23 +19324,23 @@
       </c>
       <c r="B84" s="118">
         <f t="shared" si="12"/>
-        <v>7.1176228628407525</v>
+        <v>8.5895581947852104</v>
       </c>
       <c r="C84" s="118">
         <f t="shared" si="12"/>
-        <v>8.6826016913060311</v>
+        <v>9.4777138575005555</v>
       </c>
       <c r="D84" s="118">
         <f t="shared" si="12"/>
-        <v>16.253220510206813</v>
+        <v>11.591728767852103</v>
       </c>
       <c r="E84" s="118">
         <f t="shared" si="12"/>
-        <v>39.027695466836995</v>
+        <v>14.25307246407128</v>
       </c>
       <c r="F84" s="118">
         <f t="shared" si="12"/>
-        <v>180.92955173882427</v>
+        <v>42.093604836239066</v>
       </c>
       <c r="G84" s="299"/>
       <c r="H84" s="299"/>
@@ -19357,23 +19357,23 @@
       </c>
       <c r="B85" s="118">
         <f t="shared" si="12"/>
-        <v>7.1028222830710206</v>
+        <v>8.5717364714221649</v>
       </c>
       <c r="C85" s="118">
         <f t="shared" si="12"/>
-        <v>8.9734803665754548</v>
+        <v>9.6154549027161949</v>
       </c>
       <c r="D85" s="118">
         <f t="shared" si="12"/>
-        <v>19.483619865133985</v>
+        <v>12.226021938488612</v>
       </c>
       <c r="E85" s="118">
         <f t="shared" si="12"/>
-        <v>61.116021859365269</v>
+        <v>15.744414173536777</v>
       </c>
       <c r="F85" s="118">
         <f t="shared" si="12"/>
-        <v>478.35927787703093</v>
+        <v>63.576082170984897</v>
       </c>
       <c r="G85" s="299"/>
       <c r="H85" s="299"/>
@@ -19390,23 +19390,23 @@
       </c>
       <c r="B86" s="118">
         <f t="shared" si="12"/>
-        <v>7.092392092977108</v>
+        <v>8.5591772362185683</v>
       </c>
       <c r="C86" s="118">
         <f t="shared" si="12"/>
-        <v>9.1998020882320493</v>
+        <v>9.7174745314744424</v>
       </c>
       <c r="D86" s="118">
         <f t="shared" si="12"/>
-        <v>22.828561066867707</v>
+        <v>12.744212686519274</v>
       </c>
       <c r="E86" s="118">
         <f t="shared" si="12"/>
-        <v>93.809885953867479</v>
+        <v>17.085748859660374</v>
       </c>
       <c r="F86" s="118">
         <f t="shared" si="12"/>
-        <v>1256.6012123978462</v>
+        <v>94.02606553821775</v>
       </c>
       <c r="G86" s="299"/>
       <c r="H86" s="299"/>
@@ -19423,23 +19423,23 @@
       </c>
       <c r="B87" s="118">
         <f t="shared" si="12"/>
-        <v>7.0850417819022971</v>
+        <v>8.550326555188116</v>
       </c>
       <c r="C87" s="118">
         <f t="shared" si="12"/>
-        <v>9.3758944801757451</v>
+        <v>9.7930366461344303</v>
       </c>
       <c r="D87" s="118">
         <f t="shared" si="12"/>
-        <v>26.292105481582364</v>
+        <v>13.167552655756403</v>
       </c>
       <c r="E87" s="118">
         <f t="shared" si="12"/>
-        <v>142.2014539900656</v>
+        <v>18.292165020878794</v>
       </c>
       <c r="F87" s="118">
         <f t="shared" si="12"/>
-        <v>3292.9158622834757</v>
+        <v>137.18689250509175</v>
       </c>
       <c r="G87" s="299"/>
       <c r="H87" s="299"/>
@@ -19480,7 +19480,7 @@
       </c>
       <c r="C90" s="129">
         <f>Scenarios!C29</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D90" s="132">
         <f>Scenarios!D29</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="E90" s="126">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>23.813986390211543</v>
+        <v>16.245214331022655</v>
       </c>
       <c r="F90" s="129">
         <f>Scenarios!F29</f>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="C91" s="129">
         <f>Scenarios!C22</f>
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="D91" s="132">
         <f>Scenarios!D22</f>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="E91" s="126">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>14.022370095482211</v>
+        <v>10.751388224452093</v>
       </c>
       <c r="F91" s="129">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="C92" s="129">
         <f>Scenarios!C23</f>
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="D92" s="132">
         <f>Scenarios!D23</f>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="E92" s="126">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>10.120492486733827</v>
+        <v>9.8649542320191301</v>
       </c>
       <c r="F92" s="129">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C93" s="129">
         <f>Scenarios!C24</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D93" s="132">
         <f>Scenarios!D24</f>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="E93" s="126">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>7.828262871518934</v>
+        <v>9.0406577218514386</v>
       </c>
       <c r="F93" s="129">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19604,7 +19604,7 @@
       </c>
       <c r="E94" s="126">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>7.1684275183468582</v>
+        <v>8.6507332656318496</v>
       </c>
       <c r="F94" s="129">
         <f>Scenarios!F30</f>
@@ -19828,7 +19828,7 @@
       </c>
       <c r="C9" s="450">
         <f>Normalized_FCF!C19</f>
-        <v>517879.86501135764</v>
+        <v>628323.91221729654</v>
       </c>
       <c r="D9" s="468"/>
       <c r="E9" s="468"/>
@@ -19958,7 +19958,7 @@
         <v>444</v>
       </c>
       <c r="C22" s="327">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="D22" s="328">
         <f>C18</f>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="E22" s="329">
         <f>DCF!E91</f>
-        <v>14.022370095482211</v>
+        <v>10.751388224452093</v>
       </c>
       <c r="F22" s="331">
         <f>1-F23-F24</f>
@@ -19982,7 +19982,7 @@
         <v>436</v>
       </c>
       <c r="C23" s="327">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="D23" s="328">
         <f>C18</f>
@@ -19990,7 +19990,7 @@
       </c>
       <c r="E23" s="329">
         <f>DCF!E92</f>
-        <v>10.120492486733827</v>
+        <v>9.8649542320191301</v>
       </c>
       <c r="F23" s="330">
         <v>0.55000000000000004</v>
@@ -20005,7 +20005,7 @@
         <v>445</v>
       </c>
       <c r="C24" s="327">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D24" s="328">
         <f>C18</f>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="E24" s="329">
         <f>DCF!E93</f>
-        <v>7.828262871518934</v>
+        <v>9.0406577218514386</v>
       </c>
       <c r="F24" s="330">
         <v>0.25</v>
@@ -20029,7 +20029,7 @@
       </c>
       <c r="C25" s="444">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>10.32781060467978</v>
+        <v>9.8361669029638001</v>
       </c>
       <c r="D25" s="140" t="str">
         <f>Market_currency</f>
@@ -20068,7 +20068,7 @@
         <v>443</v>
       </c>
       <c r="C29" s="327">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D29" s="328">
         <f>C18</f>
@@ -20076,7 +20076,7 @@
       </c>
       <c r="E29" s="329">
         <f>DCF!E90</f>
-        <v>23.813986390211543</v>
+        <v>16.245214331022655</v>
       </c>
       <c r="F29" s="330">
         <v>0.15</v>
@@ -20099,7 +20099,7 @@
       </c>
       <c r="E30" s="329">
         <f>DCF!E94</f>
-        <v>7.1684275183468582</v>
+        <v>8.6507332656318496</v>
       </c>
       <c r="F30" s="330">
         <v>0.05</v>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="F34" s="333">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.24433009042746481</v>
+        <v>0.19401097353978844</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="C35" s="323">
         <f>DCF!C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="D35" s="96" t="str">
         <f>Market_currency</f>
@@ -20175,7 +20175,7 @@
       </c>
       <c r="F35" s="333">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>8.5161616680961921E-2</v>
+        <v>-2.3287558753016736E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="C36" s="324">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>12.192767818192898</v>
+        <v>10.738252335306031</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C40" s="137">
         <f>DCF!C17</f>
-        <v>0.76701908934073981</v>
+        <v>0.74354626963591108</v>
       </c>
       <c r="E40" s="96" t="s">
         <v>400</v>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="C47" s="145">
         <f>DCF!I18</f>
-        <v>12.434603944721822</v>
+        <v>14.9918591479965</v>
       </c>
       <c r="D47" s="145" t="str">
         <f>Market_currency</f>
@@ -20303,7 +20303,7 @@
       </c>
       <c r="C49" s="217" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">High Growth </v>
+        <v xml:space="preserve">Negative GrowthHigh Growth </v>
       </c>
       <c r="E49" s="221" t="s">
         <v>251</v>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="C50" s="217" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E50" s="125"/>
     </row>
@@ -20354,7 +20354,7 @@
       </c>
       <c r="F53" s="251">
         <f>BS!D89/C36</f>
-        <v>1.7507694809401612E-2</v>
+        <v>1.9879143381736446E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20432,11 +20432,11 @@
       </c>
       <c r="D62" s="118">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>5.6187870129921205</v>
+        <v>4.9485033803253611</v>
       </c>
       <c r="E62" s="335">
         <f>C62+D62</f>
-        <v>5.8526420444189942</v>
+        <v>5.1823584117522348</v>
       </c>
       <c r="F62" s="304">
         <f>Thesis!E22</f>
@@ -20444,7 +20444,7 @@
       </c>
       <c r="G62" s="443">
         <f>(1-E62/C36)</f>
-        <v>0.51999069188488656</v>
+        <v>0.51739275163861742</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20457,11 +20457,11 @@
       </c>
       <c r="D63" s="118">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>7.0427539744074528</v>
+        <v>6.2026006268915728</v>
       </c>
       <c r="E63" s="335">
         <f>C63+D63</f>
-        <v>7.311645678868441</v>
+        <v>6.471492331352561</v>
       </c>
       <c r="F63" s="304">
         <f>Thesis!E23</f>
@@ -20469,7 +20469,7 @@
       </c>
       <c r="G63" s="443">
         <f>(1-E63/C36)</f>
-        <v>0.40032929455453969</v>
+        <v>0.39734212521016077</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20503,11 +20503,11 @@
       </c>
       <c r="D66" s="118">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>8.739293053306179</v>
+        <v>7.6967539641460725</v>
       </c>
       <c r="E66" s="335">
         <f>C66+D66</f>
-        <v>9.0476237328011386</v>
+        <v>8.0050846436410321</v>
       </c>
       <c r="F66" s="304">
         <f>Thesis!E24</f>
@@ -20515,7 +20515,7 @@
       </c>
       <c r="G66" s="443">
         <f>(1-E66/C36)</f>
-        <v>0.25795160969922448</v>
+        <v>0.25452630524230513</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20528,11 +20528,11 @@
       </c>
       <c r="D67" s="118">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>9.8834916847712346</v>
+        <v>8.7044573674742765</v>
       </c>
       <c r="E67" s="335">
         <f>C67+D67</f>
-        <v>10.217353238803947</v>
+        <v>9.0383189215069883</v>
       </c>
       <c r="F67" s="304">
         <f>Thesis!E25</f>
@@ -20540,7 +20540,7 @@
       </c>
       <c r="G67" s="443">
         <f>(1-E67/C36)</f>
-        <v>0.16201527076087063</v>
+        <v>0.15830633893840196</v>
       </c>
     </row>
   </sheetData>
@@ -20676,7 +20676,7 @@
       </c>
       <c r="E10" s="363">
         <f>Scenarios!F34</f>
-        <v>0.24433009042746481</v>
+        <v>0.19401097353978844</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="C18" s="362">
         <f>C125</f>
-        <v>12.192767818192898</v>
+        <v>10.738252335306031</v>
       </c>
       <c r="D18" s="353" t="s">
         <v>359</v>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="C19" s="355" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
-        <v xml:space="preserve">High Growth </v>
+        <v xml:space="preserve">Negative GrowthHigh Growth </v>
       </c>
       <c r="D19" s="346" t="s">
         <v>360</v>
@@ -20806,7 +20806,7 @@
       </c>
       <c r="C22" s="367">
         <f>E140</f>
-        <v>5.8526420444189942</v>
+        <v>5.1823584117522348</v>
       </c>
       <c r="D22" s="368" t="s">
         <v>439</v>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="C23" s="370">
         <f>E141</f>
-        <v>7.311645678868441</v>
+        <v>6.471492331352561</v>
       </c>
       <c r="D23" s="368" t="s">
         <v>440</v>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="C24" s="370">
         <f>E144</f>
-        <v>9.0476237328011386</v>
+        <v>8.0050846436410321</v>
       </c>
       <c r="D24" s="368" t="s">
         <v>442</v>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="C25" s="370">
         <f>E145</f>
-        <v>10.217353238803947</v>
+        <v>9.0383189215069883</v>
       </c>
       <c r="D25" s="368" t="s">
         <v>441</v>
@@ -20916,7 +20916,7 @@
       </c>
       <c r="C34" s="376">
         <f>Normalized_FCF!C8</f>
-        <v>767207.54639827425</v>
+        <v>914466.27600619278</v>
       </c>
       <c r="D34" s="346" t="str">
         <f>Reporting_currency</f>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="C52" s="376">
         <f>Normalized_FCF!C12</f>
-        <v>-184073.41200989831</v>
+        <v>-220888.09441187794</v>
       </c>
       <c r="D52" s="346" t="str">
         <f>Reporting_currency</f>
@@ -21135,7 +21135,7 @@
       </c>
       <c r="C61" s="376">
         <f>Normalized_FCF!C19</f>
-        <v>517879.86501135764</v>
+        <v>628323.91221729654</v>
       </c>
       <c r="D61" s="346" t="str">
         <f>Reporting_currency</f>
@@ -21148,7 +21148,7 @@
       </c>
       <c r="C62" s="381">
         <f>Normalized_FCF!C124</f>
-        <v>7.5519355908056987E-2</v>
+        <v>9.1624757705612153E-2</v>
       </c>
       <c r="F62" s="382"/>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="F63" s="383">
         <f>Normalized_FCF!C90</f>
-        <v>0.28576180044141009</v>
+        <v>0.23553183280221826</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="C66" s="381">
         <f>Normalized_FCF!C119</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D66" s="381">
         <f>Normalized_FCF!G119</f>
@@ -21199,7 +21199,7 @@
       </c>
       <c r="C67" s="386">
         <f>Normalized_FCF!C116</f>
-        <v>0.1173640985241442</v>
+        <v>0.14083691822897304</v>
       </c>
       <c r="D67" s="386">
         <f>Normalized_FCF!G116</f>
@@ -21321,7 +21321,7 @@
       </c>
       <c r="C81" s="392">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0.73455742536120039</v>
+        <v>0.61626985574718296</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="C112" s="397">
         <f>DCF!C11</f>
-        <v>9.8678617171288217</v>
+        <v>11.926776282928275</v>
       </c>
       <c r="D112" s="346" t="str">
         <f>Market_currency</f>
@@ -21619,7 +21619,7 @@
       </c>
       <c r="C118" s="399">
         <f>DCF!C90</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D118" s="400">
         <f>DCF!D90</f>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="E118" s="401" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>23.81 HKD</v>
+        <v>16.25 HKD</v>
       </c>
       <c r="F118" s="402">
         <f>DCF!F90</f>
@@ -21642,7 +21642,7 @@
       </c>
       <c r="C119" s="404">
         <f>DCF!C91</f>
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="D119" s="405">
         <f>DCF!D91</f>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="E119" s="401" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>14.02 HKD</v>
+        <v>10.75 HKD</v>
       </c>
       <c r="F119" s="406">
         <f>DCF!F91</f>
@@ -21664,7 +21664,7 @@
       </c>
       <c r="C120" s="404">
         <f>DCF!C92</f>
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="D120" s="405">
         <f>DCF!D92</f>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="E120" s="401" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>10.12 HKD</v>
+        <v>9.86 HKD</v>
       </c>
       <c r="F120" s="406">
         <f>DCF!F92</f>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C121" s="404">
         <f>DCF!C93</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D121" s="405">
         <f>DCF!D93</f>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="E121" s="401" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>7.83 HKD</v>
+        <v>9.04 HKD</v>
       </c>
       <c r="F121" s="406">
         <f>DCF!F93</f>
@@ -21716,7 +21716,7 @@
       </c>
       <c r="E122" s="401" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>7.17 HKD</v>
+        <v>8.65 HKD</v>
       </c>
       <c r="F122" s="406">
         <f>DCF!F94</f>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="C125" s="407">
         <f>Scenarios!C36</f>
-        <v>12.192767818192898</v>
+        <v>10.738252335306031</v>
       </c>
       <c r="D125" s="346" t="str">
         <f>Market_currency</f>
@@ -21845,11 +21845,11 @@
       </c>
       <c r="D140" s="412">
         <f>Scenarios!D62</f>
-        <v>5.6187870129921205</v>
+        <v>4.9485033803253611</v>
       </c>
       <c r="E140" s="413">
         <f>Scenarios!E62</f>
-        <v>5.8526420444189942</v>
+        <v>5.1823584117522348</v>
       </c>
       <c r="F140" s="414">
         <f>E22</f>
@@ -21866,11 +21866,11 @@
       </c>
       <c r="D141" s="412">
         <f>Scenarios!D63</f>
-        <v>7.0427539744074528</v>
+        <v>6.2026006268915728</v>
       </c>
       <c r="E141" s="413">
         <f>Scenarios!E63</f>
-        <v>7.311645678868441</v>
+        <v>6.471492331352561</v>
       </c>
       <c r="F141" s="414">
         <f>Scenarios!F63</f>
@@ -21906,11 +21906,11 @@
       </c>
       <c r="D144" s="412">
         <f>Scenarios!D66</f>
-        <v>8.739293053306179</v>
+        <v>7.6967539641460725</v>
       </c>
       <c r="E144" s="413">
         <f>Scenarios!E66</f>
-        <v>9.0476237328011386</v>
+        <v>8.0050846436410321</v>
       </c>
       <c r="F144" s="414">
         <f>E24</f>
@@ -21927,11 +21927,11 @@
       </c>
       <c r="D145" s="412">
         <f>Scenarios!D67</f>
-        <v>9.8834916847712346</v>
+        <v>8.7044573674742765</v>
       </c>
       <c r="E145" s="413">
         <f>Scenarios!E67</f>
-        <v>10.217353238803947</v>
+        <v>9.0383189215069883</v>
       </c>
       <c r="F145" s="414">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83712C8E-D044-4821-A082-05894CFF1735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282347D7-1486-4407-9955-7A9A336CC14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4997,30 +4997,30 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,6 +5030,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5039,16 +5048,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5418,7 +5418,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.58</v>
+        <v>6.53</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6866.4214056199999</v>
+        <v>6814.2449511699997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="306">
         <f>Scenarios!F34</f>
-        <v>0.18124758098046517</v>
+        <v>0.18430807784929162</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5451,13 +5451,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5572,7 +5572,7 @@
         <v>407</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5587,7 +5587,7 @@
         <v>408</v>
       </c>
       <c r="E23" s="446">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5635,22 +5635,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5662,13 +5662,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5688,13 +5688,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5723,13 +5723,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5745,13 +5745,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5815,13 +5815,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5837,7 +5837,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5859,22 +5859,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9765977264137663E-2</v>
+        <v>7.0300173108426608E-2</v>
       </c>
       <c r="F62" s="259"/>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.1580547112462004E-2</v>
+        <v>2.1745788667687591E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6009,13 +6009,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>479</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6034,13 +6034,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6209,31 +6209,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>486</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6283,22 +6283,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6332,13 +6332,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>492</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6473,13 +6473,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6514,22 +6514,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="C140" s="336">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763701</v>
+        <v>0.25983892380763696</v>
       </c>
       <c r="D140" s="336">
         <f>Scenarios!D62</f>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="F140" s="338">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="C141" s="336">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220924</v>
+        <v>0.29876856051220907</v>
       </c>
       <c r="D141" s="336">
         <f>Scenarios!D63</f>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F141" s="338">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6705,13 +6705,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6748,13 +6748,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>439</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6762,22 +6762,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6801,6 +6801,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6817,18 +6829,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14266,28 +14266,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1580547112462004E-2</v>
+        <v>2.1745788667687591E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1580547112462004E-2</v>
+        <v>2.1745788667687591E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1702127659574468E-2</v>
+        <v>1.1791730474732006E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1033434650455929E-3</v>
+        <v>4.1347626339969367E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9848024316109414E-2</v>
+        <v>5.0229709035222045E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.8936170212765952E-2</v>
+        <v>4.9310872894333835E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15465,50 +15465,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9765977264137663E-2</v>
+        <v>7.0300173108426608E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.3834676034455024E-2</v>
+        <v>7.4400025774381928E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.661901258810028E-2</v>
+        <v>5.7052542546661533E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.715254059286293E-2</v>
+        <v>3.7437016401384089E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9796306971859424E-2</v>
+        <v>3.0024456336115623E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12914864200938564</v>
+        <v>0.13013752900792611</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12641694249781069</v>
+        <v>0.12738491296104049</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1514643419858808</v>
+        <v>0.15262409958148476</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13291217449209183</v>
+        <v>0.13392987873781995</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.6853799193810278E-2</v>
+        <v>9.7595405619490289E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11475540947065593</v>
+        <v>0.11563408795052313</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15522,43 +15522,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.503542613960467E-2</v>
+        <v>3.5303691270842076E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7154204940523075E-2</v>
+        <v>1.728555413608604E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0666629319845351E-3</v>
+        <v>3.0901442714331147E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.3502926847442478E-2</v>
+        <v>-2.368288800247649E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5853746103829565E-2</v>
+        <v>8.6511125476753215E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2953108519352392E-2</v>
+        <v>8.3588277803574071E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10889151070571196</v>
+        <v>0.10972528950131466</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3506495170030415E-2</v>
+        <v>9.4222471396447183E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5143301205675296E-2</v>
+        <v>9.5871810403268518E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2320027654778291E-2</v>
+        <v>8.295034945917934E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.58</v>
+        <v>6.53</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19995,7 +19995,7 @@
       </c>
       <c r="F34" s="333">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18124758098046517</v>
+        <v>0.18430807784929162</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.25983892380763701</v>
+        <v>0.25983892380763696</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="F62" s="304">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="443">
         <f>(1-E62/C36)</f>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.29876856051220924</v>
+        <v>0.29876856051220907</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20305,7 +20305,7 @@
       </c>
       <c r="F63" s="304">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="443">
         <f>(1-E63/C36)</f>
@@ -20491,7 +20491,7 @@
       </c>
       <c r="C8" s="359">
         <f>Market_Price</f>
-        <v>6.58</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20509,14 +20509,14 @@
       </c>
       <c r="C10" s="360">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6866.4214056199999</v>
+        <v>6814.2449511699997</v>
       </c>
       <c r="D10" s="346" t="s">
         <v>530</v>
       </c>
       <c r="E10" s="363">
         <f>Scenarios!F34</f>
-        <v>0.18124758098046517</v>
+        <v>0.18430807784929162</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20524,13 +20524,13 @@
       <c r="E11" s="352"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="475" t="s">
+      <c r="B12" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C12" s="475"/>
-      <c r="D12" s="475"/>
-      <c r="E12" s="475"/>
-      <c r="F12" s="475"/>
+      <c r="C12" s="472"/>
+      <c r="D12" s="472"/>
+      <c r="E12" s="472"/>
+      <c r="F12" s="472"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="350" t="s">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="E22" s="369">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20669,7 +20669,7 @@
       </c>
       <c r="E23" s="371">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20715,22 +20715,22 @@
       <c r="F27" s="348"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="475" t="s">
+      <c r="B29" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C29" s="475"/>
-      <c r="D29" s="475"/>
-      <c r="E29" s="475"/>
-      <c r="F29" s="475"/>
+      <c r="C29" s="472"/>
+      <c r="D29" s="472"/>
+      <c r="E29" s="472"/>
+      <c r="F29" s="472"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="478" t="s">
+      <c r="B30" s="473" t="s">
         <v>501</v>
       </c>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
-      <c r="E30" s="478"/>
-      <c r="F30" s="478"/>
+      <c r="C30" s="473"/>
+      <c r="D30" s="473"/>
+      <c r="E30" s="473"/>
+      <c r="F30" s="473"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="372" t="s">
@@ -20920,10 +20920,10 @@
       <c r="B54" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C54" s="477"/>
-      <c r="D54" s="477"/>
-      <c r="E54" s="477"/>
-      <c r="F54" s="477"/>
+      <c r="C54" s="474"/>
+      <c r="D54" s="474"/>
+      <c r="E54" s="474"/>
+      <c r="F54" s="474"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="375" t="s">
@@ -20939,22 +20939,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="475" t="s">
+      <c r="B57" s="472" t="s">
         <v>509</v>
       </c>
-      <c r="C57" s="475"/>
-      <c r="D57" s="475"/>
-      <c r="E57" s="475"/>
-      <c r="F57" s="475"/>
+      <c r="C57" s="472"/>
+      <c r="D57" s="472"/>
+      <c r="E57" s="472"/>
+      <c r="F57" s="472"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="475" t="s">
+      <c r="B58" s="472" t="s">
         <v>510</v>
       </c>
-      <c r="C58" s="475"/>
-      <c r="D58" s="475"/>
-      <c r="E58" s="475"/>
-      <c r="F58" s="475"/>
+      <c r="C58" s="472"/>
+      <c r="D58" s="472"/>
+      <c r="E58" s="472"/>
+      <c r="F58" s="472"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="375" t="s">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="C62" s="381">
         <f>Normalized_FCF!C124</f>
-        <v>6.9765977264137663E-2</v>
+        <v>7.0300173108426608E-2</v>
       </c>
       <c r="F62" s="382"/>
     </row>
@@ -20998,7 +20998,7 @@
       </c>
       <c r="C63" s="381">
         <f>Normalized_FCF!C92</f>
-        <v>2.1580547112462004E-2</v>
+        <v>2.1745788667687591E-2</v>
       </c>
       <c r="E63" s="375" t="s">
         <v>373</v>
@@ -21089,22 +21089,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="389"/>
-      <c r="B73" s="475" t="s">
+      <c r="B73" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C73" s="475"/>
-      <c r="D73" s="475"/>
-      <c r="E73" s="475"/>
-      <c r="F73" s="475"/>
+      <c r="C73" s="472"/>
+      <c r="D73" s="472"/>
+      <c r="E73" s="472"/>
+      <c r="F73" s="472"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="478" t="s">
+      <c r="B74" s="473" t="s">
         <v>480</v>
       </c>
-      <c r="C74" s="478"/>
-      <c r="D74" s="478"/>
-      <c r="E74" s="478"/>
-      <c r="F74" s="478"/>
+      <c r="C74" s="473"/>
+      <c r="D74" s="473"/>
+      <c r="E74" s="473"/>
+      <c r="F74" s="473"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="372" t="s">
@@ -21112,13 +21112,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="475" t="s">
+      <c r="B77" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C77" s="475"/>
-      <c r="D77" s="475"/>
-      <c r="E77" s="475"/>
-      <c r="F77" s="475"/>
+      <c r="C77" s="472"/>
+      <c r="D77" s="472"/>
+      <c r="E77" s="472"/>
+      <c r="F77" s="472"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="346" t="s">
@@ -21267,33 +21267,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="388"/>
-      <c r="B96" s="475" t="s">
+      <c r="B96" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C96" s="475"/>
-      <c r="D96" s="475"/>
-      <c r="E96" s="475"/>
-      <c r="F96" s="475"/>
+      <c r="C96" s="472"/>
+      <c r="D96" s="472"/>
+      <c r="E96" s="472"/>
+      <c r="F96" s="472"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="388"/>
-      <c r="B97" s="478" t="s">
+      <c r="B97" s="473" t="s">
         <v>516</v>
       </c>
-      <c r="C97" s="478"/>
-      <c r="D97" s="478"/>
-      <c r="E97" s="478"/>
-      <c r="F97" s="478"/>
+      <c r="C97" s="473"/>
+      <c r="D97" s="473"/>
+      <c r="E97" s="473"/>
+      <c r="F97" s="473"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="388"/>
-      <c r="B98" s="478" t="s">
+      <c r="B98" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C98" s="478"/>
-      <c r="D98" s="478"/>
-      <c r="E98" s="478"/>
-      <c r="F98" s="478"/>
+      <c r="C98" s="473"/>
+      <c r="D98" s="473"/>
+      <c r="E98" s="473"/>
+      <c r="F98" s="473"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="388"/>
@@ -21356,23 +21356,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="388"/>
-      <c r="B107" s="475" t="s">
+      <c r="B107" s="472" t="s">
         <v>518</v>
       </c>
-      <c r="C107" s="475"/>
-      <c r="D107" s="475"/>
-      <c r="E107" s="475"/>
-      <c r="F107" s="475"/>
+      <c r="C107" s="472"/>
+      <c r="D107" s="472"/>
+      <c r="E107" s="472"/>
+      <c r="F107" s="472"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="388"/>
-      <c r="B108" s="475" t="s">
+      <c r="B108" s="472" t="s">
         <v>537</v>
       </c>
-      <c r="C108" s="475"/>
-      <c r="D108" s="475"/>
-      <c r="E108" s="475"/>
-      <c r="F108" s="475"/>
+      <c r="C108" s="472"/>
+      <c r="D108" s="472"/>
+      <c r="E108" s="472"/>
+      <c r="F108" s="472"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="388"/>
@@ -21416,13 +21416,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="388"/>
-      <c r="B114" s="475" t="s">
+      <c r="B114" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C114" s="475"/>
-      <c r="D114" s="475"/>
-      <c r="E114" s="475"/>
-      <c r="F114" s="475"/>
+      <c r="C114" s="472"/>
+      <c r="D114" s="472"/>
+      <c r="E114" s="472"/>
+      <c r="F114" s="472"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="388"/>
@@ -21586,13 +21586,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="473" t="s">
+      <c r="B127" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C127" s="473"/>
-      <c r="D127" s="473"/>
-      <c r="E127" s="473"/>
-      <c r="F127" s="473"/>
+      <c r="C127" s="476"/>
+      <c r="D127" s="476"/>
+      <c r="E127" s="476"/>
+      <c r="F127" s="476"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="348" t="s">
@@ -21605,22 +21605,22 @@
       <c r="F129" s="348"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="474" t="s">
+      <c r="B131" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C131" s="474"/>
-      <c r="D131" s="474"/>
-      <c r="E131" s="474"/>
-      <c r="F131" s="474"/>
+      <c r="C131" s="477"/>
+      <c r="D131" s="477"/>
+      <c r="E131" s="477"/>
+      <c r="F131" s="477"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="475" t="s">
+      <c r="B132" s="472" t="s">
         <v>523</v>
       </c>
-      <c r="C132" s="475"/>
-      <c r="D132" s="475"/>
-      <c r="E132" s="475"/>
-      <c r="F132" s="475"/>
+      <c r="C132" s="472"/>
+      <c r="D132" s="472"/>
+      <c r="E132" s="472"/>
+      <c r="F132" s="472"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="372" t="s">
@@ -21681,7 +21681,7 @@
       </c>
       <c r="C140" s="412">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763701</v>
+        <v>0.25983892380763696</v>
       </c>
       <c r="D140" s="412">
         <f>Scenarios!D62</f>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="F140" s="414">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21702,7 +21702,7 @@
       </c>
       <c r="C141" s="412">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220924</v>
+        <v>0.29876856051220907</v>
       </c>
       <c r="D141" s="412">
         <f>Scenarios!D63</f>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="F141" s="414">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21789,13 +21789,13 @@
       <c r="F147" s="348"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="476" t="s">
+      <c r="B149" s="478" t="s">
         <v>524</v>
       </c>
-      <c r="C149" s="475"/>
-      <c r="D149" s="475"/>
-      <c r="E149" s="475"/>
-      <c r="F149" s="475"/>
+      <c r="C149" s="472"/>
+      <c r="D149" s="472"/>
+      <c r="E149" s="472"/>
+      <c r="F149" s="472"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="372" t="s">
@@ -21803,13 +21803,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="477" t="s">
+      <c r="B152" s="474" t="s">
         <v>525</v>
       </c>
-      <c r="C152" s="477"/>
-      <c r="D152" s="477"/>
-      <c r="E152" s="477"/>
-      <c r="F152" s="477"/>
+      <c r="C152" s="474"/>
+      <c r="D152" s="474"/>
+      <c r="E152" s="474"/>
+      <c r="F152" s="474"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="415" t="s">
@@ -21846,22 +21846,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="472" t="s">
+      <c r="B161" s="475" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="472"/>
-      <c r="D161" s="472"/>
-      <c r="E161" s="472"/>
-      <c r="F161" s="472"/>
+      <c r="C161" s="475"/>
+      <c r="D161" s="475"/>
+      <c r="E161" s="475"/>
+      <c r="F161" s="475"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="472" t="s">
+      <c r="B162" s="475" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="472"/>
-      <c r="D162" s="472"/>
-      <c r="E162" s="472"/>
-      <c r="F162" s="472"/>
+      <c r="C162" s="475"/>
+      <c r="D162" s="475"/>
+      <c r="E162" s="475"/>
+      <c r="F162" s="475"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="346" t="s">
@@ -21885,12 +21885,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21905,15 +21908,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282347D7-1486-4407-9955-7A9A336CC14D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBE7FCD-39EA-4056-A260-31D2CEF51D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="558">
   <si>
     <t>Sales</t>
   </si>
@@ -2075,9 +2075,6 @@
   </si>
   <si>
     <t>High Growth Rate_II</t>
-  </si>
-  <si>
-    <t>Contribution Margin_II</t>
   </si>
   <si>
     <t>Try obtain this number by reverse engineering.</t>
@@ -4997,30 +4994,30 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,25 +5027,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5359,7 +5356,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="431" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F3" s="432">
         <v>46038</v>
@@ -5367,13 +5364,13 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="424" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C4" s="423" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E4" s="433" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F4" s="434" t="s">
         <v>324</v>
@@ -5384,13 +5381,13 @@
         <v>349</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E5" s="436" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F5" s="435" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5398,7 +5395,7 @@
         <v>53</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
@@ -5439,7 +5436,7 @@
         <v>6814.2449511699997</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E10" s="306">
         <f>Scenarios!F34</f>
@@ -5451,13 +5448,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5471,7 +5468,7 @@
         <v>319</v>
       </c>
       <c r="C15" s="420" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>353</v>
@@ -5486,7 +5483,7 @@
         <v>320</v>
       </c>
       <c r="C16" s="420" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>354</v>
@@ -5497,7 +5494,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C17" s="459">
         <v>0.02</v>
@@ -5547,7 +5544,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C21" s="256" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -5569,10 +5566,10 @@
         <v>5.0237106020124003</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5584,10 +5581,10 @@
         <v>6.2699463463342093</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E23" s="446">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5599,7 +5596,7 @@
         <v>7.7521729877457162</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E24" s="446">
         <v>0.1174</v>
@@ -5614,7 +5611,7 @@
         <v>8.7506459962076875</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E25" s="447">
         <v>7.2499999999999995E-2</v>
@@ -5635,22 +5632,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5662,13 +5659,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5688,13 +5685,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5723,13 +5720,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5745,13 +5742,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5815,13 +5812,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5837,7 +5834,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5859,22 +5856,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5996,7 +5993,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -6009,18 +6006,18 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
-        <v>479</v>
-      </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="B73" s="463" t="s">
+        <v>478</v>
+      </c>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6034,13 +6031,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6096,7 +6093,7 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -6184,7 +6181,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
@@ -6197,7 +6194,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6209,31 +6206,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
-        <v>486</v>
-      </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="B96" s="463" t="s">
+        <v>485</v>
+      </c>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
-        <v>485</v>
-      </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="B97" s="467" t="s">
+        <v>484</v>
+      </c>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
-        <v>484</v>
-      </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="B98" s="467" t="s">
+        <v>483</v>
+      </c>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6242,7 +6239,7 @@
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6283,31 +6280,31 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
@@ -6332,17 +6329,17 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
-        <v>492</v>
-      </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="B114" s="463" t="s">
+        <v>491</v>
+      </c>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
@@ -6359,7 +6356,7 @@
         <v>124</v>
       </c>
       <c r="F117" s="345" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6473,13 +6470,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6505,7 +6502,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6514,22 +6511,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6560,28 +6557,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="343" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C139" s="343" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="343" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E139" s="344" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="344" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -6590,7 +6587,7 @@
       </c>
       <c r="C140" s="336">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763696</v>
+        <v>0.25983892380763701</v>
       </c>
       <c r="D140" s="336">
         <f>Scenarios!D62</f>
@@ -6602,7 +6599,7 @@
       </c>
       <c r="F140" s="338">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6611,7 +6608,7 @@
       </c>
       <c r="C141" s="336">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220907</v>
+        <v>0.29876856051220924</v>
       </c>
       <c r="D141" s="336">
         <f>Scenarios!D63</f>
@@ -6623,7 +6620,7 @@
       </c>
       <c r="F141" s="338">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6635,21 +6632,21 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="343" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C143" s="343" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="343" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E143" s="344" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="344" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -6696,7 +6693,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6705,13 +6702,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6748,13 +6745,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
-        <v>439</v>
-      </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="B158" s="464" t="s">
+        <v>438</v>
+      </c>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6762,22 +6759,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6801,18 +6798,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6829,6 +6814,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -7504,7 +7501,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9622,7 +9619,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -10815,7 +10812,7 @@
       <c r="E3" s="237"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -11104,7 +11101,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C9" s="303">
         <f>C61</f>
@@ -12338,7 +12335,7 @@
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -13905,7 +13902,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -15067,7 +15064,7 @@
         <v>36</v>
       </c>
       <c r="C115" s="454" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="240"/>
@@ -16301,10 +16298,10 @@
         <v>1000</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="2:15">
@@ -16320,7 +16317,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F4" s="278">
         <f>-BS!G31</f>
@@ -16348,7 +16345,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F5" s="278">
         <f>BS!D66</f>
@@ -16380,7 +16377,7 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F6" s="287">
         <f>BS!H42</f>
@@ -16391,7 +16388,7 @@
         <v>HKD</v>
       </c>
       <c r="H6" s="311" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I6" s="308">
         <f>I7+I8</f>
@@ -16402,14 +16399,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="321" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C7" s="278">
         <f>F7</f>
         <v>227736.38078016671</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F7" s="286">
         <f>SUM(F4:F6)</f>
@@ -16420,7 +16417,7 @@
         <v>HKD</v>
       </c>
       <c r="H7" s="315" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I7" s="316">
         <f>Normalized_FCF!C9</f>
@@ -16432,7 +16429,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C8" s="286">
         <f>C6+C7</f>
@@ -16443,7 +16440,7 @@
         <v>HKD</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16493,7 +16490,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C10" s="286">
         <f>C8*Exchange_Rate</f>
@@ -16515,7 +16512,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16531,7 +16528,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16549,22 +16546,22 @@
         <v>399</v>
       </c>
       <c r="C14" s="312" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E14" s="106" t="s">
         <v>399</v>
       </c>
       <c r="F14" s="312" t="str">
-        <f>IF(F17=C17,"I","II")</f>
+        <f>IF(ROUND(F17,2)=ROUND(C17,2),"I","II")</f>
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16579,7 +16576,7 @@
         <v>8</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16589,7 +16586,7 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
@@ -16605,33 +16602,33 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="311" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C17" s="309">
         <f>Normalized_FCF!C77</f>
         <v>0.10437815343465008</v>
       </c>
       <c r="E17" s="311" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F17" s="314">
         <f>Scenarios!C40</f>
         <v>0.14083691822897304</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="311" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C18" s="309">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="311" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
@@ -16666,29 +16663,29 @@
         <v>102</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>530</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>555</v>
+      </c>
+      <c r="K20" s="121" t="s">
         <v>531</v>
       </c>
-      <c r="J20" s="121" t="s">
-        <v>556</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>532</v>
-      </c>
       <c r="L20" s="122" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18243,7 +18240,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="318" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B51" s="319">
         <f>C15+1</f>
@@ -18292,7 +18289,7 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="469" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K52" s="469"/>
       <c r="L52" s="320">
@@ -19310,7 +19307,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G89" s="326"/>
       <c r="H89" s="326"/>
@@ -19591,7 +19588,7 @@
         <v>125</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E3" s="97"/>
     </row>
@@ -19733,7 +19730,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19757,7 +19754,7 @@
         <v>15</v>
       </c>
       <c r="E18" s="453" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F18" s="322"/>
     </row>
@@ -19767,35 +19764,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E20" s="322"/>
       <c r="F20" s="322"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C21" s="153" t="s">
         <v>379</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="305" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C22" s="327">
         <v>0.03</v>
@@ -19819,7 +19816,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="305" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C23" s="327">
         <v>0.02</v>
@@ -19842,7 +19839,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="305" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C24" s="327">
         <v>0.01</v>
@@ -19865,7 +19862,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C25" s="444">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19879,33 +19876,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C28" s="153" t="s">
         <v>379</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (HKD)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="305" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C29" s="327">
         <v>0.05</v>
@@ -19928,7 +19925,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="318" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C30" s="327">
         <v>0</v>
@@ -19955,12 +19952,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19971,7 +19968,7 @@
         <v>HKD</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19991,7 +19988,7 @@
         <v>HKD</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F34" s="333">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
@@ -20000,7 +19997,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C35" s="323">
         <f>DCF!C11</f>
@@ -20011,7 +20008,7 @@
         <v>HKD</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F35" s="333">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -20020,7 +20017,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C36" s="324">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -20031,15 +20028,15 @@
         <v>HKD</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F36" s="334" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -20058,14 +20055,14 @@
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>401</v>
+        <v>553</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!C116</f>
         <v>0.14083691822897304</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="41" spans="2:7">
@@ -20237,13 +20234,13 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E60" s="416"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C61" s="153" t="s">
         <v>103</v>
@@ -20256,10 +20253,10 @@
         <v>Buy below (HKD)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
@@ -20268,7 +20265,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.25983892380763696</v>
+        <v>0.25983892380763701</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20280,7 +20277,7 @@
       </c>
       <c r="F62" s="304">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="443">
         <f>(1-E62/C36)</f>
@@ -20293,7 +20290,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.29876856051220907</v>
+        <v>0.29876856051220924</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20305,7 +20302,7 @@
       </c>
       <c r="F63" s="304">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="443">
         <f>(1-E63/C36)</f>
@@ -20314,7 +20311,7 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C65" s="153" t="s">
         <v>103</v>
@@ -20327,10 +20324,10 @@
         <v>Sell above (HKD)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
@@ -20424,7 +20421,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="438" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F3" s="439">
         <f>Thesis!F3</f>
@@ -20433,7 +20430,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="425" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C4" s="426" t="str">
         <f>Thesis!C4</f>
@@ -20441,7 +20438,7 @@
       </c>
       <c r="D4" s="352"/>
       <c r="E4" s="437" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F4" s="440" t="str">
         <f>Thesis!F4</f>
@@ -20457,7 +20454,7 @@
         <v>0345.HK</v>
       </c>
       <c r="E5" s="441" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F5" s="442" t="str">
         <f>Thesis!F5</f>
@@ -20512,7 +20509,7 @@
         <v>6814.2449511699997</v>
       </c>
       <c r="D10" s="346" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E10" s="363">
         <f>Scenarios!F34</f>
@@ -20524,13 +20521,13 @@
       <c r="E11" s="352"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="472" t="s">
-        <v>499</v>
-      </c>
-      <c r="C12" s="472"/>
-      <c r="D12" s="472"/>
-      <c r="E12" s="472"/>
-      <c r="F12" s="472"/>
+      <c r="B12" s="475" t="s">
+        <v>498</v>
+      </c>
+      <c r="C12" s="475"/>
+      <c r="D12" s="475"/>
+      <c r="E12" s="475"/>
+      <c r="F12" s="475"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="350" t="s">
@@ -20573,7 +20570,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="346" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C17" s="427">
         <f>Terminal_Growth</f>
@@ -20626,7 +20623,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="350" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C21" s="364" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -20649,11 +20646,11 @@
         <v>5.0237106020124003</v>
       </c>
       <c r="D22" s="368" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E22" s="369">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20665,11 +20662,11 @@
         <v>6.2699463463342093</v>
       </c>
       <c r="D23" s="368" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E23" s="371">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20681,7 +20678,7 @@
         <v>7.7521729877457162</v>
       </c>
       <c r="D24" s="368" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E24" s="371">
         <f>Thesis!E24</f>
@@ -20697,7 +20694,7 @@
         <v>8.7506459962076875</v>
       </c>
       <c r="D25" s="368" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E25" s="371">
         <f>Thesis!E25</f>
@@ -20715,22 +20712,22 @@
       <c r="F27" s="348"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="472" t="s">
+      <c r="B29" s="475" t="s">
+        <v>499</v>
+      </c>
+      <c r="C29" s="475"/>
+      <c r="D29" s="475"/>
+      <c r="E29" s="475"/>
+      <c r="F29" s="475"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="478" t="s">
         <v>500</v>
       </c>
-      <c r="C29" s="472"/>
-      <c r="D29" s="472"/>
-      <c r="E29" s="472"/>
-      <c r="F29" s="472"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="473" t="s">
-        <v>501</v>
-      </c>
-      <c r="C30" s="473"/>
-      <c r="D30" s="473"/>
-      <c r="E30" s="473"/>
-      <c r="F30" s="473"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
+      <c r="E30" s="478"/>
+      <c r="F30" s="478"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="372" t="s">
@@ -20743,7 +20740,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="471" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C33" s="471"/>
       <c r="D33" s="471"/>
@@ -20769,7 +20766,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="471" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C36" s="471"/>
       <c r="D36" s="471"/>
@@ -20804,7 +20801,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="471" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C40" s="471"/>
       <c r="D40" s="471"/>
@@ -20826,7 +20823,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="471" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C43" s="471"/>
       <c r="D43" s="471"/>
@@ -20878,7 +20875,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="346" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -20896,7 +20893,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="471" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C51" s="471"/>
       <c r="D51" s="471"/>
@@ -20905,7 +20902,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="375" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C52" s="376">
         <f>Normalized_FCF!C12</f>
@@ -20918,12 +20915,12 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="471" t="s">
-        <v>508</v>
-      </c>
-      <c r="C54" s="474"/>
-      <c r="D54" s="474"/>
-      <c r="E54" s="474"/>
-      <c r="F54" s="474"/>
+        <v>507</v>
+      </c>
+      <c r="C54" s="477"/>
+      <c r="D54" s="477"/>
+      <c r="E54" s="477"/>
+      <c r="F54" s="477"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="375" t="s">
@@ -20939,22 +20936,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="472" t="s">
+      <c r="B57" s="475" t="s">
+        <v>508</v>
+      </c>
+      <c r="C57" s="475"/>
+      <c r="D57" s="475"/>
+      <c r="E57" s="475"/>
+      <c r="F57" s="475"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="475" t="s">
         <v>509</v>
       </c>
-      <c r="C57" s="472"/>
-      <c r="D57" s="472"/>
-      <c r="E57" s="472"/>
-      <c r="F57" s="472"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="472" t="s">
-        <v>510</v>
-      </c>
-      <c r="C58" s="472"/>
-      <c r="D58" s="472"/>
-      <c r="E58" s="472"/>
-      <c r="F58" s="472"/>
+      <c r="C58" s="475"/>
+      <c r="D58" s="475"/>
+      <c r="E58" s="475"/>
+      <c r="F58" s="475"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="375" t="s">
@@ -21076,7 +21073,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="348" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B71" s="348"/>
       <c r="C71" s="348"/>
@@ -21089,22 +21086,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="389"/>
-      <c r="B73" s="472" t="s">
-        <v>511</v>
-      </c>
-      <c r="C73" s="472"/>
-      <c r="D73" s="472"/>
-      <c r="E73" s="472"/>
-      <c r="F73" s="472"/>
+      <c r="B73" s="475" t="s">
+        <v>510</v>
+      </c>
+      <c r="C73" s="475"/>
+      <c r="D73" s="475"/>
+      <c r="E73" s="475"/>
+      <c r="F73" s="475"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="473" t="s">
-        <v>480</v>
-      </c>
-      <c r="C74" s="473"/>
-      <c r="D74" s="473"/>
-      <c r="E74" s="473"/>
-      <c r="F74" s="473"/>
+      <c r="B74" s="478" t="s">
+        <v>479</v>
+      </c>
+      <c r="C74" s="478"/>
+      <c r="D74" s="478"/>
+      <c r="E74" s="478"/>
+      <c r="F74" s="478"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="372" t="s">
@@ -21112,13 +21109,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="472" t="s">
-        <v>512</v>
-      </c>
-      <c r="C77" s="472"/>
-      <c r="D77" s="472"/>
-      <c r="E77" s="472"/>
-      <c r="F77" s="472"/>
+      <c r="B77" s="475" t="s">
+        <v>511</v>
+      </c>
+      <c r="C77" s="475"/>
+      <c r="D77" s="475"/>
+      <c r="E77" s="475"/>
+      <c r="F77" s="475"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="346" t="s">
@@ -21166,7 +21163,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="346" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -21184,7 +21181,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="385" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C85" s="393">
         <f>BS!C66</f>
@@ -21210,7 +21207,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="346" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -21241,7 +21238,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="375" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C92" s="390">
         <f>DCF!F8</f>
@@ -21254,7 +21251,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="348" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B94" s="348"/>
       <c r="C94" s="348"/>
@@ -21267,33 +21264,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="388"/>
-      <c r="B96" s="472" t="s">
-        <v>515</v>
-      </c>
-      <c r="C96" s="472"/>
-      <c r="D96" s="472"/>
-      <c r="E96" s="472"/>
-      <c r="F96" s="472"/>
+      <c r="B96" s="475" t="s">
+        <v>514</v>
+      </c>
+      <c r="C96" s="475"/>
+      <c r="D96" s="475"/>
+      <c r="E96" s="475"/>
+      <c r="F96" s="475"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="388"/>
-      <c r="B97" s="473" t="s">
-        <v>516</v>
-      </c>
-      <c r="C97" s="473"/>
-      <c r="D97" s="473"/>
-      <c r="E97" s="473"/>
-      <c r="F97" s="473"/>
+      <c r="B97" s="478" t="s">
+        <v>515</v>
+      </c>
+      <c r="C97" s="478"/>
+      <c r="D97" s="478"/>
+      <c r="E97" s="478"/>
+      <c r="F97" s="478"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="388"/>
-      <c r="B98" s="473" t="s">
-        <v>517</v>
-      </c>
-      <c r="C98" s="473"/>
-      <c r="D98" s="473"/>
-      <c r="E98" s="473"/>
-      <c r="F98" s="473"/>
+      <c r="B98" s="478" t="s">
+        <v>516</v>
+      </c>
+      <c r="C98" s="478"/>
+      <c r="D98" s="478"/>
+      <c r="E98" s="478"/>
+      <c r="F98" s="478"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="388"/>
@@ -21337,7 +21334,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="388"/>
       <c r="B104" s="375" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C104" s="371">
         <v>0</v>
@@ -21356,23 +21353,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="388"/>
-      <c r="B107" s="472" t="s">
-        <v>518</v>
-      </c>
-      <c r="C107" s="472"/>
-      <c r="D107" s="472"/>
-      <c r="E107" s="472"/>
-      <c r="F107" s="472"/>
+      <c r="B107" s="475" t="s">
+        <v>517</v>
+      </c>
+      <c r="C107" s="475"/>
+      <c r="D107" s="475"/>
+      <c r="E107" s="475"/>
+      <c r="F107" s="475"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="388"/>
-      <c r="B108" s="472" t="s">
-        <v>537</v>
-      </c>
-      <c r="C108" s="472"/>
-      <c r="D108" s="472"/>
-      <c r="E108" s="472"/>
-      <c r="F108" s="472"/>
+      <c r="B108" s="475" t="s">
+        <v>536</v>
+      </c>
+      <c r="C108" s="475"/>
+      <c r="D108" s="475"/>
+      <c r="E108" s="475"/>
+      <c r="F108" s="475"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="388"/>
@@ -21380,13 +21377,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="388"/>
       <c r="B110" s="372" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="388"/>
       <c r="B111" s="378" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C111" s="397">
         <f>BS!D47</f>
@@ -21416,13 +21413,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="388"/>
-      <c r="B114" s="472" t="s">
-        <v>519</v>
-      </c>
-      <c r="C114" s="472"/>
-      <c r="D114" s="472"/>
-      <c r="E114" s="472"/>
-      <c r="F114" s="472"/>
+      <c r="B114" s="475" t="s">
+        <v>518</v>
+      </c>
+      <c r="C114" s="475"/>
+      <c r="D114" s="475"/>
+      <c r="E114" s="475"/>
+      <c r="F114" s="475"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="388"/>
@@ -21430,7 +21427,7 @@
     <row r="116" spans="1:6">
       <c r="A116" s="388"/>
       <c r="B116" s="372" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -21565,7 +21562,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="471" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C124" s="471"/>
       <c r="D124" s="471"/>
@@ -21586,17 +21583,17 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="476" t="s">
-        <v>521</v>
-      </c>
-      <c r="C127" s="476"/>
-      <c r="D127" s="476"/>
-      <c r="E127" s="476"/>
-      <c r="F127" s="476"/>
+      <c r="B127" s="473" t="s">
+        <v>520</v>
+      </c>
+      <c r="C127" s="473"/>
+      <c r="D127" s="473"/>
+      <c r="E127" s="473"/>
+      <c r="F127" s="473"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="348" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B129" s="348"/>
       <c r="C129" s="348"/>
@@ -21605,22 +21602,22 @@
       <c r="F129" s="348"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="477" t="s">
+      <c r="B131" s="474" t="s">
+        <v>521</v>
+      </c>
+      <c r="C131" s="474"/>
+      <c r="D131" s="474"/>
+      <c r="E131" s="474"/>
+      <c r="F131" s="474"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C131" s="477"/>
-      <c r="D131" s="477"/>
-      <c r="E131" s="477"/>
-      <c r="F131" s="477"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="472" t="s">
-        <v>523</v>
-      </c>
-      <c r="C132" s="472"/>
-      <c r="D132" s="472"/>
-      <c r="E132" s="472"/>
-      <c r="F132" s="472"/>
+      <c r="C132" s="475"/>
+      <c r="D132" s="475"/>
+      <c r="E132" s="475"/>
+      <c r="F132" s="475"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="372" t="s">
@@ -21651,28 +21648,28 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="372" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C138" s="410"/>
       <c r="D138" s="410"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="343" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C139" s="343" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="343" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E139" s="344" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (HKD)</v>
       </c>
       <c r="F139" s="344" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -21681,7 +21678,7 @@
       </c>
       <c r="C140" s="412">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763696</v>
+        <v>0.25983892380763701</v>
       </c>
       <c r="D140" s="412">
         <f>Scenarios!D62</f>
@@ -21693,7 +21690,7 @@
       </c>
       <c r="F140" s="414">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21702,7 +21699,7 @@
       </c>
       <c r="C141" s="412">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220907</v>
+        <v>0.29876856051220924</v>
       </c>
       <c r="D141" s="412">
         <f>Scenarios!D63</f>
@@ -21714,26 +21711,26 @@
       </c>
       <c r="F141" s="414">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="343" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C143" s="343" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="343" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E143" s="344" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (HKD)</v>
       </c>
       <c r="F143" s="344" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -21780,7 +21777,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="348" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B147" s="348"/>
       <c r="C147" s="348"/>
@@ -21789,13 +21786,13 @@
       <c r="F147" s="348"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="478" t="s">
-        <v>524</v>
-      </c>
-      <c r="C149" s="472"/>
-      <c r="D149" s="472"/>
-      <c r="E149" s="472"/>
-      <c r="F149" s="472"/>
+      <c r="B149" s="476" t="s">
+        <v>523</v>
+      </c>
+      <c r="C149" s="475"/>
+      <c r="D149" s="475"/>
+      <c r="E149" s="475"/>
+      <c r="F149" s="475"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="372" t="s">
@@ -21803,13 +21800,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="474" t="s">
-        <v>525</v>
-      </c>
-      <c r="C152" s="474"/>
-      <c r="D152" s="474"/>
-      <c r="E152" s="474"/>
-      <c r="F152" s="474"/>
+      <c r="B152" s="477" t="s">
+        <v>524</v>
+      </c>
+      <c r="C152" s="477"/>
+      <c r="D152" s="477"/>
+      <c r="E152" s="477"/>
+      <c r="F152" s="477"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="415" t="s">
@@ -21828,12 +21825,12 @@
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="346" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="471" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C158" s="471"/>
       <c r="D158" s="471"/>
@@ -21842,30 +21839,30 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="346" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="475" t="s">
+      <c r="B161" s="472" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="475"/>
-      <c r="D161" s="475"/>
-      <c r="E161" s="475"/>
-      <c r="F161" s="475"/>
+      <c r="C161" s="472"/>
+      <c r="D161" s="472"/>
+      <c r="E161" s="472"/>
+      <c r="F161" s="472"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="475" t="s">
+      <c r="B162" s="472" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="475"/>
-      <c r="D162" s="475"/>
-      <c r="E162" s="475"/>
-      <c r="F162" s="475"/>
+      <c r="C162" s="472"/>
+      <c r="D162" s="472"/>
+      <c r="E162" s="472"/>
+      <c r="F162" s="472"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="346" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="165" spans="2:6">
@@ -21885,15 +21882,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21908,12 +21902,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B18A0F-57BE-4A66-A9E9-A91B58EDDDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7F467E-F4B0-4F33-8CFB-8885920BEDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4991,30 +4991,30 @@
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5024,6 +5024,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5033,16 +5042,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5412,7 +5412,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6814.2449511699997</v>
+        <v>6824.6802420600006</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20720003239761747</v>
+        <v>0.20657380007864951</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5445,13 +5445,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5629,22 +5629,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5682,13 +5682,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5717,13 +5717,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5739,13 +5739,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5809,13 +5809,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5831,7 +5831,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5853,22 +5853,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.0300173108426608E-2</v>
+        <v>7.0192680488994769E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.1745788667687591E-2</v>
+        <v>2.1712538226299691E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6003,13 +6003,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6028,13 +6028,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6203,31 +6203,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6277,22 +6277,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6326,13 +6326,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6467,13 +6467,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6508,22 +6508,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6699,13 +6699,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6742,13 +6742,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6756,22 +6756,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6795,6 +6795,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6811,18 +6823,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14260,28 +14260,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1745788667687591E-2</v>
+        <v>2.1712538226299691E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1745788667687591E-2</v>
+        <v>2.1712538226299691E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1791730474732006E-2</v>
+        <v>1.1773700305810398E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1347626339969367E-3</v>
+        <v>4.1284403669724773E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0229709035222045E-2</v>
+        <v>5.015290519877675E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9310872894333835E-2</v>
+        <v>4.9235474006116199E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15474,50 +15474,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0300173108426608E-2</v>
+        <v>7.0192680488994769E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4400025774381928E-2</v>
+        <v>7.4286264267081653E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7052542546661533E-2</v>
+        <v>5.6965306243073367E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.7437016401384089E-2</v>
+        <v>3.7379773257039464E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0024456336115623E-2</v>
+        <v>2.9978547381473243E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13013752900792611</v>
+        <v>0.12993854196051338</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12738491296104049</v>
+        <v>0.1271901348066658</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15262409958148476</v>
+        <v>0.15239072939863846</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13392987873781995</v>
+        <v>0.13372509299051441</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.7595405619490289E-2</v>
+        <v>9.7446177170530821E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11563408795052313</v>
+        <v>0.1154572774184887</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15531,43 +15531,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5303691270842076E-2</v>
+        <v>3.5249710091528857E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.728555413608604E-2</v>
+        <v>1.725912362517459E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0901442714331147E-3</v>
+        <v>3.0854192801923913E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.368288800247649E-2</v>
+        <v>-2.3646675635500228E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6511125476753215E-2</v>
+        <v>8.637884546837897E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3588277803574071E-2</v>
+        <v>8.3460466981244444E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10972528950131466</v>
+        <v>0.1095575138292943</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4222471396447183E-2</v>
+        <v>9.4078400339266066E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5871810403268518E-2</v>
+        <v>9.5725217421000514E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.295034945917934E-2</v>
+        <v>8.2823514062452766E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19993,7 +19993,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20004,7 +20004,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20720003239761747</v>
+        <v>0.20657380007864951</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20518,14 +20518,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6814.2449511699997</v>
+        <v>6824.6802420600006</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20720003239761747</v>
+        <v>0.20657380007864951</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20533,13 +20533,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20724,22 +20724,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20929,10 +20929,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20948,22 +20948,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.0300173108426608E-2</v>
+        <v>7.0192680488994769E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.1745788667687591E-2</v>
+        <v>2.1712538226299691E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21098,22 +21098,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21121,13 +21121,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21276,33 +21276,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21365,23 +21365,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21425,13 +21425,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21595,13 +21595,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21614,22 +21614,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21798,13 +21798,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21812,13 +21812,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21855,22 +21855,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21894,12 +21894,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21914,15 +21917,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7F467E-F4B0-4F33-8CFB-8885920BEDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664F65A5-2D13-4114-84EA-1FA1768D6930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3261,10 +3261,10 @@
     <t>FCFE Margin</t>
   </si>
   <si>
-    <t>Long-term Projection</t>
-  </si>
-  <si>
     <t>FCFE and TV</t>
+  </si>
+  <si>
+    <t>Sales/Total Assets g Projection</t>
   </si>
 </sst>
 </file>
@@ -4985,12 +4985,10 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5412,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.54</v>
+        <v>6.9</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5430,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6824.6802420600006</v>
+        <v>7200.3507141</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.20657380007864951</v>
+        <v>0.1848541854186791</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5902,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.0192680488994769E-2</v>
+        <v>6.6530453680873292E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5912,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.1712538226299691E-2</v>
+        <v>2.0579710144927533E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -10821,7 +10819,7 @@
       <c r="B4" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="459">
+      <c r="C4" s="458">
         <f>C100*C117</f>
         <v>6273585</v>
       </c>
@@ -14260,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1712538226299691E-2</v>
+        <v>2.0579710144927533E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1712538226299691E-2</v>
+        <v>2.0579710144927533E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1773700305810398E-2</v>
+        <v>1.1159420289855072E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1284403669724773E-3</v>
+        <v>3.913043478260869E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.015290519877675E-2</v>
+        <v>4.7536231884057964E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9235474006116199E-2</v>
+        <v>4.6666666666666655E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -14953,7 +14951,9 @@
         <v>303</v>
       </c>
       <c r="C112" s="151"/>
-      <c r="E112" s="237"/>
+      <c r="E112" s="451" t="s">
+        <v>557</v>
+      </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>3.5707866382893818</v>
@@ -15005,7 +15005,10 @@
         <v>304</v>
       </c>
       <c r="C113" s="151"/>
-      <c r="E113" s="237"/>
+      <c r="E113" s="459">
+        <f>(Normalized_FCF!E117/Normalized_FCF!C117)^(1/DCF!C15)-1</f>
+        <v>0</v>
+      </c>
       <c r="G113" s="251">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6943804489328969</v>
@@ -15064,8 +15067,9 @@
         <v>327</v>
       </c>
       <c r="D115" s="52"/>
-      <c r="E115" s="451" t="s">
-        <v>556</v>
+      <c r="E115" s="451" t="str">
+        <f>DCF!F15&amp;"yrs Projection"</f>
+        <v>8yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -15179,7 +15183,7 @@
         <f>G117</f>
         <v>1.1106245684847842</v>
       </c>
-      <c r="E117" s="458">
+      <c r="E117" s="452">
         <f>C117</f>
         <v>1.1106245684847842</v>
       </c>
@@ -15474,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0192680488994769E-2</v>
+        <v>6.6530453680873292E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.4286264267081653E-2</v>
+        <v>7.0410459174886086E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.6965306243073367E-2</v>
+        <v>5.3993203308652149E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.7379773257039464E-2</v>
+        <v>3.5429524217541752E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9978547381473243E-2</v>
+        <v>2.8414449257222463E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12993854196051338</v>
+        <v>0.1231591397712692</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.1271901348066658</v>
+        <v>0.12055412777327454</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15239072939863846</v>
+        <v>0.14443990873436166</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13372509299051441</v>
+        <v>0.12674813161709628</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.7446177170530821E-2</v>
+        <v>9.2362028796416168E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.1154572774184887</v>
+        <v>0.10943341946621971</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15531,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5249710091528857E-2</v>
+        <v>3.3410594782405614E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.725912362517459E-2</v>
+        <v>1.6358647609948092E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0854192801923913E-3</v>
+        <v>2.9244408829649619E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.3646675635500228E-2</v>
+        <v>-2.2412936037126303E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.637884546837897E-2</v>
+        <v>8.1872123096115731E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3460466981244444E-2</v>
+        <v>7.9106007834396905E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1095575138292943</v>
+        <v>0.10384146962950502</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4078400339266066E-2</v>
+        <v>8.9169962060695662E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5725217421000514E-2</v>
+        <v>9.073085825120919E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2823514062452766E-2</v>
+        <v>7.8502287241803054E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16685,7 +16689,7 @@
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I20" s="121" t="s">
         <v>530</v>
@@ -19993,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.54</v>
+        <v>6.9</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20004,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.20657380007864951</v>
+        <v>0.1848541854186791</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20500,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.54</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20518,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6824.6802420600006</v>
+        <v>7200.3507141</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.20657380007864951</v>
+        <v>0.1848541854186791</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20997,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.0192680488994769E-2</v>
+        <v>6.6530453680873292E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21007,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.1712538226299691E-2</v>
+        <v>2.0579710144927533E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664F65A5-2D13-4114-84EA-1FA1768D6930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E27A97-7DEF-4D6C-8C4C-4F80413309F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7200.3507141</v>
+        <v>7116.8683869800007</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1848541854186791</v>
+        <v>0.18954671847205182</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6530453680873292E-2</v>
+        <v>6.7310869559827818E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.0579710144927533E-2</v>
+        <v>2.0821114369501462E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0579710144927533E-2</v>
+        <v>2.0821114369501462E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0579710144927533E-2</v>
+        <v>2.0821114369501462E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1159420289855072E-2</v>
+        <v>1.1290322580645161E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.913043478260869E-3</v>
+        <v>3.9589442815249265E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7536231884057964E-2</v>
+        <v>4.8093841642228734E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6666666666666655E-2</v>
+        <v>4.7214076246334301E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6530453680873292E-2</v>
+        <v>6.7310869559827818E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.0410459174886086E-2</v>
+        <v>7.123638831476746E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3993203308652149E-2</v>
+        <v>5.4626554667111409E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5429524217541752E-2</v>
+        <v>3.5845119809536377E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8414449257222463E-2</v>
+        <v>2.8747756579887832E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1231591397712692</v>
+        <v>0.12460382176272104</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12055412777327454</v>
+        <v>0.1219682524392367</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14443990873436166</v>
+        <v>0.14613421851423689</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12674813161709628</v>
+        <v>0.12823491321964287</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.2362028796416168E-2</v>
+        <v>9.3445454354145391E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10943341946621971</v>
+        <v>0.11071709594089678</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3410594782405614E-2</v>
+        <v>3.3802507917683099E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6358647609948092E-2</v>
+        <v>1.6550537904492936E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9244408829649619E-3</v>
+        <v>2.9587451748472491E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2412936037126303E-2</v>
+        <v>-2.2675844377737755E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1872123096115731E-2</v>
+        <v>8.2832499906627347E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9106007834396905E-2</v>
+        <v>8.0033937545064313E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10384146962950502</v>
+        <v>0.10505955138468984</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9169962060695662E-2</v>
+        <v>9.0215944020351921E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.073085825120919E-2</v>
+        <v>9.1795149843598739E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8502287241803054E-2</v>
+        <v>7.9423135185988425E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1848541854186791</v>
+        <v>0.18954671847205182</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7200.3507141</v>
+        <v>7116.8683869800007</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1848541854186791</v>
+        <v>0.18954671847205182</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6530453680873292E-2</v>
+        <v>6.7310869559827818E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.0579710144927533E-2</v>
+        <v>2.0821114369501462E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E27A97-7DEF-4D6C-8C4C-4F80413309F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E0B712-4BC6-4514-B9FF-BE5608215561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E0B712-4BC6-4514-B9FF-BE5608215561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890D9A15-C00F-45A8-90B1-5ADEE652E6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5564,7 +5564,7 @@
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5579,7 +5579,7 @@
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763696</v>
+        <v>0.25983892380763701</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220907</v>
+        <v>0.29876856051220924</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -16568,7 +16568,7 @@
         <v>399</v>
       </c>
       <c r="F14" s="309" t="str">
-        <f>IF(ROUND(F17,2)=ROUND(C17,2),"I","II")</f>
+        <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>II</v>
       </c>
       <c r="H14" s="106" t="s">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.25983892380763696</v>
+        <v>0.25983892380763701</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.29876856051220907</v>
+        <v>0.29876856051220924</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763696</v>
+        <v>0.25983892380763701</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.29465259038036601</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220907</v>
+        <v>0.29876856051220924</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
@@ -21727,7 +21727,7 @@
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.20075184365903001</v>
       </c>
     </row>
     <row r="143" spans="1:6">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890D9A15-C00F-45A8-90B1-5ADEE652E6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA1D92-CF9D-4FCA-B964-38046DB5B1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.82</v>
+        <v>6.95</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7116.8683869800007</v>
+        <v>7252.5271685500002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18954671847205182</v>
+        <v>0.18195844033521166</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5564,7 +5564,7 @@
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5579,7 +5579,7 @@
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7310869559827818E-2</v>
+        <v>6.6051817323456941E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.0821114369501462E-2</v>
+        <v>2.043165467625899E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763701</v>
+        <v>0.25983892380763696</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220924</v>
+        <v>0.29876856051220907</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0821114369501462E-2</v>
+        <v>2.043165467625899E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0821114369501462E-2</v>
+        <v>2.043165467625899E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1290322580645161E-2</v>
+        <v>1.1079136690647482E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.9589442815249265E-3</v>
+        <v>3.8848920863309351E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.8093841642228734E-2</v>
+        <v>4.7194244604316538E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7214076246334301E-2</v>
+        <v>4.6330935251798551E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7310869559827818E-2</v>
+        <v>6.6051817323456941E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.123638831476746E-2</v>
+        <v>6.9903909108879711E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.4626554667111409E-2</v>
+        <v>5.3604762997079114E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5845119809536377E-2</v>
+        <v>3.5174635554106201E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8747756579887832E-2</v>
+        <v>2.8210028758969066E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12460382176272104</v>
+        <v>0.12227310279449749</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.1219682524392367</v>
+        <v>0.11968683189001358</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14613421851423689</v>
+        <v>0.14340077270030152</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12823491321964287</v>
+        <v>0.12583627455510277</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.3445454354145391E-2</v>
+        <v>9.1697553769103823E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11071709594089678</v>
+        <v>0.10864612867869296</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3802507917683099E-2</v>
+        <v>3.3170230791165288E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6550537904492936E-2</v>
+        <v>1.6240959497646305E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9587451748472491E-3</v>
+        <v>2.9034017399220489E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2675844377737755E-2</v>
+        <v>-2.2251691892974313E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2832499906627347E-2</v>
+        <v>8.1283115016287558E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0033937545064313E-2</v>
+        <v>7.8536899864365281E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10505955138468984</v>
+        <v>0.10309440869691866</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0215944020351921E-2</v>
+        <v>8.8528451542273401E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1795149843598739E-2</v>
+        <v>9.0078118263790419E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9423135185988425E-2</v>
+        <v>7.7937522585387206E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.82</v>
+        <v>6.95</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18954671847205182</v>
+        <v>0.18195844033521166</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.25983892380763701</v>
+        <v>0.25983892380763696</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
@@ -20306,7 +20306,7 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.29876856051220924</v>
+        <v>0.29876856051220907</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
@@ -20318,7 +20318,7 @@
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.82</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7116.8683869800007</v>
+        <v>7252.5271685500002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18954671847205182</v>
+        <v>0.18195844033521166</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7310869559827818E-2</v>
+        <v>6.6051817323456941E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.0821114369501462E-2</v>
+        <v>2.043165467625899E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763701</v>
+        <v>0.25983892380763696</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
@@ -21706,7 +21706,7 @@
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.29465259038036606</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220924</v>
+        <v>0.29876856051220907</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
@@ -21727,7 +21727,7 @@
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.20075184365903009</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA1D92-CF9D-4FCA-B964-38046DB5B1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42F55ED-008A-4215-BC64-8EB249778FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.95</v>
+        <v>6.98</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7252.5271685500002</v>
+        <v>7283.8330412200003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18195844033521166</v>
+        <v>0.18023444042885403</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.6051817323456941E-2</v>
+        <v>6.5767926991121162E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.043165467625899E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.043165467625899E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.043165467625899E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1079136690647482E-2</v>
+        <v>1.1031518624641834E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.8848920863309351E-3</v>
+        <v>3.8681948424068766E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7194244604316538E-2</v>
+        <v>4.6991404011461312E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6330935251798551E-2</v>
+        <v>4.6131805157593117E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6051817323456941E-2</v>
+        <v>6.5767926991121162E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9903909108879711E-2</v>
+        <v>6.9603462508125213E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3604762997079114E-2</v>
+        <v>5.3374370032908285E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5174635554106201E-2</v>
+        <v>3.5023455172068493E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8210028758969066E-2</v>
+        <v>2.8088782217025071E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12227310279449749</v>
+        <v>0.12174757369939219</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11968683189001358</v>
+        <v>0.11917241857243471</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14340077270030152</v>
+        <v>0.14278443700101656</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12583627455510277</v>
+        <v>0.12529543096818971</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.1697553769103823E-2</v>
+        <v>9.1303438208491627E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10864612867869296</v>
+        <v>0.10817916824024584</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3170230791165288E-2</v>
+        <v>3.3027665329312138E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6240959497646305E-2</v>
+        <v>1.6171155946796825E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9034017399220489E-3</v>
+        <v>2.890922935882269E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2251691892974313E-2</v>
+        <v>-2.2156054248735169E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1283115016287558E-2</v>
+        <v>8.0933760653753364E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8536899864365281E-2</v>
+        <v>7.8199348718816425E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10309440869691866</v>
+        <v>0.1026513095191382</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8528451542273401E-2</v>
+        <v>8.8147956764871083E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0078118263790419E-2</v>
+        <v>8.9690963027699633E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7937522585387206E-2</v>
+        <v>7.7602547559948581E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.95</v>
+        <v>6.98</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18195844033521166</v>
+        <v>0.18023444042885403</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.95</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7252.5271685500002</v>
+        <v>7283.8330412200003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18195844033521166</v>
+        <v>0.18023444042885403</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.6051817323456941E-2</v>
+        <v>6.5767926991121162E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.043165467625899E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42F55ED-008A-4215-BC64-8EB249778FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98CC97A-E44D-492E-96FF-15E8058E3E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98CC97A-E44D-492E-96FF-15E8058E3E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D3E540-6374-44A9-A7B8-CF220FC35C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.98</v>
+        <v>7.11</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7283.8330412200003</v>
+        <v>7419.4918227899998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18023444042885403</v>
+        <v>0.17287760400666741</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.5767926991121162E-2</v>
+        <v>6.4565419183969866E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.0343839541547275E-2</v>
+        <v>1.9971870604781995E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0343839541547275E-2</v>
+        <v>1.9971870604781995E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0343839541547275E-2</v>
+        <v>1.9971870604781995E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1031518624641834E-2</v>
+        <v>1.0829817158931082E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.8681948424068766E-3</v>
+        <v>3.7974683544303796E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6991404011461312E-2</v>
+        <v>4.6132208157524605E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6131805157593117E-2</v>
+        <v>4.5288326300984519E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5767926991121162E-2</v>
+        <v>6.4565419183969866E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9603462508125213E-2</v>
+        <v>6.8330825359594102E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3374370032908285E-2</v>
+        <v>5.2398467345949343E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5023455172068493E-2</v>
+        <v>3.4383082573985667E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8088782217025071E-2</v>
+        <v>2.7575203920511254E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12174757369939219</v>
+        <v>0.11952152804806716</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11917241857243471</v>
+        <v>0.11699345733271369</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14278443700101656</v>
+        <v>0.1401737510924185</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12529543096818971</v>
+        <v>0.12300451591532549</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.1303438208491627E-2</v>
+        <v>8.9634036384707669E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10817916824024584</v>
+        <v>0.10620120876468579</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3027665329312138E-2</v>
+        <v>3.2423783966047642E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6171155946796825E-2</v>
+        <v>1.587548080290321E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.890922935882269E-3</v>
+        <v>2.8380649919069255E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2156054248735169E-2</v>
+        <v>-2.1750950584552953E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0933760653753364E-2</v>
+        <v>7.9453959122812737E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8199348718816425E-2</v>
+        <v>7.6769543467980123E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1026513095191382</v>
+        <v>0.10077442200331711</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8147956764871083E-2</v>
+        <v>8.653625010109707E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9690963027699633E-2</v>
+        <v>8.8051043872481499E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7602547559948581E-2</v>
+        <v>7.6183654285294111E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.98</v>
+        <v>7.11</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18023444042885403</v>
+        <v>0.17287760400666741</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.98</v>
+        <v>7.11</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7283.8330412200003</v>
+        <v>7419.4918227899998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18023444042885403</v>
+        <v>0.17287760400666741</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.5767926991121162E-2</v>
+        <v>6.4565419183969866E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.0343839541547275E-2</v>
+        <v>1.9971870604781995E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D3E540-6374-44A9-A7B8-CF220FC35C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646B6A4E-9280-464A-8604-7FDD316F3FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7419.4918227899998</v>
+        <v>7461.2329863500008</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17287760400666741</v>
+        <v>0.17065035608892362</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4565419183969866E-2</v>
+        <v>6.4204214041681917E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>1.9971870604781995E-2</v>
+        <v>1.9860139860139858E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9971870604781995E-2</v>
+        <v>1.9860139860139858E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9971870604781995E-2</v>
+        <v>1.9860139860139858E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0829817158931082E-2</v>
+        <v>1.0769230769230769E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.7974683544303796E-3</v>
+        <v>3.7762237762237758E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6132208157524605E-2</v>
+        <v>4.5874125874125864E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5288326300984519E-2</v>
+        <v>4.5034965034965027E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4565419183969866E-2</v>
+        <v>6.4204214041681917E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.8330825359594102E-2</v>
+        <v>6.7948555007932038E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.2398467345949343E-2</v>
+        <v>5.210532906709088E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4383082573985667E-2</v>
+        <v>3.4190729664480848E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7575203920511254E-2</v>
+        <v>2.742093704543147E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11952152804806716</v>
+        <v>0.11885287614290314</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11699345733271369</v>
+        <v>0.1163389484805027</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.1401737510924185</v>
+        <v>0.13938956227511826</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12300451591532549</v>
+        <v>0.12231637876335165</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.9634036384707669E-2</v>
+        <v>8.9132587230107904E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10620120876468579</v>
+        <v>0.10560707612824</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2423783966047642E-2</v>
+        <v>3.2242392167636184E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.587548080290321E-2</v>
+        <v>1.578666692428557E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8380649919069255E-3</v>
+        <v>2.8221877052389144E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1750950584552953E-2</v>
+        <v>-2.1629266944919089E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9453959122812737E-2</v>
+        <v>7.9009461449398397E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6769543467980123E-2</v>
+        <v>7.6340063504522895E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10077442200331711</v>
+        <v>0.10021064901308877</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.653625010109707E-2</v>
+        <v>8.6052131219412603E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8051043872481499E-2</v>
+        <v>8.7558450620048023E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6183654285294111E-2</v>
+        <v>7.57574520235582E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17287760400666741</v>
+        <v>0.17065035608892362</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.11</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7419.4918227899998</v>
+        <v>7461.2329863500008</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17287760400666741</v>
+        <v>0.17065035608892362</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4565419183969866E-2</v>
+        <v>6.4204214041681917E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>1.9971870604781995E-2</v>
+        <v>1.9860139860139858E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{646B6A4E-9280-464A-8604-7FDD316F3FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0604A62D-9DB9-405D-B979-31215EAEB4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7461.2329863500008</v>
+        <v>7555.1506043600002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17065035608892362</v>
+        <v>0.16569989622717521</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4204214041681917E-2</v>
+        <v>6.340609535884334E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>1.9860139860139858E-2</v>
+        <v>1.9613259668508284E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9860139860139858E-2</v>
+        <v>1.9613259668508284E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9860139860139858E-2</v>
+        <v>1.9613259668508284E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0769230769230769E-2</v>
+        <v>1.0635359116022099E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.7762237762237758E-3</v>
+        <v>3.729281767955801E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5874125874125864E-2</v>
+        <v>4.5303867403314907E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5034965034965027E-2</v>
+        <v>4.447513812154695E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4204214041681917E-2</v>
+        <v>6.340609535884334E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7948555007932038E-2</v>
+        <v>6.7103890650098627E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.210532906709088E-2</v>
+        <v>5.1457610888080083E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4190729664480848E-2</v>
+        <v>3.3765706781911341E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.742093704543147E-2</v>
+        <v>2.7080069043485498E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11885287614290314</v>
+        <v>0.11737542326267369</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.1163389484805027</v>
+        <v>0.11489274608226442</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13938956227511826</v>
+        <v>0.13765681909766514</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12231637876335165</v>
+        <v>0.12079587129253651</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.9132587230107904E-2</v>
+        <v>8.8024585455148005E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10560707612824</v>
+        <v>0.10429428098299945</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2242392167636184E-2</v>
+        <v>3.1841588950082697E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.578666692428557E-2</v>
+        <v>1.5590423827160473E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8221877052389144E-3</v>
+        <v>2.7871052613892594E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1629266944919089E-2</v>
+        <v>-2.1360394842012635E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9009461449398397E-2</v>
+        <v>7.8027299635800892E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6340063504522895E-2</v>
+        <v>7.5391084814549536E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10021064901308877</v>
+        <v>9.8964936525356997E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6052131219412603E-2</v>
+        <v>8.4982422405911612E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7558450620048023E-2</v>
+        <v>8.6470016841622019E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.57574520235582E-2</v>
+        <v>7.4815715741497382E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17065035608892362</v>
+        <v>0.16569989622717521</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7461.2329863500008</v>
+        <v>7555.1506043600002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17065035608892362</v>
+        <v>0.16569989622717521</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4204214041681917E-2</v>
+        <v>6.340609535884334E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>1.9860139860139858E-2</v>
+        <v>1.9613259668508284E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0604A62D-9DB9-405D-B979-31215EAEB4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC97279-9567-4CA6-8397-3EC05407EE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7555.1506043600002</v>
+        <v>7544.7153134700002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16569989622717521</v>
+        <v>0.16624584104942389</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.340609535884334E-2</v>
+        <v>6.3493793969298162E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>1.9613259668508284E-2</v>
+        <v>1.9640387275242043E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9613259668508284E-2</v>
+        <v>1.9640387275242043E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9613259668508284E-2</v>
+        <v>1.9640387275242043E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0635359116022099E-2</v>
+        <v>1.0650069156293221E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.729281767955801E-3</v>
+        <v>3.734439834024896E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5303867403314907E-2</v>
+        <v>4.5366528354080213E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.447513812154695E-2</v>
+        <v>4.453665283540801E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.340609535884334E-2</v>
+        <v>6.3493793969298162E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7103890650098627E-2</v>
+        <v>6.7196703776862238E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1457610888080083E-2</v>
+        <v>5.1528783240622378E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3765706781911341E-2</v>
+        <v>3.3812409004292956E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7080069043485498E-2</v>
+        <v>2.7117524187390732E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11737542326267369</v>
+        <v>0.11753776824643948</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11489274608226442</v>
+        <v>0.11505165721100889</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13765681909766514</v>
+        <v>0.13784721580457754</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12079587129253651</v>
+        <v>0.12096294718644042</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.8024585455148005E-2</v>
+        <v>8.8146334535998835E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10429428098299945</v>
+        <v>0.10443853310054163</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1841588950082697E-2</v>
+        <v>3.188562987532486E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5590423827160473E-2</v>
+        <v>1.5611987345593614E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7871052613892594E-3</v>
+        <v>2.7909601787632419E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1360394842012635E-2</v>
+        <v>-2.1389938956593565E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8027299635800892E-2</v>
+        <v>7.8135221212060652E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5391084814549536E-2</v>
+        <v>7.5495360173905762E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8964936525356997E-2</v>
+        <v>9.9101817488739238E-2</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4982422405911612E-2</v>
+        <v>8.509996379236516E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6470016841622019E-2</v>
+        <v>8.6589615758415409E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4815715741497382E-2</v>
+        <v>7.4919195293007071E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16569989622717521</v>
+        <v>0.16624584104942389</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7555.1506043600002</v>
+        <v>7544.7153134700002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16569989622717521</v>
+        <v>0.16624584104942389</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.340609535884334E-2</v>
+        <v>6.3493793969298162E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>1.9613259668508284E-2</v>
+        <v>1.9640387275242043E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC97279-9567-4CA6-8397-3EC05407EE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D869E7-CEFE-4845-9C25-A8D0CF6E4FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7544.7153134700002</v>
+        <v>7409.0565318999998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16624584104942389</v>
+        <v>0.17343705650576521</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.3493793969298162E-2</v>
+        <v>6.4656356394088135E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>1.9640387275242043E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9640387275242043E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9640387275242043E-2</v>
+        <v>0.02</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0650069156293221E-2</v>
+        <v>1.0845070422535212E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.734439834024896E-3</v>
+        <v>3.802816901408451E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5366528354080213E-2</v>
+        <v>4.6197183098591547E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.453665283540801E-2</v>
+        <v>4.5352112676056336E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.3493793969298162E-2</v>
+        <v>6.4656356394088135E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7196703776862238E-2</v>
+        <v>6.8427065958692121E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.1528783240622378E-2</v>
+        <v>5.247226800418308E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.3812409004292956E-2</v>
+        <v>3.4431509450850439E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7117524187390732E-2</v>
+        <v>2.7614042235892255E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11753776824643948</v>
+        <v>0.11968986822841655</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11505165721100889</v>
+        <v>0.11715823685008372</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13784721580457754</v>
+        <v>0.14037117891085854</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12096294718644042</v>
+        <v>0.12317776171238935</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.8146334535998835E-2</v>
+        <v>8.9760281506376285E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10443853310054163</v>
+        <v>0.10635078793196001</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.188562987532486E-2</v>
+        <v>3.2469451267408272E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5611987345593614E-2</v>
+        <v>1.5897840635019977E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7909601787632419E-3</v>
+        <v>2.8420622665434143E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1389938956593565E-2</v>
+        <v>-2.1781585726221339E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8135221212060652E-2</v>
+        <v>7.956586610749275E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5495360173905762E-2</v>
+        <v>7.6877669585540667E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9101817488739238E-2</v>
+        <v>0.1009163578089556</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.509996379236516E-2</v>
+        <v>8.665813214349298E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6589615758415409E-2</v>
+        <v>8.8175059427231472E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4919195293007071E-2</v>
+        <v>7.6290955206822691E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16624584104942389</v>
+        <v>0.17343705650576521</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7544.7153134700002</v>
+        <v>7409.0565318999998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16624584104942389</v>
+        <v>0.17343705650576521</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.3493793969298162E-2</v>
+        <v>6.4656356394088135E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>1.9640387275242043E-2</v>
+        <v>0.02</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D869E7-CEFE-4845-9C25-A8D0CF6E4FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD96E67-C3D0-4EFB-89D7-013A94C7A3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD96E67-C3D0-4EFB-89D7-013A94C7A3FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D73A41-07E1-454F-BFA5-B14CAD1655C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3272,27 +3283,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4044,7 +4055,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4086,17 +4097,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4105,7 +4116,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4179,10 +4190,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4193,7 +4204,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4231,7 +4242,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4241,7 +4252,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4252,19 +4263,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4272,8 +4283,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4296,29 +4307,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4335,15 +4346,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4354,11 +4365,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4419,14 +4430,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4439,7 +4450,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4476,7 +4487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4493,7 +4504,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4539,7 +4550,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4554,13 +4565,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4576,53 +4587,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4639,7 +4650,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4652,21 +4663,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4676,14 +4687,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4692,8 +4703,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4705,7 +4716,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4713,7 +4724,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4752,7 +4763,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4766,39 +4777,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4809,7 +4820,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4820,10 +4831,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4832,7 +4843,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4845,7 +4856,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4854,8 +4865,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4863,10 +4874,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4875,10 +4886,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4895,16 +4906,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4925,7 +4936,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4943,7 +4954,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4953,10 +4964,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4971,7 +4982,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4985,34 +4996,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5033,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,21 +5051,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5327,7 +5338,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5336,7 +5347,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5349,7 +5360,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5357,7 +5368,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5371,7 +5382,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5385,7 +5396,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5395,7 +5406,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5405,16 +5416,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.1</v>
+        <v>7.02</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5422,43 +5433,43 @@
         <v>1043529089</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7409.0565318999998</v>
+        <v>7325.5742047799995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17343705650576521</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.17795125135209935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5473,7 +5484,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5487,7 +5498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5501,7 +5512,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -5517,7 +5528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5533,11 +5544,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5552,7 +5563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
@@ -5567,7 +5578,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
@@ -5582,7 +5593,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
@@ -5597,7 +5608,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
@@ -5612,11 +5623,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5626,25 +5637,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5653,16 +5664,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5675,20 +5686,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5701,7 +5712,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5714,16 +5725,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5736,16 +5747,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5760,7 +5771,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5775,7 +5786,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5788,12 +5799,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5806,16 +5817,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5828,8 +5839,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5837,7 +5848,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5850,25 +5861,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5881,7 +5892,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5894,23 +5905,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4656356394088135E-2</v>
+        <v>6.5393180968379747E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>0.02</v>
+        <v>2.0227920227920228E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5920,7 +5931,7 @@
         <v>0.3093276688543603</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5931,7 +5942,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5944,7 +5955,7 @@
         <v>0.18518613957341221</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5958,7 +5969,7 @@
         <v>9.3932894828076763E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5972,7 +5983,7 @@
         <v>1.1106245684847842</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5986,7 +5997,7 @@
         <v>1.775102743966247</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -5996,45 +6007,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6048,7 +6059,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6062,7 +6073,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6072,7 +6083,7 @@
         <v>0.17709797868255178</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6082,16 +6093,16 @@
         <v>0.82178780749892033</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6105,7 +6116,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6119,7 +6130,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6133,16 +6144,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6156,7 +6167,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6170,10 +6181,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
@@ -6187,7 +6198,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6197,42 +6208,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6241,7 +6252,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6250,7 +6261,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6259,7 +6270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6268,36 +6279,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
@@ -6310,7 +6321,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
@@ -6323,21 +6334,21 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6354,7 +6365,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (15yrs)</v>
@@ -6376,7 +6387,7 @@
         <v>-7.7511615190408695E-2</v>
       </c>
     </row>
-    <row r="119" spans="2:6">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (15yrs)</v>
@@ -6398,7 +6409,7 @@
         <v>-7.8752060805006227E-3</v>
       </c>
     </row>
-    <row r="120" spans="2:6">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (15yrs)</v>
@@ -6420,7 +6431,7 @@
         <v>2.8313892406829591E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (15yrs)</v>
@@ -6442,7 +6453,7 @@
         <v>6.5359848466424314E-2</v>
       </c>
     </row>
-    <row r="122" spans="2:6">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (15yrs)</v>
@@ -6464,16 +6475,16 @@
         <v>0.10320883220705934</v>
       </c>
     </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6486,7 +6497,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6495,7 +6506,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6505,30 +6516,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6537,7 +6548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6550,14 +6561,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6576,7 +6587,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6597,7 +6608,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6618,14 +6629,14 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6644,7 +6655,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6665,7 +6676,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6686,7 +6697,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6696,21 +6707,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6719,80 +6730,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6832,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6848,15 +6859,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>HKD</v>
@@ -6905,7 +6916,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6921,7 +6932,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6929,7 +6940,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6965,7 +6976,7 @@
       </c>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -7001,7 +7012,7 @@
       </c>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7037,7 +7048,7 @@
       </c>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7073,7 +7084,7 @@
       </c>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7089,7 +7100,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7105,7 +7116,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7121,7 +7132,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7137,7 +7148,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7173,7 +7184,7 @@
       </c>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7189,7 +7200,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7225,7 +7236,7 @@
       </c>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7261,7 +7272,7 @@
       </c>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7297,13 +7308,13 @@
       </c>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7319,7 +7330,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7335,7 +7346,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7351,7 +7362,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7387,7 +7398,7 @@
       </c>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7423,7 +7434,7 @@
       </c>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7459,7 +7470,7 @@
       </c>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7491,7 +7502,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7499,7 +7510,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7536,7 +7547,7 @@
       </c>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7573,7 +7584,7 @@
       </c>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7610,7 +7621,7 @@
       </c>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7647,7 +7658,7 @@
       </c>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7684,7 +7695,7 @@
       </c>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7700,12 +7711,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7754,7 +7765,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7803,7 +7814,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7852,7 +7863,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7901,7 +7912,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7950,7 +7961,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7999,7 +8010,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -8048,7 +8059,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -8097,7 +8108,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -8146,7 +8157,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -8195,7 +8206,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8244,7 +8255,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8293,7 +8304,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8342,12 +8353,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8396,7 +8407,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8445,12 +8456,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8499,7 +8510,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8548,7 +8559,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8597,7 +8608,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8646,13 +8657,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8701,7 +8712,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8750,7 +8761,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8799,7 +8810,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8848,7 +8859,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8897,12 +8908,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8952,7 +8963,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -9001,7 +9012,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -9051,7 +9062,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -9100,7 +9111,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9150,7 +9161,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -9166,13 +9177,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9221,7 +9232,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9255,7 +9266,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9289,7 +9300,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9338,7 +9349,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9419,7 +9430,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9430,7 +9441,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9446,7 +9457,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9457,7 +9468,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9477,7 +9488,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9498,7 +9509,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9519,7 +9530,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9540,7 +9551,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9561,7 +9572,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9582,7 +9593,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9603,7 +9614,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9623,7 +9634,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9635,7 +9646,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9659,12 +9670,12 @@
         <v>1141627.5</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9684,7 +9695,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9704,7 +9715,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9724,7 +9735,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9744,7 +9755,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9764,7 +9775,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9785,7 +9796,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9805,7 +9816,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9825,7 +9836,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9837,7 +9848,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9849,7 +9860,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9873,7 +9884,7 @@
         <v>655.20000000000005</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9890,7 +9901,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9909,7 +9920,7 @@
         <v>-74725.049999999814</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9924,7 +9935,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9943,7 +9954,7 @@
         <v>-173749.04999999981</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9959,7 +9970,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9976,7 +9987,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9996,7 +10007,7 @@
         <v>2391792.9500000002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -10007,7 +10018,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -10020,7 +10031,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -10039,7 +10050,7 @@
         <v>1249510.25</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -10055,7 +10066,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -10071,7 +10082,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -10087,7 +10098,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -10106,7 +10117,7 @@
         <v>277808.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -10126,7 +10137,7 @@
         <v>1142282.7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10146,7 +10157,7 @@
         <v>1142282.7</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -10165,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -10176,7 +10187,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -10190,7 +10201,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -10204,7 +10215,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -10219,10 +10230,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10235,7 +10246,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10249,7 +10260,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10260,10 +10271,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10275,7 +10286,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10289,7 +10300,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10303,10 +10314,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10318,7 +10329,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10329,7 +10340,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10340,10 +10351,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10355,7 +10366,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10371,7 +10382,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10382,7 +10393,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10396,7 +10407,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10412,7 +10423,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10422,7 +10433,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10432,7 +10443,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10442,7 +10453,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10452,10 +10463,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10467,7 +10478,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10483,7 +10494,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10499,7 +10510,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10512,7 +10523,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10525,10 +10536,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10540,7 +10551,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10554,7 +10565,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10568,7 +10579,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10582,7 +10593,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10596,7 +10607,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10607,7 +10618,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10615,7 +10626,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10632,7 +10643,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10649,7 +10660,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10666,7 +10677,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10702,19 +10713,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10771,7 +10782,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10794,7 +10805,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10814,7 +10825,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10871,7 +10882,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10926,7 +10937,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10981,7 +10992,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -11036,7 +11047,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -11093,7 +11104,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -11150,7 +11161,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11205,7 +11216,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11260,7 +11271,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11315,7 +11326,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11372,7 +11383,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11429,7 +11440,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11484,7 +11495,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11539,7 +11550,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11565,7 +11576,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11590,7 +11601,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11647,7 +11658,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11666,7 +11677,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11689,7 +11700,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11710,7 +11721,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11767,7 +11778,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11824,7 +11835,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11881,7 +11892,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11938,18 +11949,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -12005,7 +12016,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -12062,7 +12073,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -12119,7 +12130,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -12174,18 +12185,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12242,18 +12253,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12308,18 +12319,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12378,10 +12389,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12404,14 +12415,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12466,7 +12477,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12521,7 +12532,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12578,7 +12589,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12633,11 +12644,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12647,7 +12658,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12671,7 +12682,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12695,7 +12706,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12750,11 +12761,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12764,7 +12775,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12819,7 +12830,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12874,7 +12885,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12929,7 +12940,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12984,7 +12995,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -13040,7 +13051,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -13095,11 +13106,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -13109,7 +13120,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -13134,7 +13145,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -13159,7 +13170,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -13184,7 +13195,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13211,10 +13222,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13237,7 +13248,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13258,7 +13269,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13315,7 +13326,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13372,7 +13383,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13429,7 +13440,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13486,7 +13497,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13543,7 +13554,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13600,7 +13611,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13657,7 +13668,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13714,7 +13725,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13772,7 +13783,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13829,7 +13840,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13886,7 +13897,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13945,7 +13956,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13971,7 +13982,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13995,7 +14006,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -14052,18 +14063,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -14119,7 +14130,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14175,7 +14186,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14230,7 +14241,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14251,35 +14262,35 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>0.02</v>
+        <v>2.0227920227920228E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>0.02</v>
+        <v>2.0227920227920228E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0845070422535212E-2</v>
+        <v>1.0968660968660969E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.802816901408451E-3</v>
+        <v>3.8461538461538464E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6197183098591547E-2</v>
+        <v>4.672364672364672E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5352112676056336E-2</v>
+        <v>4.5868945868945868E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -14306,11 +14317,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14331,7 +14342,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14388,7 +14399,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14445,10 +14456,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14471,7 +14482,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14481,7 +14492,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14538,7 +14549,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14595,7 +14606,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14652,7 +14663,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14709,7 +14720,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14766,11 +14777,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14793,7 +14804,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14850,7 +14861,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14907,7 +14918,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14934,18 +14945,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14999,7 +15010,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -15054,11 +15065,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -15117,7 +15128,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -15175,7 +15186,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15232,7 +15243,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15291,7 +15302,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15350,7 +15361,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15369,7 +15380,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15392,7 +15403,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15413,7 +15424,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15471,795 +15482,795 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4656356394088135E-2</v>
+        <v>6.5393180968379747E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.8427065958692121E-2</v>
+        <v>6.9206861582153001E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.247226800418308E-2</v>
+        <v>5.3070242568333315E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.4431509450850439E-2</v>
+        <v>3.48238913249342E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7614042235892255E-2</v>
+        <v>2.7928732175902426E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11968986822841655</v>
+        <v>0.12105385533073471</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11715823685008372</v>
+        <v>0.11849337345236388</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14037117891085854</v>
+        <v>0.14197085046539823</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12317776171238935</v>
+        <v>0.12458149688859892</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.9760281506376285E-2</v>
+        <v>9.0783190697332136E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10635078793196001</v>
+        <v>0.10756276272320742</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2469451267408272E-2</v>
+        <v>3.2839473504073895E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5897840635019977E-2</v>
+        <v>1.6079012608068637E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8420622665434143E-3</v>
+        <v>2.8744504405211167E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1781585726221339E-2</v>
+        <v>-2.2029808925380555E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.956586610749275E-2</v>
+        <v>8.0472599624387256E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6877669585540667E-2</v>
+        <v>7.7753768384236283E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1009163578089556</v>
+        <v>0.10206640177259042</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.665813214349298E-2</v>
+        <v>8.7645689204957286E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8175059427231472E-2</v>
+        <v>8.9179903409308189E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6290955206822691E-2</v>
+        <v>7.7160367801772239E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16281,16 +16292,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16305,7 +16316,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16320,7 +16331,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16352,7 +16363,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16380,7 +16391,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16413,7 +16424,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16443,7 +16454,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16478,7 +16489,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*HKD</v>
@@ -16504,7 +16515,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
@@ -16526,7 +16537,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
@@ -16542,7 +16553,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16557,7 +16568,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16575,7 +16586,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16600,7 +16611,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16616,7 +16627,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>552</v>
       </c>
@@ -16635,7 +16646,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16662,10 +16673,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16704,7 +16715,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16753,7 +16764,7 @@
         <v>457315.24497758423</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16802,7 +16813,7 @@
         <v>436573.35158244928</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16859,7 +16870,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16916,7 +16927,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16973,7 +16984,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17022,7 +17033,7 @@
         <v>362596.32457844954</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17071,7 +17082,7 @@
         <v>346150.48247615411</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17120,7 +17131,7 @@
         <v>492602.66371136025</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17169,7 +17180,7 @@
         <v>470260.28162575676</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17218,7 +17229,7 @@
         <v>448931.25589007267</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17267,7 +17278,7 @@
         <v>428569.62492832245</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17316,7 +17327,7 @@
         <v>409131.51178802684</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17373,7 +17384,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17430,7 +17441,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17487,7 +17498,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17536,7 +17547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17585,7 +17596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17634,7 +17645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17683,7 +17694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17732,7 +17743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17781,7 +17792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17830,7 +17841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17879,7 +17890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17928,7 +17939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17977,7 +17988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18026,7 +18037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18083,7 +18094,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18140,7 +18151,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18197,7 +18208,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18254,7 +18265,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18300,7 +18311,7 @@
         <v>5007831.7223625863</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18313,10 +18324,10 @@
         <v>11173811.441417836</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18331,7 +18342,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>11173811.441417836</v>
@@ -18363,7 +18374,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18390,7 +18401,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18416,7 +18427,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18442,7 +18453,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18468,7 +18479,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18494,7 +18505,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18520,7 +18531,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18546,7 +18557,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18572,7 +18583,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18598,7 +18609,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18624,7 +18635,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18659,7 +18670,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18694,7 +18705,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18729,7 +18740,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18764,7 +18775,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18785,7 +18796,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18809,7 +18820,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18837,7 +18848,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18868,7 +18879,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18899,7 +18910,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18930,7 +18941,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18961,7 +18972,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18992,7 +19003,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -19023,7 +19034,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -19054,7 +19065,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -19086,7 +19097,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -19117,7 +19128,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -19149,7 +19160,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -19181,7 +19192,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -19213,7 +19224,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -19245,7 +19256,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19277,7 +19288,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19309,7 +19320,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19332,7 +19343,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19360,7 +19371,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19388,7 +19399,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19416,7 +19427,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19444,7 +19455,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19472,7 +19483,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19485,16 +19496,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19506,7 +19517,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19518,7 +19529,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19530,7 +19541,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19542,7 +19553,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19582,14 +19593,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19599,7 +19610,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19608,7 +19619,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19629,14 +19640,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19649,7 +19660,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19662,7 +19673,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19675,7 +19686,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19688,14 +19699,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19705,7 +19716,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19718,7 +19729,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19731,7 +19742,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19744,7 +19755,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19754,7 +19765,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19762,7 +19773,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19774,18 +19785,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19806,7 +19817,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19830,7 +19841,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19853,7 +19864,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19876,7 +19887,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
@@ -19890,12 +19901,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19916,7 +19927,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19939,7 +19950,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19962,16 +19973,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19991,13 +20002,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.1</v>
+        <v>7.02</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,10 +20019,10 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17343705650576521</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>0.17795125135209935</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
@@ -20031,7 +20042,7 @@
         <v>7.7413410886670489E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
@@ -20050,7 +20061,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -20060,7 +20071,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -20069,7 +20080,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>553</v>
       </c>
@@ -20081,7 +20092,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -20091,7 +20102,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -20101,7 +20112,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -20109,7 +20120,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -20122,7 +20133,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -20134,7 +20145,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -20150,7 +20161,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -20162,7 +20173,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -20172,7 +20183,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -20184,7 +20195,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -20194,7 +20205,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20210,7 +20221,7 @@
         <v>1.9897936077943486E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="13.9">
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20220,12 +20231,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20235,7 +20246,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20248,13 +20259,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20275,7 +20286,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20297,10 +20308,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.5154794527578811</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="13.15">
+        <v>0.51547945275788098</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20325,7 +20336,7 @@
         <v>0.39514217170030708</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="13.15">
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20346,7 +20357,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20371,7 +20382,7 @@
         <v>0.25200367940708179</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="13.15">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20412,7 +20423,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20421,7 +20432,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20435,7 +20446,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20444,7 +20455,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20461,7 +20472,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20477,7 +20488,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20487,7 +20498,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20498,16 +20509,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20516,43 +20527,43 @@
         <v>1043529089</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7409.0565318999998</v>
+        <v>7325.5742047799995</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17343705650576521</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.17795125135209935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20568,7 +20579,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20584,7 +20595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20600,7 +20611,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
@@ -20617,7 +20628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20633,11 +20644,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20653,7 +20664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
@@ -20669,7 +20680,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
@@ -20685,7 +20696,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
@@ -20701,7 +20712,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
@@ -20717,7 +20728,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20727,25 +20738,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20754,7 +20765,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20763,7 +20774,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20776,11 +20787,11 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20789,7 +20800,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20802,7 +20813,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20815,7 +20826,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20824,7 +20835,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20837,7 +20848,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20846,7 +20857,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20861,7 +20872,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20876,7 +20887,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20889,12 +20900,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20907,7 +20918,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20916,7 +20927,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20929,16 +20940,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20951,25 +20962,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20982,7 +20993,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20995,23 +21006,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4656356394088135E-2</v>
+        <v>6.5393180968379747E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>0.02</v>
+        <v>2.0227920227920228E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21021,7 +21032,7 @@
         <v>0.3093276688543603</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -21032,7 +21043,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -21045,7 +21056,7 @@
         <v>0.18518613957341221</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -21059,7 +21070,7 @@
         <v>9.3932894828076763E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -21073,7 +21084,7 @@
         <v>1.1106245684847842</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -21087,7 +21098,7 @@
         <v>1.775102743966247</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -21097,43 +21108,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -21146,7 +21157,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -21159,7 +21170,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -21168,7 +21179,7 @@
         <v>0.17709797868255178</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -21177,12 +21188,12 @@
         <v>0.82178780749892033</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -21195,7 +21206,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21208,7 +21219,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -21221,12 +21232,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21239,7 +21250,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21252,7 +21263,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
@@ -21265,7 +21276,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21275,49 +21286,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21327,7 +21338,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21337,7 +21348,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21347,7 +21358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21356,47 +21367,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
@@ -21410,7 +21421,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
@@ -21424,29 +21435,29 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21464,7 +21475,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21487,7 +21498,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21510,7 +21521,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21532,7 +21543,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21554,7 +21565,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21576,7 +21587,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21585,7 +21596,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21598,16 +21609,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21617,30 +21628,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21649,7 +21660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21662,14 +21673,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21688,7 +21699,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21709,7 +21720,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21730,7 +21741,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21749,7 +21760,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21770,7 +21781,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21791,7 +21802,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21801,50 +21812,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21853,57 +21864,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21932,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D73A41-07E1-454F-BFA5-B14CAD1655C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A0117D-C77A-48F2-971C-572C7459E8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3283,27 +3272,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4055,7 +4044,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4097,17 +4086,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4116,7 +4105,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4190,10 +4179,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4204,7 +4193,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4242,7 +4231,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4252,7 +4241,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4263,19 +4252,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4283,8 +4272,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4307,29 +4296,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4346,15 +4335,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4365,11 +4354,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4430,14 +4419,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4450,7 +4439,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4487,7 +4476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4504,7 +4493,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4550,7 +4539,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4565,13 +4554,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4587,53 +4576,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4650,7 +4639,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4663,21 +4652,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4687,14 +4676,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4703,8 +4692,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4716,7 +4705,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4724,7 +4713,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4763,7 +4752,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4777,39 +4766,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4820,7 +4809,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4831,10 +4820,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4843,7 +4832,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4856,7 +4845,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4865,8 +4854,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4874,10 +4863,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4886,10 +4875,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4906,16 +4895,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4936,7 +4925,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4954,7 +4943,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4964,10 +4953,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4982,7 +4971,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4996,34 +4985,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5033,30 +5022,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5338,7 +5327,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5347,7 +5336,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5360,7 +5349,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5368,7 +5357,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5382,7 +5371,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5396,7 +5385,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5406,7 +5395,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5416,16 +5405,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.02</v>
+        <v>7.12</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5433,43 +5422,43 @@
         <v>1043529089</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7325.5742047799995</v>
+        <v>7429.9271136800007</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17795125135209935</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.17231921120814414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5484,7 +5473,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5498,7 +5487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5512,7 +5501,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -5528,7 +5517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5544,11 +5533,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5563,7 +5552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
@@ -5578,7 +5567,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
@@ -5593,7 +5582,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
@@ -5608,7 +5597,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
@@ -5623,11 +5612,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5637,25 +5626,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5664,16 +5653,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5686,20 +5675,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5712,7 +5701,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5725,16 +5714,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5747,16 +5736,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5771,7 +5760,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5786,7 +5775,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5799,12 +5788,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5817,16 +5806,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5839,8 +5828,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,7 +5837,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5861,25 +5850,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5892,7 +5881,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5905,23 +5894,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.5393180968379747E-2</v>
+        <v>6.4474737415453051E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.0227920227920228E-2</v>
+        <v>1.9943820224719098E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5931,7 +5920,7 @@
         <v>0.3093276688543603</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5942,7 +5931,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5955,7 +5944,7 @@
         <v>0.18518613957341221</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5969,7 +5958,7 @@
         <v>9.3932894828076763E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5983,7 +5972,7 @@
         <v>1.1106245684847842</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5997,7 +5986,7 @@
         <v>1.775102743966247</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6007,45 +5996,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6059,7 +6048,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6073,7 +6062,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6083,7 +6072,7 @@
         <v>0.17709797868255178</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6093,16 +6082,16 @@
         <v>0.82178780749892033</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6116,7 +6105,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6130,7 +6119,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6144,16 +6133,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6167,7 +6156,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6181,10 +6170,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
@@ -6198,7 +6187,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6208,42 +6197,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6252,7 +6241,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6261,7 +6250,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6270,7 +6259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6279,36 +6268,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
@@ -6321,7 +6310,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
@@ -6334,21 +6323,21 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6365,7 +6354,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (15yrs)</v>
@@ -6387,7 +6376,7 @@
         <v>-7.7511615190408695E-2</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (15yrs)</v>
@@ -6409,7 +6398,7 @@
         <v>-7.8752060805006227E-3</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (15yrs)</v>
@@ -6431,7 +6420,7 @@
         <v>2.8313892406829591E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (15yrs)</v>
@@ -6453,7 +6442,7 @@
         <v>6.5359848466424314E-2</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (15yrs)</v>
@@ -6475,16 +6464,16 @@
         <v>0.10320883220705934</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="461" t="s">
+    <row r="124" spans="2:6">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6497,7 +6486,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6506,7 +6495,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6516,30 +6505,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6548,7 +6537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6561,14 +6550,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6587,7 +6576,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6608,7 +6597,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6629,14 +6618,14 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6655,7 +6644,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6676,7 +6665,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6697,7 +6686,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6707,21 +6696,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6730,92 +6719,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6832,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6859,15 +6848,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>HKD</v>
@@ -6916,7 +6905,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6932,7 +6921,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6940,7 +6929,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6976,7 +6965,7 @@
       </c>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -7012,7 +7001,7 @@
       </c>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7048,7 +7037,7 @@
       </c>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7084,7 +7073,7 @@
       </c>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7100,7 +7089,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7116,7 +7105,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7132,7 +7121,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7148,7 +7137,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7184,7 +7173,7 @@
       </c>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7200,7 +7189,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7236,7 +7225,7 @@
       </c>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7272,7 +7261,7 @@
       </c>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7308,13 +7297,13 @@
       </c>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7330,7 +7319,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7346,7 +7335,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7362,7 +7351,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7398,7 +7387,7 @@
       </c>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7434,7 +7423,7 @@
       </c>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7470,7 +7459,7 @@
       </c>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7502,7 +7491,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7510,7 +7499,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7547,7 +7536,7 @@
       </c>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7584,7 +7573,7 @@
       </c>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7621,7 +7610,7 @@
       </c>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7658,7 +7647,7 @@
       </c>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7695,7 +7684,7 @@
       </c>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7711,12 +7700,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7765,7 +7754,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7814,7 +7803,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7863,7 +7852,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7912,7 +7901,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7961,7 +7950,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -8010,7 +7999,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -8059,7 +8048,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -8108,7 +8097,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -8157,7 +8146,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -8206,7 +8195,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8255,7 +8244,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8304,7 +8293,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8353,12 +8342,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8407,7 +8396,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8456,12 +8445,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8510,7 +8499,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8559,7 +8548,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8608,7 +8597,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8657,13 +8646,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8712,7 +8701,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8761,7 +8750,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8810,7 +8799,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8859,7 +8848,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8908,12 +8897,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8963,7 +8952,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -9012,7 +9001,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -9062,7 +9051,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -9111,7 +9100,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -9161,7 +9150,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -9177,13 +9166,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -9232,7 +9221,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9266,7 +9255,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9300,7 +9289,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9349,7 +9338,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9430,7 +9419,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9441,7 +9430,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9457,7 +9446,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9468,7 +9457,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9488,7 +9477,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9509,7 +9498,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9530,7 +9519,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9551,7 +9540,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9572,7 +9561,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9593,7 +9582,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9614,7 +9603,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9634,7 +9623,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9646,7 +9635,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9670,12 +9659,12 @@
         <v>1141627.5</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9695,7 +9684,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9715,7 +9704,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9735,7 +9724,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9755,7 +9744,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9775,7 +9764,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9796,7 +9785,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9816,7 +9805,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9836,7 +9825,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9848,7 +9837,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9860,7 +9849,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9884,7 +9873,7 @@
         <v>655.20000000000005</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9901,7 +9890,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9920,7 +9909,7 @@
         <v>-74725.049999999814</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9935,7 +9924,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9954,7 +9943,7 @@
         <v>-173749.04999999981</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9970,7 +9959,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9987,7 +9976,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -10007,7 +9996,7 @@
         <v>2391792.9500000002</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -10018,7 +10007,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -10031,7 +10020,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -10050,7 +10039,7 @@
         <v>1249510.25</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -10066,7 +10055,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -10082,7 +10071,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -10098,7 +10087,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -10117,7 +10106,7 @@
         <v>277808.2</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -10137,7 +10126,7 @@
         <v>1142282.7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -10157,7 +10146,7 @@
         <v>1142282.7</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -10176,7 +10165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -10187,7 +10176,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -10201,7 +10190,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -10215,7 +10204,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -10230,10 +10219,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -10246,7 +10235,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10260,7 +10249,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10271,10 +10260,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10286,7 +10275,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10300,7 +10289,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10314,10 +10303,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10329,7 +10318,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10340,7 +10329,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10351,10 +10340,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10366,7 +10355,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10382,7 +10371,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10393,7 +10382,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10407,7 +10396,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10423,7 +10412,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10433,7 +10422,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10443,7 +10432,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10453,7 +10442,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10463,10 +10452,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10478,7 +10467,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10494,7 +10483,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10510,7 +10499,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10523,7 +10512,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10536,10 +10525,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10551,7 +10540,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10565,7 +10554,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10579,7 +10568,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10593,7 +10582,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10607,7 +10596,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10618,7 +10607,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10626,7 +10615,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10643,7 +10632,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10660,7 +10649,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10677,7 +10666,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10713,19 +10702,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10782,7 +10771,7 @@
         <v>42094</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10805,7 +10794,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10825,7 +10814,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10882,7 +10871,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10937,7 +10926,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10992,7 +10981,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -11047,7 +11036,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -11104,7 +11093,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -11161,7 +11150,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -11216,7 +11205,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11271,7 +11260,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11326,7 +11315,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11383,7 +11372,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11440,7 +11429,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11495,7 +11484,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11550,7 +11539,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11576,7 +11565,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11601,7 +11590,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11658,7 +11647,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11677,7 +11666,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11700,7 +11689,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11721,7 +11710,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11778,7 +11767,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11835,7 +11824,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11892,7 +11881,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11949,18 +11938,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -12016,7 +12005,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -12073,7 +12062,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -12130,7 +12119,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -12185,18 +12174,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -12253,18 +12242,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12319,18 +12308,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12389,10 +12378,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12415,14 +12404,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12477,7 +12466,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12532,7 +12521,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12589,7 +12578,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12644,11 +12633,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12658,7 +12647,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12682,7 +12671,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12706,7 +12695,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12761,11 +12750,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12775,7 +12764,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12830,7 +12819,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12885,7 +12874,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12940,7 +12929,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12995,7 +12984,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -13051,7 +13040,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -13106,11 +13095,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -13120,7 +13109,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -13145,7 +13134,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -13170,7 +13159,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -13195,7 +13184,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -13222,10 +13211,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -13248,7 +13237,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13269,7 +13258,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13326,7 +13315,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13383,7 +13372,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13440,7 +13429,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13497,7 +13486,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13554,7 +13543,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13611,7 +13600,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13668,7 +13657,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13725,7 +13714,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13783,7 +13772,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13840,7 +13829,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13897,7 +13886,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13956,7 +13945,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13982,7 +13971,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -14006,7 +13995,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -14063,18 +14052,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -14130,7 +14119,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -14186,7 +14175,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -14241,7 +14230,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14262,35 +14251,35 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0227920227920228E-2</v>
+        <v>1.9943820224719098E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0227920227920228E-2</v>
+        <v>1.9943820224719098E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0968660968660969E-2</v>
+        <v>1.0814606741573033E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.8461538461538464E-3</v>
+        <v>3.7921348314606741E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.672364672364672E-2</v>
+        <v>4.6067415730337069E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5868945868945868E-2</v>
+        <v>4.5224719101123585E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -14317,11 +14306,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14342,7 +14331,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14399,7 +14388,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14456,10 +14445,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14482,7 +14471,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14492,7 +14481,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14549,7 +14538,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14606,7 +14595,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14663,7 +14652,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14720,7 +14709,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14777,11 +14766,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14804,7 +14793,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14861,7 +14850,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14918,7 +14907,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14945,18 +14934,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -15010,7 +14999,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -15065,11 +15054,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -15128,7 +15117,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -15186,7 +15175,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -15243,7 +15232,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15302,7 +15291,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15361,7 +15350,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15380,7 +15369,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15403,7 +15392,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15424,7 +15413,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15482,795 +15471,795 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5393180968379747E-2</v>
+        <v>6.4474737415453051E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9206861582153001E-2</v>
+        <v>6.8234855099257585E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3070242568333315E-2</v>
+        <v>5.2324873992935367E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.48238913249342E-2</v>
+        <v>3.433479172767389E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.7928732175902426E-2</v>
+        <v>2.753647470152177E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12105385533073471</v>
+        <v>0.11935366073339292</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11849337345236388</v>
+        <v>0.11682914067915651</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14197085046539823</v>
+        <v>0.13997687784650217</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12458149688859892</v>
+        <v>0.12283175676375903</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.0783190697332136E-2</v>
+        <v>8.9508145884167362E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10756276272320742</v>
+        <v>0.10605204976361181</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2839473504073895E-2</v>
+        <v>3.2378244943623416E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6079012608068637E-2</v>
+        <v>1.5853183779303628E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8744504405211167E-3</v>
+        <v>2.8340789455699772E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2029808925380555E-2</v>
+        <v>-2.1720401496653299E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0472599624387256E-2</v>
+        <v>7.93423664835953E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7753768384236283E-2</v>
+        <v>7.6661721075468911E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10206640177259042</v>
+        <v>0.10063288489376189</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7645689204957286E-2</v>
+        <v>8.641471042398878E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9179903409308189E-2</v>
+        <v>8.7927376676031385E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7160367801772239E-2</v>
+        <v>7.6076654770848476E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16292,16 +16281,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16316,7 +16305,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16331,7 +16320,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16363,7 +16352,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16391,7 +16380,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16424,7 +16413,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16454,7 +16443,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16489,7 +16478,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*HKD</v>
@@ -16515,7 +16504,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
@@ -16537,7 +16526,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
@@ -16553,7 +16542,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16568,7 +16557,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16586,7 +16575,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16611,7 +16600,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16627,7 +16616,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>552</v>
       </c>
@@ -16646,7 +16635,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16673,10 +16662,10 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16715,7 +16704,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16764,7 +16753,7 @@
         <v>457315.24497758423</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16813,7 +16802,7 @@
         <v>436573.35158244928</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16870,7 +16859,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16927,7 +16916,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16984,7 +16973,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17033,7 +17022,7 @@
         <v>362596.32457844954</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17082,7 +17071,7 @@
         <v>346150.48247615411</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17131,7 +17120,7 @@
         <v>492602.66371136025</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17180,7 +17169,7 @@
         <v>470260.28162575676</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17229,7 +17218,7 @@
         <v>448931.25589007267</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17278,7 +17267,7 @@
         <v>428569.62492832245</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17327,7 +17316,7 @@
         <v>409131.51178802684</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17384,7 +17373,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17441,7 +17430,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -17498,7 +17487,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17547,7 +17536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17596,7 +17585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17645,7 +17634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17694,7 +17683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17743,7 +17732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17792,7 +17781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17841,7 +17830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17890,7 +17879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17939,7 +17928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17988,7 +17977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18037,7 +18026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18094,7 +18083,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18151,7 +18140,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18208,7 +18197,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18265,7 +18254,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18311,7 +18300,7 @@
         <v>5007831.7223625863</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18324,10 +18313,10 @@
         <v>11173811.441417836</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18342,7 +18331,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>11173811.441417836</v>
@@ -18374,7 +18363,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18401,7 +18390,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18427,7 +18416,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18453,7 +18442,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18479,7 +18468,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18505,7 +18494,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18531,7 +18520,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18557,7 +18546,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18583,7 +18572,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18609,7 +18598,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18635,7 +18624,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18670,7 +18659,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18705,7 +18694,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18740,7 +18729,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18775,7 +18764,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18796,7 +18785,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18820,7 +18809,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18848,7 +18837,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18879,7 +18868,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18910,7 +18899,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18941,7 +18930,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18972,7 +18961,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -19003,7 +18992,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -19034,7 +19023,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -19065,7 +19054,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -19097,7 +19086,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -19128,7 +19117,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -19160,7 +19149,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -19192,7 +19181,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -19224,7 +19213,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -19256,7 +19245,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19288,7 +19277,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19320,7 +19309,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19343,7 +19332,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19371,7 +19360,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19399,7 +19388,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19427,7 +19416,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19455,7 +19444,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19483,7 +19472,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19496,16 +19485,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19517,7 +19506,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19529,7 +19518,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19541,7 +19530,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19553,7 +19542,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19593,14 +19582,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19610,7 +19599,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19619,7 +19608,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19640,14 +19629,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19660,7 +19649,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19673,7 +19662,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19686,7 +19675,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19699,14 +19688,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19716,7 +19705,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19729,7 +19718,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19742,7 +19731,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19755,7 +19744,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19765,7 +19754,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19773,7 +19762,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19785,18 +19774,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19817,7 +19806,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19841,7 +19830,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19864,7 +19853,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19887,7 +19876,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
@@ -19901,12 +19890,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19927,7 +19916,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19950,7 +19939,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19973,16 +19962,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -20002,13 +19991,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.02</v>
+        <v>7.12</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20019,10 +20008,10 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17795125135209935</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.17231921120814414</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
@@ -20042,7 +20031,7 @@
         <v>7.7413410886670489E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
@@ -20061,7 +20050,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -20071,7 +20060,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -20080,7 +20069,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>553</v>
       </c>
@@ -20092,7 +20081,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -20102,7 +20091,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -20112,7 +20101,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -20120,7 +20109,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -20133,7 +20122,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -20145,7 +20134,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -20161,7 +20150,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -20173,7 +20162,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -20183,7 +20172,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -20195,7 +20184,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -20205,7 +20194,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -20221,7 +20210,7 @@
         <v>1.9897936077943486E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -20231,12 +20220,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -20246,7 +20235,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20259,13 +20248,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20286,7 +20275,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20308,10 +20297,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.51547945275788098</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.5154794527578811</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20336,7 +20325,7 @@
         <v>0.39514217170030708</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20357,7 +20346,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20382,7 +20371,7 @@
         <v>0.25200367940708179</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20423,7 +20412,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20432,7 +20421,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20446,7 +20435,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20455,7 +20444,7 @@
         <v>46038</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20472,7 +20461,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20488,7 +20477,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20498,7 +20487,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20509,16 +20498,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.02</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>7.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20527,43 +20516,43 @@
         <v>1043529089</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7325.5742047799995</v>
+        <v>7429.9271136800007</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17795125135209935</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.17231921120814414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20579,7 +20568,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20595,7 +20584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20611,7 +20600,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
@@ -20628,7 +20617,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20644,11 +20633,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20664,7 +20653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
@@ -20680,7 +20669,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
@@ -20696,7 +20685,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
@@ -20712,7 +20701,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
@@ -20728,7 +20717,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20738,25 +20727,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20765,7 +20754,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20774,7 +20763,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20787,11 +20776,11 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20800,7 +20789,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20813,7 +20802,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20826,7 +20815,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20835,7 +20824,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20848,7 +20837,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20857,7 +20846,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20872,7 +20861,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20887,7 +20876,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20900,12 +20889,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20918,7 +20907,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20927,7 +20916,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20940,16 +20929,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20962,25 +20951,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20993,7 +20982,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -21006,23 +20995,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.5393180968379747E-2</v>
+        <v>6.4474737415453051E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.0227920227920228E-2</v>
+        <v>1.9943820224719098E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21032,7 +21021,7 @@
         <v>0.3093276688543603</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -21043,7 +21032,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -21056,7 +21045,7 @@
         <v>0.18518613957341221</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -21070,7 +21059,7 @@
         <v>9.3932894828076763E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -21084,7 +21073,7 @@
         <v>1.1106245684847842</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -21098,7 +21087,7 @@
         <v>1.775102743966247</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -21108,43 +21097,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -21157,7 +21146,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -21170,7 +21159,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -21179,7 +21168,7 @@
         <v>0.17709797868255178</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -21188,12 +21177,12 @@
         <v>0.82178780749892033</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -21206,7 +21195,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -21219,7 +21208,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -21232,12 +21221,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21250,7 +21239,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21263,7 +21252,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
@@ -21276,7 +21265,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21286,49 +21275,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21338,7 +21327,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21348,7 +21337,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21358,7 +21347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21367,47 +21356,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
@@ -21421,7 +21410,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
@@ -21435,29 +21424,29 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21475,7 +21464,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21498,7 +21487,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21521,7 +21510,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21543,7 +21532,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21565,7 +21554,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21587,7 +21576,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21596,7 +21585,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21609,16 +21598,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21628,30 +21617,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21660,7 +21649,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21673,14 +21662,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21699,7 +21688,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21720,7 +21709,7 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21741,7 +21730,7 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21760,7 +21749,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21781,7 +21770,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21802,7 +21791,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21812,50 +21801,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21864,60 +21853,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21932,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A0117D-C77A-48F2-971C-572C7459E8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292ECE92-3325-4903-B7E6-C49E46294902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>7.12</v>
+        <v>6.98</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7429.9271136800007</v>
+        <v>7283.8330412200003</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.17231921120814414</v>
+        <v>0.18023444042885403</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.4474737415453051E-2</v>
+        <v>6.5767926991121162E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>1.9943820224719098E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>1.9943820224719098E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>1.9943820224719098E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.0814606741573033E-2</v>
+        <v>1.1031518624641834E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.7921348314606741E-3</v>
+        <v>3.8681948424068766E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6067415730337069E-2</v>
+        <v>4.6991404011461312E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.5224719101123585E-2</v>
+        <v>4.6131805157593117E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4474737415453051E-2</v>
+        <v>6.5767926991121162E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.8234855099257585E-2</v>
+        <v>6.9603462508125213E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.2324873992935367E-2</v>
+        <v>5.3374370032908285E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.433479172767389E-2</v>
+        <v>3.5023455172068493E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.753647470152177E-2</v>
+        <v>2.8088782217025071E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.11935366073339292</v>
+        <v>0.12174757369939219</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11682914067915651</v>
+        <v>0.11917241857243471</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.13997687784650217</v>
+        <v>0.14278443700101656</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12283175676375903</v>
+        <v>0.12529543096818971</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>8.9508145884167362E-2</v>
+        <v>9.1303438208491627E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10605204976361181</v>
+        <v>0.10817916824024584</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2378244943623416E-2</v>
+        <v>3.3027665329312138E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5853183779303628E-2</v>
+        <v>1.6171155946796825E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8340789455699772E-3</v>
+        <v>2.890922935882269E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.1720401496653299E-2</v>
+        <v>-2.2156054248735169E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.93423664835953E-2</v>
+        <v>8.0933760653753364E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6661721075468911E-2</v>
+        <v>7.8199348718816425E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10063288489376189</v>
+        <v>0.1026513095191382</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.641471042398878E-2</v>
+        <v>8.8147956764871083E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7927376676031385E-2</v>
+        <v>8.9690963027699633E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6076654770848476E-2</v>
+        <v>7.7602547559948581E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>7.12</v>
+        <v>6.98</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.17231921120814414</v>
+        <v>0.18023444042885403</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>7.12</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7429.9271136800007</v>
+        <v>7283.8330412200003</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.17231921120814414</v>
+        <v>0.18023444042885403</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.4474737415453051E-2</v>
+        <v>6.5767926991121162E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>1.9943820224719098E-2</v>
+        <v>2.0343839541547275E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292ECE92-3325-4903-B7E6-C49E46294902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7AC905-0ECA-4924-805A-CC65F29D9023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.98</v>
+        <v>6.62</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7283.8330412200003</v>
+        <v>6908.16256918</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.18023444042885403</v>
+        <v>0.2016100017554775</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.5767926991121162E-2</v>
+        <v>6.9344430573719903E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.0343839541547275E-2</v>
+        <v>2.145015105740181E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.0343839541547275E-2</v>
+        <v>2.145015105740181E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.0343839541547275E-2</v>
+        <v>2.145015105740181E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1031518624641834E-2</v>
+        <v>1.1631419939577038E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.8681948424068766E-3</v>
+        <v>4.0785498489425984E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6991404011461312E-2</v>
+        <v>4.9546827794561925E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.6131805157593117E-2</v>
+        <v>4.864048338368579E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5767926991121162E-2</v>
+        <v>6.9344430573719903E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.9603462508125213E-2</v>
+        <v>7.338854506143716E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.3374370032908285E-2</v>
+        <v>5.6276903750709942E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.5023455172068493E-2</v>
+        <v>3.6928053942755001E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.8088782217025071E-2</v>
+        <v>2.9616268863268128E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12174757369939219</v>
+        <v>0.12836828767700265</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.11917241857243471</v>
+        <v>0.12565309390265775</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14278443700101656</v>
+        <v>0.15054914958717455</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.12529543096818971</v>
+        <v>0.13210907978216985</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.1303438208491627E-2</v>
+        <v>9.6268579863334078E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.10817916824024584</v>
+        <v>0.1140620233107124</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3027665329312138E-2</v>
+        <v>3.4823731721842707E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6171155946796825E-2</v>
+        <v>1.7050554155383962E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.890922935882269E-3</v>
+        <v>3.0481332465949001E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2156054248735169E-2</v>
+        <v>-2.336091520485974E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0933760653753364E-2</v>
+        <v>8.5334992350936334E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8199348718816425E-2</v>
+        <v>8.2451881277543604E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1026513095191382</v>
+        <v>0.10823355595824542</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8147956764871083E-2</v>
+        <v>9.2941501241510599E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9690963027699633E-2</v>
+        <v>9.4568417210474834E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7602547559948581E-2</v>
+        <v>8.1822625674991101E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.98</v>
+        <v>6.62</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.18023444042885403</v>
+        <v>0.2016100017554775</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.98</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7283.8330412200003</v>
+        <v>6908.16256918</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.18023444042885403</v>
+        <v>0.2016100017554775</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.5767926991121162E-2</v>
+        <v>6.9344430573719903E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.0343839541547275E-2</v>
+        <v>2.145015105740181E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7AC905-0ECA-4924-805A-CC65F29D9023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227939BC-730F-42AB-859E-B43D39762453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,39 +4989,48 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.62</v>
+        <v>6.76</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6908.16256918</v>
+        <v>7054.2566416399995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2016100017554775</v>
+        <v>0.19311510168342902</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,13 +5829,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="464"/>
-      <c r="D54" s="464"/>
-      <c r="E54" s="464"/>
-      <c r="F54" s="464"/>
+      <c r="C54" s="465"/>
+      <c r="D54" s="465"/>
+      <c r="E54" s="465"/>
+      <c r="F54" s="465"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9344430573719903E-2</v>
+        <v>6.7908303313317431E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.145015105740181E-2</v>
+        <v>2.1005917159763313E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6487,13 +6487,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="465" t="s">
+      <c r="B127" s="466" t="s">
         <v>358</v>
       </c>
-      <c r="C127" s="465"/>
-      <c r="D127" s="465"/>
-      <c r="E127" s="465"/>
-      <c r="F127" s="465"/>
+      <c r="C127" s="466"/>
+      <c r="D127" s="466"/>
+      <c r="E127" s="466"/>
+      <c r="F127" s="466"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6711,13 +6711,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="464" t="s">
+      <c r="B152" s="465" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="464"/>
-      <c r="D152" s="464"/>
-      <c r="E152" s="464"/>
-      <c r="F152" s="464"/>
+      <c r="C152" s="465"/>
+      <c r="D152" s="465"/>
+      <c r="E152" s="465"/>
+      <c r="F152" s="465"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.145015105740181E-2</v>
+        <v>2.1005917159763313E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.145015105740181E-2</v>
+        <v>2.1005917159763313E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1631419939577038E-2</v>
+        <v>1.1390532544378698E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.0785498489425984E-3</v>
+        <v>3.9940828402366861E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9546827794561925E-2</v>
+        <v>4.8520710059171593E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.864048338368579E-2</v>
+        <v>4.7633136094674552E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9344430573719903E-2</v>
+        <v>6.7908303313317431E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.338854506143716E-2</v>
+        <v>7.1868663950697353E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.6276903750709942E-2</v>
+        <v>5.5111405744038437E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.6928053942755001E-2</v>
+        <v>3.6163271760508597E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9616268863268128E-2</v>
+        <v>2.9002914182667903E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12836828767700265</v>
+        <v>0.12570977284345525</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12565309390265775</v>
+        <v>0.12305081089283941</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15054914958717455</v>
+        <v>0.14743126779099047</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13210907978216985</v>
+        <v>0.1293730929227758</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.6268579863334078E-2</v>
+        <v>9.4274851877998764E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.1140620233107124</v>
+        <v>0.1116997920587154</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4823731721842707E-2</v>
+        <v>3.4102530177307508E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7050554155383962E-2</v>
+        <v>1.6697436169917434E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.0481332465949001E-3</v>
+        <v>2.9850062266950062E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.336091520485974E-2</v>
+        <v>-2.2877109268664424E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5334992350936334E-2</v>
+        <v>8.3567699609940621E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2451881277543604E-2</v>
+        <v>8.0744297937476145E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10823355595824542</v>
+        <v>0.10599203260999775</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2941501241510599E-2</v>
+        <v>9.1016677251301803E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4568417210474834E-2</v>
+        <v>9.2609899694281586E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1822625674991101E-2</v>
+        <v>8.0128074255686563E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18304,10 +18304,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="468" t="s">
+      <c r="J52" s="460" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="468"/>
+      <c r="K52" s="460"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>11173811.441417836</v>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.62</v>
+        <v>6.76</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2016100017554775</v>
+        <v>0.19311510168342902</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.62</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6908.16256918</v>
+        <v>7054.2566416399995</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2016100017554775</v>
+        <v>0.19311510168342902</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9344430573719903E-2</v>
+        <v>6.7908303313317431E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.145015105740181E-2</v>
+        <v>2.1005917159763313E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227939BC-730F-42AB-859E-B43D39762453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF598A-2220-4EA7-AAE4-D1BA8AC2ABD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,55 +4992,55 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.76</v>
+        <v>6.42</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>7054.2566416399995</v>
+        <v>6699.4567513800002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.19311510168342902</v>
+        <v>0.2141750898751657</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="463"/>
+      <c r="D12" s="463"/>
+      <c r="E12" s="463"/>
+      <c r="F12" s="463"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="463"/>
+      <c r="D29" s="463"/>
+      <c r="E29" s="463"/>
+      <c r="F29" s="463"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="467"/>
+      <c r="D30" s="467"/>
+      <c r="E30" s="467"/>
+      <c r="F30" s="467"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="464" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="464"/>
+      <c r="D33" s="464"/>
+      <c r="E33" s="464"/>
+      <c r="F33" s="464"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="464" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="464"/>
+      <c r="D36" s="464"/>
+      <c r="E36" s="464"/>
+      <c r="F36" s="464"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="464" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="464"/>
+      <c r="D40" s="464"/>
+      <c r="E40" s="464"/>
+      <c r="F40" s="464"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="464" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="464"/>
+      <c r="D43" s="464"/>
+      <c r="E43" s="464"/>
+      <c r="F43" s="464"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="464" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="464"/>
+      <c r="D51" s="464"/>
+      <c r="E51" s="464"/>
+      <c r="F51" s="464"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="464" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="463" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="463"/>
+      <c r="D57" s="463"/>
+      <c r="E57" s="463"/>
+      <c r="F57" s="463"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="463" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="463"/>
+      <c r="D58" s="463"/>
+      <c r="E58" s="463"/>
+      <c r="F58" s="463"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7908303313317431E-2</v>
+        <v>7.1504693208415224E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.1005917159763313E-2</v>
+        <v>2.2118380062305293E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="463" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="463"/>
+      <c r="D73" s="463"/>
+      <c r="E73" s="463"/>
+      <c r="F73" s="463"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="463" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="463"/>
+      <c r="D77" s="463"/>
+      <c r="E77" s="463"/>
+      <c r="F77" s="463"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="463" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="463"/>
+      <c r="D96" s="463"/>
+      <c r="E96" s="463"/>
+      <c r="F96" s="463"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="467" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="467"/>
+      <c r="D97" s="467"/>
+      <c r="E97" s="467"/>
+      <c r="F97" s="467"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="467" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="467"/>
+      <c r="D98" s="467"/>
+      <c r="E98" s="467"/>
+      <c r="F98" s="467"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="463" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="463"/>
+      <c r="D107" s="463"/>
+      <c r="E107" s="463"/>
+      <c r="F107" s="463"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="463"/>
+      <c r="D108" s="463"/>
+      <c r="E108" s="463"/>
+      <c r="F108" s="463"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="463" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="463"/>
+      <c r="D114" s="463"/>
+      <c r="E114" s="463"/>
+      <c r="F114" s="463"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="464" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="464"/>
+      <c r="D124" s="464"/>
+      <c r="E124" s="464"/>
+      <c r="F124" s="464"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="468" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="468"/>
+      <c r="D131" s="468"/>
+      <c r="E131" s="468"/>
+      <c r="F131" s="468"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="463" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="463"/>
+      <c r="D132" s="463"/>
+      <c r="E132" s="463"/>
+      <c r="F132" s="463"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="462" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="463"/>
+      <c r="D149" s="463"/>
+      <c r="E149" s="463"/>
+      <c r="F149" s="463"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="464" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="464"/>
+      <c r="D158" s="464"/>
+      <c r="E158" s="464"/>
+      <c r="F158" s="464"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="461" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="461"/>
+      <c r="D161" s="461"/>
+      <c r="E161" s="461"/>
+      <c r="F161" s="461"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="461" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="461"/>
+      <c r="D162" s="461"/>
+      <c r="E162" s="461"/>
+      <c r="F162" s="461"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1005917159763313E-2</v>
+        <v>2.2118380062305293E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1005917159763313E-2</v>
+        <v>2.2118380062305293E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1390532544378698E-2</v>
+        <v>1.1993769470404984E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>3.9940828402366861E-3</v>
+        <v>4.2056074766355141E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>4.8520710059171593E-2</v>
+        <v>5.1090342679127723E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.7633136094674552E-2</v>
+        <v>5.0155763239875382E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7908303313317431E-2</v>
+        <v>7.1504693208415224E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1868663950697353E-2</v>
+        <v>7.5674792571139265E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5111405744038437E-2</v>
+        <v>5.8030078322383154E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.6163271760508597E-2</v>
+        <v>3.807846060763833E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>2.9002914182667903E-2</v>
+        <v>3.0538894061500781E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.12570977284345525</v>
+        <v>0.13236729975416783</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12305081089283941</v>
+        <v>0.12956752050398668</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.14743126779099047</v>
+        <v>0.15523915424721116</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.1293730929227758</v>
+        <v>0.13622462743893526</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.4274851877998764E-2</v>
+        <v>9.9267601042877199E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.1116997920587154</v>
+        <v>0.11761535737023615</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4102530177307508E-2</v>
+        <v>3.5908583177351829E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6697436169917434E-2</v>
+        <v>1.7581724066766641E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9850062266950062E-3</v>
+        <v>3.1430906686072024E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.2877109268664424E-2</v>
+        <v>-2.4088669572612381E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3567699609940621E-2</v>
+        <v>8.7993403327601014E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0744297937476145E-2</v>
+        <v>8.5020475709865845E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10599203260999775</v>
+        <v>0.11160531782610353</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1016677251301803E-2</v>
+        <v>9.5836875111962636E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2609899694281586E-2</v>
+        <v>9.7514473821393055E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0128074255686563E-2</v>
+        <v>8.4371617129040677E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.76</v>
+        <v>6.42</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.19311510168342902</v>
+        <v>0.2141750898751657</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.76</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>7054.2566416399995</v>
+        <v>6699.4567513800002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.19311510168342902</v>
+        <v>0.2141750898751657</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7908303313317431E-2</v>
+        <v>7.1504693208415224E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.1005917159763313E-2</v>
+        <v>2.2118380062305293E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAF598A-2220-4EA7-AAE4-D1BA8AC2ABD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19EF68D-968A-40FA-898C-2AA65113CF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,36 +4992,45 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5419,7 +5419,7 @@
         <v>346</v>
       </c>
       <c r="C9" s="48">
-        <v>1043529089</v>
+        <v>1016799089</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6699.4567513800002</v>
+        <v>6527.8501513800002</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.2141750898751657</v>
+        <v>0.22442988622852325</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="463" t="s">
+      <c r="B12" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="463"/>
-      <c r="D12" s="463"/>
-      <c r="E12" s="463"/>
-      <c r="F12" s="463"/>
+      <c r="C12" s="461"/>
+      <c r="D12" s="461"/>
+      <c r="E12" s="461"/>
+      <c r="F12" s="461"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>10.967807599967429</v>
+        <v>11.25643603289171</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>5.3141281403824898</v>
+        <v>5.4471366348176424</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>6.6339642861251669</v>
+        <v>6.8006810704857621</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>8.2038797297466814</v>
+        <v>8.410757158764735</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>9.2614927891107719</v>
+        <v>9.4954558038529377</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="463" t="s">
+      <c r="B29" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="463"/>
-      <c r="D29" s="463"/>
-      <c r="E29" s="463"/>
-      <c r="F29" s="463"/>
+      <c r="C29" s="461"/>
+      <c r="D29" s="461"/>
+      <c r="E29" s="461"/>
+      <c r="F29" s="461"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="467" t="s">
+      <c r="B30" s="463" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="467"/>
-      <c r="D30" s="467"/>
-      <c r="E30" s="467"/>
-      <c r="F30" s="467"/>
+      <c r="C30" s="463"/>
+      <c r="D30" s="463"/>
+      <c r="E30" s="463"/>
+      <c r="F30" s="463"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="464" t="s">
+      <c r="B33" s="462" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="464"/>
-      <c r="D33" s="464"/>
-      <c r="E33" s="464"/>
-      <c r="F33" s="464"/>
+      <c r="C33" s="462"/>
+      <c r="D33" s="462"/>
+      <c r="E33" s="462"/>
+      <c r="F33" s="462"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="464" t="s">
+      <c r="B36" s="462" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="464"/>
-      <c r="D36" s="464"/>
-      <c r="E36" s="464"/>
-      <c r="F36" s="464"/>
+      <c r="C36" s="462"/>
+      <c r="D36" s="462"/>
+      <c r="E36" s="462"/>
+      <c r="F36" s="462"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="464" t="s">
+      <c r="B40" s="462" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="464"/>
-      <c r="D40" s="464"/>
-      <c r="E40" s="464"/>
-      <c r="F40" s="464"/>
+      <c r="C40" s="462"/>
+      <c r="D40" s="462"/>
+      <c r="E40" s="462"/>
+      <c r="F40" s="462"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="464" t="s">
+      <c r="B43" s="462" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="464"/>
-      <c r="D43" s="464"/>
-      <c r="E43" s="464"/>
-      <c r="F43" s="464"/>
+      <c r="C43" s="462"/>
+      <c r="D43" s="462"/>
+      <c r="E43" s="462"/>
+      <c r="F43" s="462"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
-        <v>2867.9977153189998</v>
+        <v>2866.0998853190004</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
-        <v>-30945.482284680995</v>
+        <v>-30947.380114680996</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="464" t="s">
+      <c r="B51" s="462" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="464"/>
-      <c r="D51" s="464"/>
-      <c r="E51" s="464"/>
-      <c r="F51" s="464"/>
+      <c r="C51" s="462"/>
+      <c r="D51" s="462"/>
+      <c r="E51" s="462"/>
+      <c r="F51" s="462"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
-        <v>-141442.24702650897</v>
+        <v>-141441.83709522896</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="464" t="s">
+      <c r="B54" s="462" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="465"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+      <c r="B57" s="461" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="463"/>
-      <c r="D57" s="463"/>
-      <c r="E57" s="463"/>
-      <c r="F57" s="463"/>
+      <c r="C57" s="461"/>
+      <c r="D57" s="461"/>
+      <c r="E57" s="461"/>
+      <c r="F57" s="461"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+      <c r="B58" s="461" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="463"/>
-      <c r="D58" s="463"/>
-      <c r="E58" s="463"/>
-      <c r="F58" s="463"/>
+      <c r="C58" s="461"/>
+      <c r="D58" s="461"/>
+      <c r="E58" s="461"/>
+      <c r="F58" s="461"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
-        <v>479042.59967047302</v>
+        <v>479041.111771753</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.1504693208415224E-2</v>
+        <v>7.3384207765627527E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
-        <v>0.3093276688543603</v>
+        <v>0.30140517606930323</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="463" t="s">
+      <c r="B73" s="461" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="463"/>
-      <c r="D73" s="463"/>
-      <c r="E73" s="463"/>
-      <c r="F73" s="463"/>
+      <c r="C73" s="461"/>
+      <c r="D73" s="461"/>
+      <c r="E73" s="461"/>
+      <c r="F73" s="461"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="463" t="s">
+      <c r="B77" s="461" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="463"/>
-      <c r="D77" s="463"/>
-      <c r="E77" s="463"/>
-      <c r="F77" s="463"/>
+      <c r="C77" s="461"/>
+      <c r="D77" s="461"/>
+      <c r="E77" s="461"/>
+      <c r="F77" s="461"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.54005011066826136</v>
+        <v>-0.55424715275290737</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
-        <v>791294.38078016671</v>
+        <v>791610.68578016665</v>
       </c>
       <c r="D84" s="1" t="str">
         <f>Reporting_currency</f>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.75828684520759604</v>
+        <v>0.77853205647410506</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>0.21823673453933465</v>
+        <v>0.22428490372119783</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="463" t="s">
+      <c r="B96" s="461" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="463"/>
-      <c r="D96" s="463"/>
-      <c r="E96" s="463"/>
-      <c r="F96" s="463"/>
+      <c r="C96" s="461"/>
+      <c r="D96" s="461"/>
+      <c r="E96" s="461"/>
+      <c r="F96" s="461"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="467" t="s">
+      <c r="B97" s="463" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="467"/>
-      <c r="D97" s="467"/>
-      <c r="E97" s="467"/>
-      <c r="F97" s="467"/>
+      <c r="C97" s="463"/>
+      <c r="D97" s="463"/>
+      <c r="E97" s="463"/>
+      <c r="F97" s="463"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="467" t="s">
+      <c r="B98" s="463" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="467"/>
-      <c r="D98" s="467"/>
-      <c r="E98" s="467"/>
-      <c r="F98" s="467"/>
+      <c r="C98" s="463"/>
+      <c r="D98" s="463"/>
+      <c r="E98" s="463"/>
+      <c r="F98" s="463"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="463" t="s">
+      <c r="B107" s="461" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="463"/>
-      <c r="D107" s="463"/>
-      <c r="E107" s="463"/>
-      <c r="F107" s="463"/>
+      <c r="C107" s="461"/>
+      <c r="D107" s="461"/>
+      <c r="E107" s="461"/>
+      <c r="F107" s="461"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="463" t="s">
+      <c r="B108" s="461" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="463"/>
-      <c r="D108" s="463"/>
-      <c r="E108" s="463"/>
-      <c r="F108" s="463"/>
+      <c r="C108" s="461"/>
+      <c r="D108" s="461"/>
+      <c r="E108" s="461"/>
+      <c r="F108" s="461"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-0.16650139591844174</v>
+        <v>-0.17087844774809768</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="463" t="s">
+      <c r="B114" s="461" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="463"/>
-      <c r="D114" s="463"/>
-      <c r="E114" s="463"/>
-      <c r="F114" s="463"/>
+      <c r="C114" s="461"/>
+      <c r="D114" s="461"/>
+      <c r="E114" s="461"/>
+      <c r="F114" s="461"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>14.47 HKD</v>
+        <v>14.85 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-7.7511615190408695E-2</v>
+        <v>-7.7785906325716775E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>11.66 HKD</v>
+        <v>11.97 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-7.8752060805006227E-3</v>
+        <v>-8.1932337426571349E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>10.49 HKD</v>
+        <v>10.77 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.8313892406829591E-2</v>
+        <v>2.797135907923998E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>9.45 HKD</v>
+        <v>9.69 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>6.5359848466424314E-2</v>
+        <v>6.4990919408088335E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>8.52 HKD</v>
+        <v>8.74 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.10320883220705934</v>
+        <v>0.10281152465368253</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="464" t="s">
+      <c r="B124" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="464"/>
-      <c r="D124" s="464"/>
-      <c r="E124" s="464"/>
-      <c r="F124" s="464"/>
+      <c r="C124" s="462"/>
+      <c r="D124" s="462"/>
+      <c r="E124" s="462"/>
+      <c r="F124" s="462"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>10.967807599967429</v>
+        <v>11.25643603289171</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="468" t="s">
+      <c r="B131" s="464" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="468"/>
-      <c r="D131" s="468"/>
-      <c r="E131" s="468"/>
-      <c r="F131" s="468"/>
+      <c r="C131" s="464"/>
+      <c r="D131" s="464"/>
+      <c r="E131" s="464"/>
+      <c r="F131" s="464"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="463" t="s">
+      <c r="B132" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="463"/>
-      <c r="D132" s="463"/>
-      <c r="E132" s="463"/>
-      <c r="F132" s="463"/>
+      <c r="C132" s="461"/>
+      <c r="D132" s="461"/>
+      <c r="E132" s="461"/>
+      <c r="F132" s="461"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6586,11 +6586,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>5.054289216574853</v>
+        <v>5.1872977110100056</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>5.3141281403824898</v>
+        <v>5.4471366348176424</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6607,11 +6607,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>6.3351957256129579</v>
+        <v>6.5019125099735531</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>6.6339642861251669</v>
+        <v>6.8006810704857621</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6654,11 +6654,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>7.8612900858633932</v>
+        <v>8.0681675148814467</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>8.2038797297466814</v>
+        <v>8.410757158764735</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6675,11 +6675,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>8.8905355068522027</v>
+        <v>9.1244985215943704</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>9.2614927891107719</v>
+        <v>9.4954558038529377</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="462" t="s">
+      <c r="B149" s="468" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="463"/>
-      <c r="D149" s="463"/>
-      <c r="E149" s="463"/>
-      <c r="F149" s="463"/>
+      <c r="C149" s="461"/>
+      <c r="D149" s="461"/>
+      <c r="E149" s="461"/>
+      <c r="F149" s="461"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="464" t="s">
+      <c r="B158" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="464"/>
-      <c r="D158" s="464"/>
-      <c r="E158" s="464"/>
-      <c r="F158" s="464"/>
+      <c r="C158" s="462"/>
+      <c r="D158" s="462"/>
+      <c r="E158" s="462"/>
+      <c r="F158" s="462"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="461" t="s">
+      <c r="B161" s="467" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="461"/>
-      <c r="D161" s="461"/>
-      <c r="E161" s="461"/>
-      <c r="F161" s="461"/>
+      <c r="C161" s="467"/>
+      <c r="D161" s="467"/>
+      <c r="E161" s="467"/>
+      <c r="F161" s="467"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="461" t="s">
+      <c r="B162" s="467" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="461"/>
-      <c r="D162" s="461"/>
-      <c r="E162" s="461"/>
-      <c r="F162" s="461"/>
+      <c r="C162" s="467"/>
+      <c r="D162" s="467"/>
+      <c r="E162" s="467"/>
+      <c r="F162" s="467"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -10211,11 +10211,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>2.9545491663816952</v>
+        <v>3.032219475169101</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-0.16650139591844174</v>
+        <v>-0.17087844774809768</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="D66" s="73">
         <f>C66-D75</f>
-        <v>791294.38078016671</v>
+        <v>791610.68578016665</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>193</v>
@@ -10473,11 +10473,11 @@
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
-        <v>-483279.51088649995</v>
+        <v>-482963.20588650001</v>
       </c>
       <c r="D73" s="285">
         <f>(Normalized_FCF!C26+Normalized_FCF!C35-Normalized_FCF!C89)/12</f>
-        <v>-477999.61921983329</v>
+        <v>-477683.31421983335</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>278</v>
@@ -10489,11 +10489,11 @@
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
-        <v>2.6264179867085211</v>
+        <v>2.6281380952616371</v>
       </c>
       <c r="D74" s="228">
         <f>-$C$66/D73</f>
-        <v>2.655428893587148</v>
+        <v>2.6571872247056585</v>
       </c>
       <c r="F74" s="223" t="s">
         <v>257</v>
@@ -10506,7 +10506,7 @@
       <c r="C75" s="261"/>
       <c r="D75" s="262">
         <f>MAX(-D73*D76,G5)</f>
-        <v>477999.61921983329</v>
+        <v>477683.31421983335</v>
       </c>
       <c r="F75" s="223" t="s">
         <v>279</v>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.54005011066826136</v>
+        <v>-0.55424715275290737</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10638,11 +10638,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>791294.38078016671</v>
+        <v>791610.68578016665</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.75828684520759604</v>
+        <v>0.77853205647410506</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10672,11 +10672,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>227736.38078016671</v>
+        <v>228052.68578016665</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>0.21823673453933468</v>
+        <v>0.22428490372119769</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="C10" s="266">
         <f>C48</f>
-        <v>-30945.482284680995</v>
+        <v>-30947.380114680996</v>
       </c>
       <c r="E10" s="237"/>
       <c r="G10" s="266">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
-        <v>654825.21771531925</v>
+        <v>654823.31988531922</v>
       </c>
       <c r="E11" s="237"/>
       <c r="G11" s="267">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
-        <v>-141442.24702650897</v>
+        <v>-141441.83709522896</v>
       </c>
       <c r="E12" s="237"/>
       <c r="G12" s="266">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
-        <v>479042.59967047302</v>
+        <v>479041.111771753</v>
       </c>
       <c r="D14" s="58"/>
       <c r="E14" s="243"/>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
-        <v>479042.59967047302</v>
+        <v>479041.111771753</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="234"/>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
-        <v>2867.9977153189998</v>
+        <v>2866.0998853190004</v>
       </c>
       <c r="E46" s="237"/>
       <c r="G46" s="274">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
-        <v>-30945.482284680995</v>
+        <v>-30947.380114680996</v>
       </c>
       <c r="E48" s="237"/>
       <c r="G48" s="267">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
-        <v>4.9326632674429362E-3</v>
+        <v>4.9329657786865077E-3</v>
       </c>
       <c r="D76" s="26"/>
       <c r="E76" s="234"/>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="D77" s="26"/>
       <c r="E77" s="234"/>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
-        <v>2.2545681141884419E-2</v>
+        <v>2.2545615799455805E-2</v>
       </c>
       <c r="D78" s="26"/>
       <c r="E78" s="234"/>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596239E-2</v>
       </c>
       <c r="D80" s="26"/>
       <c r="E80" s="234"/>
@@ -14002,7 +14002,7 @@
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596239E-2</v>
       </c>
       <c r="D85" s="72"/>
       <c r="E85" s="234"/>
@@ -14127,28 +14127,28 @@
       </c>
       <c r="C89" s="71">
         <f>C88*Common_Shares/scaling_factor</f>
-        <v>148181.13063799997</v>
+        <v>144385.47063799997</v>
       </c>
       <c r="E89" s="237"/>
       <c r="G89" s="71">
         <f t="shared" ref="G89:Q89" si="36">IF(G$4="","",G88*Common_Shares/scaling_factor)</f>
-        <v>148181.13063799997</v>
+        <v>144385.47063799997</v>
       </c>
       <c r="H89" s="71">
         <f t="shared" si="36"/>
-        <v>80351.739853000006</v>
+        <v>78293.529853</v>
       </c>
       <c r="I89" s="71">
         <f t="shared" si="36"/>
-        <v>28175.285403000002</v>
+        <v>27453.575403000003</v>
       </c>
       <c r="J89" s="71">
         <f t="shared" si="36"/>
-        <v>342277.54119199998</v>
+        <v>333510.10119199997</v>
       </c>
       <c r="K89" s="71">
         <f t="shared" si="36"/>
-        <v>336016.36665799993</v>
+        <v>327409.30665799993</v>
       </c>
       <c r="L89" s="71">
         <f t="shared" si="36"/>
@@ -14182,28 +14182,28 @@
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.3093276688543603</v>
+        <v>0.30140517606930323</v>
       </c>
       <c r="E90" s="237"/>
       <c r="G90" s="152">
         <f t="shared" ref="G90:Q90" si="37">IF(G$4="","",G88/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.29228200449327385</v>
+        <v>0.28479520028008992</v>
       </c>
       <c r="H90" s="152">
         <f t="shared" si="37"/>
-        <v>0.20668194524526071</v>
+        <v>0.20138778674537644</v>
       </c>
       <c r="I90" s="152">
         <f t="shared" si="37"/>
-        <v>0.11044583760804375</v>
+        <v>0.10761676722526019</v>
       </c>
       <c r="J90" s="152">
         <f t="shared" si="37"/>
-        <v>1.6729598189194208</v>
+        <v>1.6301069493338023</v>
       </c>
       <c r="K90" s="152">
         <f t="shared" si="37"/>
-        <v>0.3789135483841139</v>
+        <v>0.36920767697614648</v>
       </c>
       <c r="L90" s="152">
         <f t="shared" si="37"/>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
-        <v>0.11119915579830719</v>
+        <v>0.11119593529451954</v>
       </c>
       <c r="D96" s="26"/>
       <c r="E96" s="234"/>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="C116" s="22">
         <f>C77</f>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
-        <v>0.20577868195952315</v>
+        <v>0.20577808556685923</v>
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
@@ -15421,50 +15421,50 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.45906013039802579</v>
+        <v>0.47112661385532872</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.48583216830671405</v>
+        <v>0.49860390856428077</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>0.37255310282969983</v>
+        <v>0.38234692006101906</v>
       </c>
       <c r="I123" s="159">
         <f t="shared" si="48"/>
-        <v>0.24446371710103809</v>
+        <v>0.25089027199157926</v>
       </c>
       <c r="J123" s="159">
         <f t="shared" si="48"/>
-        <v>0.19605969987483501</v>
+        <v>0.20121379160677041</v>
       </c>
       <c r="K123" s="159">
         <f t="shared" si="48"/>
-        <v>0.84979806442175754</v>
+        <v>0.87213787816444432</v>
       </c>
       <c r="L123" s="159">
         <f t="shared" si="48"/>
-        <v>0.83182348163559439</v>
+        <v>0.85369077273042282</v>
       </c>
       <c r="M123" s="159">
         <f t="shared" si="48"/>
-        <v>0.99663537026709559</v>
+        <v>1.0228352987833962</v>
       </c>
       <c r="N123" s="159">
         <f t="shared" si="48"/>
-        <v>0.87456210815796431</v>
+        <v>0.89755292847238177</v>
       </c>
       <c r="O123" s="159">
         <f t="shared" si="48"/>
-        <v>0.63729799869527159</v>
+        <v>0.65405153013468131</v>
       </c>
       <c r="P123" s="159">
         <f t="shared" si="48"/>
-        <v>0.75509059431691605</v>
+        <v>0.77494070217444899</v>
       </c>
       <c r="Q123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.1504693208415224E-2</v>
+        <v>7.3384207765627527E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.5674792571139265E-2</v>
+        <v>7.7664160212504788E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.8030078322383154E-2</v>
+        <v>5.955559502508085E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.807846060763833E-2</v>
+        <v>3.9079481618626052E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0538894061500781E-2</v>
+        <v>3.1341712088281994E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.13236729975416783</v>
+        <v>0.1358470215209415</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12956752050398668</v>
+        <v>0.13297364061221539</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15523915424721116</v>
+        <v>0.15932013999741373</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13622462743893526</v>
+        <v>0.13980575209850182</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.9267601042877199E-2</v>
+        <v>0.10187718537923385</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11761535737023615</v>
+        <v>0.1207072744820014</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5908583177351829E-2</v>
+        <v>3.6852561627681274E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7581724066766641E-2</v>
+        <v>1.8043919095645813E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1430906686072024E-3</v>
+        <v>3.2257174278959989E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.4088669572612381E-2</v>
+        <v>-2.4721921652243156E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7993403327601014E-2</v>
+        <v>9.0306607279484946E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5020475709865845E-2</v>
+        <v>8.7255526213264462E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11160531782610353</v>
+        <v>0.11453924073945476</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5836875111962636E-2</v>
+        <v>9.8356271224189842E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7514473821393055E-2</v>
+        <v>0.10007797128460315</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4371617129040677E-2</v>
+        <v>8.6589610192033331E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16326,7 +16326,7 @@
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
-        <v>479042.59967047302</v>
+        <v>479041.111771753</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -16365,7 +16365,7 @@
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
-        <v>791294.38078016671</v>
+        <v>791610.68578016665</v>
       </c>
       <c r="G5" t="str">
         <f>Reporting_currency</f>
@@ -16386,7 +16386,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>9307113.3650263343</v>
+        <v>9307084.4572797753</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
-        <v>-30945.482284680995</v>
+        <v>-30947.380114680996</v>
       </c>
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
@@ -16419,14 +16419,14 @@
       </c>
       <c r="C7" s="275">
         <f>F7</f>
-        <v>227736.38078016671</v>
+        <v>228052.68578016665</v>
       </c>
       <c r="E7" s="140" t="s">
         <v>424</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
-        <v>227736.38078016671</v>
+        <v>228052.68578016665</v>
       </c>
       <c r="G7" t="str">
         <f>Reporting_currency</f>
@@ -16449,7 +16449,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>9534849.7458065003</v>
+        <v>9535137.1430599429</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16460,7 +16460,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>0.21823673453933465</v>
+        <v>0.22428490372119783</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="I8" s="313">
         <f>Normalized_FCF!C10</f>
-        <v>-30945.482284680995</v>
+        <v>-30947.380114680996</v>
       </c>
       <c r="J8" s="313"/>
       <c r="N8" s="304"/>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>9534849.7458065003</v>
+        <v>9535137.1430599429</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="E17" s="308" t="s">
         <v>553</v>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>10.925951123340464</v>
+        <v>11.21347920429608</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16722,11 +16722,11 @@
       </c>
       <c r="E21" s="299">
         <f>$C$17</f>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F21" s="277">
         <f>C21*E21</f>
-        <v>670446.67385539948</v>
+        <v>670444.73075092421</v>
       </c>
       <c r="G21" s="299">
         <f t="shared" ref="G21:G50" si="2">IF(A21="",0%,IF(A21="I",$C$18,$F$18))</f>
@@ -16734,7 +16734,7 @@
       </c>
       <c r="H21" s="277">
         <f>(F21*(1-$I$10)+C21*(G21-$I$9))</f>
-        <v>490470.60023845913</v>
+        <v>490469.07684455049</v>
       </c>
       <c r="I21" s="299">
         <f>H21/C4-1</f>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="J21" s="299">
         <f>H21/C21</f>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596239E-2</v>
       </c>
       <c r="K21" s="119">
         <f t="shared" ref="K21:K50" si="3">IF($C$15&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="L21" s="277">
         <f t="shared" ref="L21:L51" si="4">H21*K21</f>
-        <v>457315.24497758423</v>
+        <v>457313.82456368342</v>
       </c>
     </row>
     <row r="22" spans="1:21">
@@ -16771,11 +16771,11 @@
       </c>
       <c r="E22" s="299">
         <f t="shared" ref="E22:E50" si="6">IF($C$15&lt;B22,0,IF(B22&gt;=$F$15,$F$17,$C$17))</f>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F22" s="277">
         <f t="shared" ref="F22:F50" si="7">IF(A22="", 0,C22*E22)</f>
-        <v>686440.79415888479</v>
+        <v>686438.80469987029</v>
       </c>
       <c r="G22" s="299">
         <f t="shared" si="2"/>
@@ -16783,15 +16783,15 @@
       </c>
       <c r="H22" s="277">
         <f t="shared" ref="H22:H50" si="8">IF(A22="", 0,F22*(1-$I$10)+C22*(G22-$I$9))</f>
-        <v>502171.22624115966</v>
+        <v>502169.66650529235</v>
       </c>
       <c r="I22" s="299">
         <f t="shared" ref="I22:I50" si="9">IF(A22="", 0,H22/H21-1)</f>
-        <v>2.3855917147759476E-2</v>
+        <v>2.385591714775992E-2</v>
       </c>
       <c r="J22" s="299">
         <f>IF(A22="", 0,H22/C22)</f>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596252E-2</v>
       </c>
       <c r="K22" s="119">
         <f t="shared" si="3"/>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="L22" s="277">
         <f t="shared" si="4"/>
-        <v>436573.35158244928</v>
+        <v>436571.99559254071</v>
       </c>
     </row>
     <row r="23" spans="1:21">
@@ -16820,11 +16820,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>702816.46887118137</v>
+        <v>702814.43195179733</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16832,15 +16832,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>514150.98140835756</v>
+        <v>514149.38446356048</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596239E-2</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>416772.22311116074</v>
+        <v>416770.92862324312</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16877,11 +16877,11 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>719582.80032265314</v>
+        <v>719580.7148106891</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>526416.52462227456</v>
+        <v>526414.88958089473</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
@@ -16897,7 +16897,7 @@
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596252E-2</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>397869.19042907975</v>
+        <v>397867.95465368201</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16934,11 +16934,11 @@
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>736749.10798810306</v>
+        <v>736746.97272433841</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>538974.67361887498</v>
+        <v>538972.99957208347</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>7.6358668874411201E-2</v>
+        <v>7.6358431705596239E-2</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16962,7 +16962,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>379823.51969380141</v>
+        <v>379822.33996797085</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16991,11 +16991,11 @@
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>754324.933666953</v>
+        <v>754322.74746451282</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>551832.40877746756</v>
+        <v>551830.6947947545</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>7.6358668874411187E-2</v>
+        <v>7.6358431705596239E-2</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>362596.32457844954</v>
+        <v>362595.19836001389</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -17040,11 +17040,11 @@
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0.10437815343465008</v>
+        <v>0.10437785092340651</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>772320.04678700108</v>
+        <v>772317.8084306966</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>564996.87700071151</v>
+        <v>564995.12212936883</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>7.6358668874411215E-2</v>
+        <v>7.6358431705596252E-2</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>346150.48247615411</v>
+        <v>346149.40733824333</v>
       </c>
     </row>
     <row r="28" spans="1:21">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>0.5262620841986807</v>
+        <v>0.52626682475924147</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
@@ -18310,7 +18310,7 @@
       <c r="K52" s="460"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>11173811.441417836</v>
+        <v>11173802.753668532</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18334,7 +18334,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>11173811.441417836</v>
+        <v>11173802.753668532</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18369,19 +18369,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>9814279.8883100115</v>
+        <v>9814278.5009918585</v>
       </c>
       <c r="C56" s="118">
-        <v>9912422.6871931106</v>
+        <v>9912421.2860017754</v>
       </c>
       <c r="D56" s="118">
-        <v>10010565.486076213</v>
+        <v>10010564.071011696</v>
       </c>
       <c r="E56" s="118">
-        <v>10108708.284959309</v>
+        <v>10108706.856021611</v>
       </c>
       <c r="F56" s="118">
-        <v>10304993.882725511</v>
+        <v>10304992.426041448</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18395,19 +18395,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>9801863.3709403966</v>
+        <v>9801861.9836222436</v>
       </c>
       <c r="C57" s="118">
-        <v>9994369.5610537138</v>
+        <v>9994368.1598623786</v>
       </c>
       <c r="D57" s="118">
-        <v>10188746.791887904</v>
+        <v>10188745.376823386</v>
       </c>
       <c r="E57" s="118">
-        <v>10384995.063442957</v>
+        <v>10384993.634505259</v>
       </c>
       <c r="F57" s="118">
-        <v>10783104.728715679</v>
+        <v>10783103.272031618</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18421,19 +18421,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>9790286.1985677965</v>
+        <v>9790284.8112496417</v>
       </c>
       <c r="C58" s="118">
-        <v>10071540.97606463</v>
+        <v>10071539.574873295</v>
       </c>
       <c r="D58" s="118">
-        <v>10358205.93587664</v>
+        <v>10358204.520812124</v>
       </c>
       <c r="E58" s="118">
-        <v>10650333.414807204</v>
+        <v>10650331.985869506</v>
       </c>
       <c r="F58" s="118">
-        <v>11251185.277237521</v>
+        <v>11251183.820553461</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18447,19 +18447,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>9779491.6322530154</v>
+        <v>9779490.2449348606</v>
       </c>
       <c r="C59" s="118">
-        <v>10144215.222368615</v>
+        <v>10144213.821177278</v>
       </c>
       <c r="D59" s="118">
-        <v>10519369.877012786</v>
+        <v>10519368.461948268</v>
       </c>
       <c r="E59" s="118">
-        <v>10905157.192807367</v>
+        <v>10905155.763869669</v>
       </c>
       <c r="F59" s="118">
-        <v>11709445.954112053</v>
+        <v>11709444.497427993</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18473,19 +18473,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>9565066.8829123434</v>
+        <v>9565064.2020574491</v>
       </c>
       <c r="C60" s="118">
-        <v>10004186.853388794</v>
+        <v>10004184.132660629</v>
       </c>
       <c r="D60" s="118">
-        <v>10460028.649153311</v>
+        <v>10460025.888293169</v>
       </c>
       <c r="E60" s="118">
-        <v>10933077.656179186</v>
+        <v>10933074.854928359</v>
       </c>
       <c r="F60" s="118">
-        <v>11932785.996710166</v>
+        <v>11932783.11390185</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18499,19 +18499,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>9555682.3946169913</v>
+        <v>9555679.7137620971</v>
       </c>
       <c r="C61" s="118">
-        <v>10068637.708278472</v>
+        <v>10068634.987550307</v>
       </c>
       <c r="D61" s="118">
-        <v>10605800.484218795</v>
+        <v>10605797.723358653</v>
       </c>
       <c r="E61" s="118">
-        <v>11168105.76063884</v>
+        <v>11168102.959388016</v>
       </c>
       <c r="F61" s="118">
-        <v>12372020.642254733</v>
+        <v>12372017.759446416</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18525,19 +18525,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>9356386.9410605729</v>
+        <v>9356383.0541108176</v>
       </c>
       <c r="C62" s="118">
-        <v>9933013.6233365368</v>
+        <v>9933009.6599676292</v>
       </c>
       <c r="D62" s="118">
-        <v>10542228.387475109</v>
+        <v>10542224.34669745</v>
       </c>
       <c r="E62" s="118">
-        <v>11185606.350693326</v>
+        <v>11185602.23151008</v>
       </c>
       <c r="F62" s="118">
-        <v>12581460.516570132</v>
+        <v>12581456.237556249</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18551,19 +18551,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>9348228.3344063163</v>
+        <v>9348224.4474565573</v>
       </c>
       <c r="C63" s="118">
-        <v>9990171.5975470319</v>
+        <v>9990167.6341781262</v>
       </c>
       <c r="D63" s="118">
-        <v>10674078.153300881</v>
+        <v>10674074.112523222</v>
       </c>
       <c r="E63" s="118">
-        <v>11402376.584301054</v>
+        <v>11402372.465117808</v>
       </c>
       <c r="F63" s="118">
-        <v>13002459.052081574</v>
+        <v>13002454.77306769</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18577,19 +18577,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>9162956.5818897784</v>
+        <v>9162951.5703760479</v>
       </c>
       <c r="C64" s="118">
-        <v>9859120.1297805868</v>
+        <v>9859114.9961858988</v>
       </c>
       <c r="D64" s="118">
-        <v>10607163.793035693</v>
+        <v>10607158.534993824</v>
       </c>
       <c r="E64" s="118">
-        <v>11410593.71514282</v>
+        <v>11410588.330252912</v>
       </c>
       <c r="F64" s="118">
-        <v>13198672.945771238</v>
+        <v>13198667.299842816</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18603,19 +18603,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>9155863.7217951193</v>
+        <v>9155858.7102813888</v>
       </c>
       <c r="C65" s="118">
-        <v>9909810.4429104887</v>
+        <v>9909805.3093158007</v>
       </c>
       <c r="D65" s="118">
-        <v>10726421.129272845</v>
+        <v>10726415.871230975</v>
       </c>
       <c r="E65" s="118">
-        <v>11610524.418266093</v>
+        <v>11610519.033376185</v>
       </c>
       <c r="F65" s="118">
-        <v>13602192.496655108</v>
+        <v>13602186.850726686</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18629,19 +18629,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>8662848.4765127506</v>
+        <v>8662840.5272159502</v>
       </c>
       <c r="C66" s="277">
-        <v>9629780.5506112427</v>
+        <v>9629772.2998443879</v>
       </c>
       <c r="D66" s="118">
-        <v>10718382.899369128</v>
+        <v>10718374.335528303</v>
       </c>
       <c r="E66" s="118">
-        <v>11943844.058020264</v>
+        <v>11943835.169076212</v>
       </c>
       <c r="F66" s="118">
-        <v>14875252.222583853</v>
+        <v>14875242.645577185</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18664,19 +18664,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>8383007.2223415617</v>
+        <v>8382997.6305945963</v>
       </c>
       <c r="C67" s="277">
-        <v>9504786.4173546731</v>
+        <v>9504776.3794680331</v>
       </c>
       <c r="D67" s="118">
-        <v>10811525.873104215</v>
+        <v>10811515.366300512</v>
       </c>
       <c r="E67" s="118">
-        <v>12334947.697280739</v>
+        <v>12334936.69761261</v>
       </c>
       <c r="F67" s="118">
-        <v>16186221.156987902</v>
+        <v>16186209.094790336</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18699,19 +18699,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>8041583.4567711819</v>
+        <v>8041571.7947245166</v>
       </c>
       <c r="C68" s="277">
-        <v>9256573.4063230623</v>
+        <v>9256561.0596638508</v>
       </c>
       <c r="D68" s="118">
-        <v>10716473.74578896</v>
+        <v>10716460.666867826</v>
       </c>
       <c r="E68" s="118">
-        <v>12474629.398934327</v>
+        <v>12474615.536601864</v>
       </c>
       <c r="F68" s="118">
-        <v>17159873.460580766</v>
+        <v>17159857.86271356</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18734,19 +18734,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>7848611.5001595914</v>
+        <v>7848598.6806537081</v>
       </c>
       <c r="C69" s="277">
-        <v>9133771.931616772</v>
+        <v>9133758.2613049299</v>
       </c>
       <c r="D69" s="118">
-        <v>10719854.496215774</v>
+        <v>10719839.905548539</v>
       </c>
       <c r="E69" s="118">
-        <v>12685794.413808919</v>
+        <v>12685778.827103974</v>
       </c>
       <c r="F69" s="118">
-        <v>18184857.791080728</v>
+        <v>18184839.957996249</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18843,23 +18843,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18874,23 +18874,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>9.6231301790669832</v>
+        <v>9.876416388854599</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>9.7171791135122589</v>
+        <v>9.9729377037059308</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>9.8112280479575382</v>
+        <v>10.069459018557268</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>9.9052769824028104</v>
+        <v>10.165980333408596</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>10.093374851293365</v>
+        <v>10.359022963111265</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18905,23 +18905,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>9.6112315961712138</v>
+        <v>9.8642050114999762</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>9.7957077091445406</v>
+        <v>10.053530688836549</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>9.9819768154714748</v>
+        <v>10.244696494415873</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>10.170038915152007</v>
+        <v>10.437702428237939</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>10.551542094573891</v>
+        <v>10.829234680610325</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18936,23 +18936,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>9.6001373463849475</v>
+        <v>9.8528191118686266</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>9.8696600462900896</v>
+        <v>10.129427113062119</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>10.1443672517085</v>
+        <v>10.411355912015665</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>10.424309116300419</v>
+        <v>10.698656980847936</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>11.000097437645735</v>
+        <v>11.289581816623389</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18967,23 +18967,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>9.5897930575399428</v>
+        <v>9.8422028884361339</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>9.9393028066789046</v>
+        <v>10.200900668743071</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>10.298808505752111</v>
+        <v>10.569857176306376</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>10.668503342111944</v>
+        <v>10.949270677060802</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>11.439242528765021</v>
+        <v>11.740271320412406</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18998,23 +18998,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>9.3843126817641682</v>
+        <v>9.6313194944627014</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>9.8051154893766075</v>
+        <v>10.063184486626538</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>10.24194259900835</v>
+        <v>10.511495033482801</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>10.695259149560087</v>
+        <v>10.976728501679968</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>11.653266311094018</v>
+        <v>11.959920038522002</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -19029,23 +19029,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>9.3753196518675654</v>
+        <v>9.6220900523862127</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>9.8668778835149826</v>
+        <v>10.126570514000996</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>10.381633803213473</v>
+        <v>10.654858493031972</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>10.920483445592772</v>
+        <v>11.207873579406975</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>12.074179010293884</v>
+        <v>12.391897850359486</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -19061,23 +19061,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>9.1843374783400407</v>
+        <v>9.4260860808963471</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>9.7369111328306275</v>
+        <v>9.9931859259836493</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>10.320713511279296</v>
+        <v>10.592335446592456</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>10.937254027495051</v>
+        <v>11.225083736567203</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>12.274882446856543</v>
+        <v>12.597876081826836</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>9.1765191944605977</v>
+        <v>9.4180622670057534</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>9.7916848567382839</v>
+        <v>10.049399562314411</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>10.447063382323257</v>
+        <v>10.722006850955577</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>11.144982049543248</v>
+        <v>11.438272591625006</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>12.678319725174179</v>
+        <v>13.011919072291633</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -19124,23 +19124,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>8.9989757464920501</v>
+        <v>9.2358503835719059</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>9.6660999840712183</v>
+        <v>9.9205121160037404</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>10.382940243859229</v>
+        <v>10.656196821960362</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>11.152856416370572</v>
+        <v>11.446352717998037</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>12.866348881005083</v>
+        <v>13.204889865536634</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -19156,23 +19156,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>8.9921787533181892</v>
+        <v>9.2288747084642164</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>9.7146758346768554</v>
+        <v>9.9703649469890188</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>10.497222957675511</v>
+        <v>10.773483843090995</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>11.344447341080551</v>
+        <v>11.642980257583956</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>13.253036281612726</v>
+        <v>13.601742651155005</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -19188,23 +19188,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>8.519728823096484</v>
+        <v>8.7440019460876197</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>9.4463269259103608</v>
+        <v>9.6949585146850534</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>10.489520029229674</v>
+        <v>10.76557516595933</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>11.663863103676672</v>
+        <v>11.970789496701034</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>14.472992427874733</v>
+        <v>14.853765601040337</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -19220,23 +19220,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>8.2515606837307125</v>
+        <v>8.4687824856762468</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>9.3265467160684388</v>
+        <v>9.5720277196749137</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>10.578777697958719</v>
+        <v>10.857177363266382</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>12.038652501867061</v>
+        <v>12.355429424851478</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>15.729276462716861</v>
+        <v>16.143072862814595</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19252,23 +19252,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>7.9243788455152009</v>
+        <v>8.1329975311422444</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>9.0886875000216012</v>
+        <v>9.3279132997374443</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>10.487690512831621</v>
+        <v>10.763693114056274</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>12.172507612496936</v>
+        <v>12.49280055401587</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>16.662314471773133</v>
+        <v>17.10063545158598</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19284,23 +19284,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>7.7394563947222732</v>
+        <v>7.9432126305080466</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>8.9710084856071877</v>
+        <v>9.207139392986905</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>10.490930240849224</v>
+        <v>10.767016522502713</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>12.374864228235314</v>
+        <v>12.700475101314867</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>17.644543277184003</v>
+        <v>18.108683261985515</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19347,7 +19347,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>14.472992427874733</v>
+        <v>14.853765601040337</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19375,7 +19375,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>11.663863103676672</v>
+        <v>11.970789496701034</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19403,7 +19403,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>10.489520029229674</v>
+        <v>10.76557516595933</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>9.4463269259103608</v>
+        <v>9.6949585146850534</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>8.519728823096484</v>
+        <v>8.7440019460876197</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
-        <v>479042.59967047302</v>
+        <v>479041.111771753</v>
       </c>
       <c r="D9" s="469"/>
       <c r="E9" s="469"/>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>11.663863103676672</v>
+        <v>11.970789496701034</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19843,7 +19843,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>10.489520029229674</v>
+        <v>10.76557516595933</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>9.4463269259103608</v>
+        <v>9.6949585146850534</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>10.463590368289244</v>
+        <v>10.738963869289101</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>14.472992427874733</v>
+        <v>14.853765601040337</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19952,7 +19952,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>8.519728823096484</v>
+        <v>8.7440019460876197</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.2141750898751657</v>
+        <v>0.22442988622852325</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>7.7413410886670489E-2</v>
+        <v>7.7036393374037698E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>10.967807599967429</v>
+        <v>11.25643603289171</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>10.925951123340464</v>
+        <v>11.21347920429608</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>1.9897936077943486E-2</v>
+        <v>1.9925036935832013E-2</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20285,11 +20285,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>5.054289216574853</v>
+        <v>5.1872977110100056</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>5.3141281403824898</v>
+        <v>5.4471366348176424</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20297,7 +20297,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.5154794527578811</v>
+        <v>0.51608691961639419</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20310,11 +20310,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>6.3351957256129579</v>
+        <v>6.5019125099735531</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>6.6339642861251669</v>
+        <v>6.8006810704857621</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20322,7 +20322,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.39514217170030708</v>
+        <v>0.39584065057413131</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20356,11 +20356,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>7.8612900858633932</v>
+        <v>8.0681675148814467</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>8.2038797297466814</v>
+        <v>8.410757158764735</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20368,7 +20368,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.25200367940708179</v>
+        <v>0.25280460581056019</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20381,11 +20381,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>8.8905355068522027</v>
+        <v>9.1244985215943704</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>9.2614927891107719</v>
+        <v>9.4954558038529377</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.1555748307311412</v>
+        <v>0.15644207668334142</v>
       </c>
     </row>
   </sheetData>
@@ -20513,7 +20513,7 @@
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
-        <v>1043529089</v>
+        <v>1016799089</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6699.4567513800002</v>
+        <v>6527.8501513800002</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.2141750898751657</v>
+        <v>0.22442988622852325</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20607,7 +20607,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>10.967807599967429</v>
+        <v>11.25643603289171</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>5.3141281403824898</v>
+        <v>5.4471366348176424</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>6.6339642861251669</v>
+        <v>6.8006810704857621</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>8.2038797297466814</v>
+        <v>8.410757158764735</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>9.2614927891107719</v>
+        <v>9.4954558038529377</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
-        <v>2867.9977153189998</v>
+        <v>2866.0998853190004</v>
       </c>
       <c r="D44" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
-        <v>-30945.482284680995</v>
+        <v>-30947.380114680996</v>
       </c>
       <c r="D46" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20922,7 +20922,7 @@
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
-        <v>-141442.24702650897</v>
+        <v>-141441.83709522896</v>
       </c>
       <c r="D52" s="343" t="str">
         <f>Reporting_currency</f>
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
-        <v>479042.59967047302</v>
+        <v>479041.111771753</v>
       </c>
       <c r="D61" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.1504693208415224E-2</v>
+        <v>7.3384207765627527E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21018,7 +21018,7 @@
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
-        <v>0.3093276688543603</v>
+        <v>0.30140517606930323</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.54005011066826136</v>
+        <v>-0.55424715275290737</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -21188,7 +21188,7 @@
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
-        <v>791294.38078016671</v>
+        <v>791610.68578016665</v>
       </c>
       <c r="D84" s="343" t="str">
         <f>Reporting_currency</f>
@@ -21214,7 +21214,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.75828684520759604</v>
+        <v>0.77853205647410506</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -21258,7 +21258,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>0.21823673453933465</v>
+        <v>0.22428490372119783</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-0.16650139591844174</v>
+        <v>-0.17087844774809768</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>9.1371192679866926</v>
+        <v>9.3776019729104441</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21480,7 +21480,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>14.47 HKD</v>
+        <v>14.85 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>11.66 HKD</v>
+        <v>11.97 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21525,7 +21525,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>10.49 HKD</v>
+        <v>10.77 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21547,7 +21547,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>9.45 HKD</v>
+        <v>9.69 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>8.52 HKD</v>
+        <v>8.74 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21591,7 +21591,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>10.967807599967429</v>
+        <v>11.25643603289171</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21698,11 +21698,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>5.054289216574853</v>
+        <v>5.1872977110100056</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>5.3141281403824898</v>
+        <v>5.4471366348176424</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21719,11 +21719,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>6.3351957256129579</v>
+        <v>6.5019125099735531</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>6.6339642861251669</v>
+        <v>6.8006810704857621</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21759,11 +21759,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>7.8612900858633932</v>
+        <v>8.0681675148814467</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>8.2038797297466814</v>
+        <v>8.410757158764735</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21780,11 +21780,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>8.8905355068522027</v>
+        <v>9.1244985215943704</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>9.2614927891107719</v>
+        <v>9.4954558038529377</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,12 +21898,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21918,15 +21921,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B19EF68D-968A-40FA-898C-2AA65113CF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889A6A83-353A-4041-8883-8EC14317E815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,58 +4989,58 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.42</v>
+        <v>6.55</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6527.8501513800002</v>
+        <v>6660.0340329499995</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.22442988622852325</v>
+        <v>0.21613572546466733</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="461" t="s">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="461"/>
-      <c r="D12" s="461"/>
-      <c r="E12" s="461"/>
-      <c r="F12" s="461"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5558,13 +5558,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>5.4471366348176424</v>
+        <v>5.3814365192952689</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5573,13 +5573,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>6.8006810704857621</v>
+        <v>6.8132615931086278</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="461" t="s">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="461"/>
-      <c r="D29" s="461"/>
-      <c r="E29" s="461"/>
-      <c r="F29" s="461"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="463" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="463"/>
-      <c r="D30" s="463"/>
-      <c r="E30" s="463"/>
-      <c r="F30" s="463"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="462" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="462"/>
-      <c r="D33" s="462"/>
-      <c r="E33" s="462"/>
-      <c r="F33" s="462"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="462" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="462"/>
-      <c r="D36" s="462"/>
-      <c r="E36" s="462"/>
-      <c r="F36" s="462"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="462" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="462"/>
-      <c r="D40" s="462"/>
-      <c r="E40" s="462"/>
-      <c r="F40" s="462"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="462" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="462"/>
-      <c r="D43" s="462"/>
-      <c r="E43" s="462"/>
-      <c r="F43" s="462"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="462" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="462"/>
-      <c r="D51" s="462"/>
-      <c r="E51" s="462"/>
-      <c r="F51" s="462"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,13 +5829,13 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="462" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
-      <c r="C54" s="465"/>
-      <c r="D54" s="465"/>
-      <c r="E54" s="465"/>
-      <c r="F54" s="465"/>
+      <c r="C54" s="464"/>
+      <c r="D54" s="464"/>
+      <c r="E54" s="464"/>
+      <c r="F54" s="464"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="461" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="461"/>
-      <c r="D57" s="461"/>
-      <c r="E57" s="461"/>
-      <c r="F57" s="461"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="461" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="461"/>
-      <c r="D58" s="461"/>
-      <c r="E58" s="461"/>
-      <c r="F58" s="461"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.3384207765627527E-2</v>
+        <v>7.1927727306157055E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.2118380062305293E-2</v>
+        <v>2.1679389312977099E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="461" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="461"/>
-      <c r="D73" s="461"/>
-      <c r="E73" s="461"/>
-      <c r="F73" s="461"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="461" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="461"/>
-      <c r="D77" s="461"/>
-      <c r="E77" s="461"/>
-      <c r="F77" s="461"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="461" t="s">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="461"/>
-      <c r="D96" s="461"/>
-      <c r="E96" s="461"/>
-      <c r="F96" s="461"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="463" t="s">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="463"/>
-      <c r="D97" s="463"/>
-      <c r="E97" s="463"/>
-      <c r="F97" s="463"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="463" t="s">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="463"/>
-      <c r="D98" s="463"/>
-      <c r="E98" s="463"/>
-      <c r="F98" s="463"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="461" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="461"/>
-      <c r="D107" s="461"/>
-      <c r="E107" s="461"/>
-      <c r="F107" s="461"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="461" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="461"/>
-      <c r="D108" s="461"/>
-      <c r="E108" s="461"/>
-      <c r="F108" s="461"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="461" t="s">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="461"/>
-      <c r="D114" s="461"/>
-      <c r="E114" s="461"/>
-      <c r="F114" s="461"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="462" t="s">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="462"/>
-      <c r="D124" s="462"/>
-      <c r="E124" s="462"/>
-      <c r="F124" s="462"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6487,13 +6487,13 @@
       </c>
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B127" s="466" t="s">
+      <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
-      <c r="C127" s="466"/>
-      <c r="D127" s="466"/>
-      <c r="E127" s="466"/>
-      <c r="F127" s="466"/>
+      <c r="C127" s="465"/>
+      <c r="D127" s="465"/>
+      <c r="E127" s="465"/>
+      <c r="F127" s="465"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="464" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="464"/>
-      <c r="D131" s="464"/>
-      <c r="E131" s="464"/>
-      <c r="F131" s="464"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="461" t="s">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="461"/>
-      <c r="D132" s="461"/>
-      <c r="E132" s="461"/>
-      <c r="F132" s="461"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6582,19 +6582,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763696</v>
+        <v>0.25788802913063269</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>5.1872977110100056</v>
+        <v>5.1235484901646364</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>5.4471366348176424</v>
+        <v>5.3814365192952689</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6603,19 +6603,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220907</v>
+        <v>0.29912037037037031</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>6.5019125099735531</v>
+        <v>6.5141412227382576</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>6.8006810704857621</v>
+        <v>6.8132615931086278</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="468" t="s">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="461"/>
-      <c r="D149" s="461"/>
-      <c r="E149" s="461"/>
-      <c r="F149" s="461"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6711,13 +6711,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="465" t="s">
+      <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
-      <c r="C152" s="465"/>
-      <c r="D152" s="465"/>
-      <c r="E152" s="465"/>
-      <c r="F152" s="465"/>
+      <c r="C152" s="464"/>
+      <c r="D152" s="464"/>
+      <c r="E152" s="464"/>
+      <c r="F152" s="464"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="462" t="s">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="462"/>
-      <c r="D158" s="462"/>
-      <c r="E158" s="462"/>
-      <c r="F158" s="462"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="467" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="467"/>
-      <c r="D161" s="467"/>
-      <c r="E161" s="467"/>
-      <c r="F161" s="467"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="467" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="467"/>
-      <c r="D162" s="467"/>
-      <c r="E162" s="467"/>
-      <c r="F162" s="467"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.2118380062305293E-2</v>
+        <v>2.1679389312977099E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.2118380062305293E-2</v>
+        <v>2.1679389312977099E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1993769470404984E-2</v>
+        <v>1.1755725190839695E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.2056074766355141E-3</v>
+        <v>4.1221374045801529E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.1090342679127723E-2</v>
+        <v>5.0076335877862588E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0155763239875382E-2</v>
+        <v>4.9160305343511443E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3384207765627527E-2</v>
+        <v>7.1927727306157055E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.7664160212504788E-2</v>
+        <v>7.6122734131951267E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.955559502508085E-2</v>
+        <v>5.8373575581834973E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.9079481618626052E-2</v>
+        <v>3.8303858319325076E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.1341712088281994E-2</v>
+        <v>3.0719662840728308E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1358470215209415</v>
+        <v>0.1331508210938083</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.13297364061221539</v>
+        <v>0.13033446911914853</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15932013999741373</v>
+        <v>0.15615806088296125</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13980575209850182</v>
+        <v>0.13703098144616516</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>0.10187718537923385</v>
+        <v>9.9855195440409369E-2</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.1207072744820014</v>
+        <v>0.11831155758388534</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6852561627681274E-2</v>
+        <v>3.6121136740414318E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8043919095645813E-2</v>
+        <v>1.7685795510541395E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.2257174278959989E-3</v>
+        <v>3.1616955552812693E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.4721921652243156E-2</v>
+        <v>-2.4231257558381843E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0306607279484946E-2</v>
+        <v>8.8514262402182187E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7255526213264462E-2</v>
+        <v>8.5523737143382877E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11453924073945476</v>
+        <v>0.11226594283164879</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8356271224189842E-2</v>
+        <v>9.6404162024320422E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10007797128460315</v>
+        <v>9.8091690938496526E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6589610192033331E-2</v>
+        <v>8.4871037776008254E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18304,10 +18304,10 @@
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
-      <c r="J52" s="460" t="s">
+      <c r="J52" s="468" t="s">
         <v>420</v>
       </c>
-      <c r="K52" s="460"/>
+      <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
         <v>11173802.753668532</v>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.42</v>
+        <v>6.55</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.22442988622852325</v>
+        <v>0.21613572546466733</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20281,23 +20281,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.25983892380763696</v>
+        <v>0.25788802913063269</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>5.1872977110100056</v>
+        <v>5.1235484901646364</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>5.4471366348176424</v>
+        <v>5.3814365192952689</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.51608691961639419</v>
+        <v>0.521923590773268</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20306,23 +20306,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.29876856051220907</v>
+        <v>0.29912037037037031</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>6.5019125099735531</v>
+        <v>6.5141412227382576</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>6.8006810704857621</v>
+        <v>6.8132615931086278</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.39584065057413131</v>
+        <v>0.3947230212831101</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.42</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6527.8501513800002</v>
+        <v>6660.0340329499995</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.22442988622852325</v>
+        <v>0.21613572546466733</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20659,14 +20659,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>5.4471366348176424</v>
+        <v>5.3814365192952689</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20675,14 +20675,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>6.8006810704857621</v>
+        <v>6.8132615931086278</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.3384207765627527E-2</v>
+        <v>7.1927727306157055E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.2118380062305293E-2</v>
+        <v>2.1679389312977099E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21618,22 +21618,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21694,19 +21694,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.25983892380763696</v>
+        <v>0.25788802913063269</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>5.1872977110100056</v>
+        <v>5.1235484901646364</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>5.4471366348176424</v>
+        <v>5.3814365192952689</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036606</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21715,19 +21715,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.29876856051220907</v>
+        <v>0.29912037037037031</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>6.5019125099735531</v>
+        <v>6.5141412227382576</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>6.8006810704857621</v>
+        <v>6.8132615931086278</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903009</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21802,13 +21802,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21816,13 +21816,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21859,22 +21859,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21898,15 +21898,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21921,12 +21918,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/0345.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0345.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889A6A83-353A-4041-8883-8EC14317E815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EF16F7-12A3-4A8E-8EE8-15CC3FCE721F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>6660.0340329499995</v>
+        <v>6629.5300602799998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.21613572546466733</v>
+        <v>0.21802994295402547</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.1927727306157055E-2</v>
+        <v>7.2258683106645516E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.1679389312977099E-2</v>
+        <v>2.1779141104294478E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14258,28 +14258,28 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.1679389312977099E-2</v>
+        <v>2.1779141104294478E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.1679389312977099E-2</v>
+        <v>2.1779141104294478E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>1.1755725190839695E-2</v>
+        <v>1.1809815950920247E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1221374045801529E-3</v>
+        <v>4.141104294478528E-3</v>
       </c>
       <c r="J92" s="22">
         <f t="shared" si="38"/>
-        <v>5.0076335877862588E-2</v>
+        <v>5.0306748466257663E-2</v>
       </c>
       <c r="K92" s="22">
         <f t="shared" si="38"/>
-        <v>4.9160305343511443E-2</v>
+        <v>4.9386503067484662E-2</v>
       </c>
       <c r="L92" s="22">
         <f t="shared" si="38"/>
@@ -15478,50 +15478,50 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.1927727306157055E-2</v>
+        <v>7.2258683106645516E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.6122734131951267E-2</v>
+        <v>7.6472992111086019E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.8373575581834973E-2</v>
+        <v>5.8642165653530531E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>3.8303858319325076E-2</v>
+        <v>3.8480103066193143E-2</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>3.0719662840728308E-2</v>
+        <v>3.08610109826335E-2</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.1331508210938083</v>
+        <v>0.13376347824608043</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.13033446911914853</v>
+        <v>0.13093416759669063</v>
       </c>
       <c r="M124" s="74">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
-        <v>0.15615806088296125</v>
+        <v>0.15687657956800555</v>
       </c>
       <c r="N124" s="74">
         <f t="shared" ref="N124" si="56">IF(N$4="","",N123/Market_Price)</f>
-        <v>0.13703098144616516</v>
+        <v>0.13766149209699108</v>
       </c>
       <c r="O124" s="74">
         <f t="shared" ref="O124" si="57">IF(O$4="","",O123/Market_Price)</f>
-        <v>9.9855195440409369E-2</v>
+        <v>0.10031465186114745</v>
       </c>
       <c r="P124" s="74">
         <f t="shared" ref="P124" si="58">IF(P$4="","",P123/Market_Price)</f>
-        <v>0.11831155758388534</v>
+        <v>0.11885593591632654</v>
       </c>
       <c r="Q124" s="74" t="str">
         <f t="shared" ref="Q124" si="59">IF(Q$4="","",Q123/Market_Price)</f>
@@ -15535,43 +15535,43 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6121136740414318E-2</v>
+        <v>3.6287338289833403E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7685795510541395E-2</v>
+        <v>1.7767171870252473E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.1616955552812693E-3</v>
+        <v>3.1762432342166123E-3</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-2.4231257558381843E-2</v>
+        <v>-2.4342751074754768E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8514262402182187E-2</v>
+        <v>8.8921536615689162E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5523737143382877E-2</v>
+        <v>8.591725127134324E-2</v>
       </c>
       <c r="M125" s="22">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11226594283164879</v>
+        <v>0.11278250391829749</v>
       </c>
       <c r="N125" s="22">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6404162024320422E-2</v>
+        <v>9.6847739456947676E-2</v>
       </c>
       <c r="O125" s="22">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8091690938496526E-2</v>
+        <v>9.854303307471661E-2</v>
       </c>
       <c r="P125" s="22">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4871037776008254E-2</v>
+        <v>8.5261548686020552E-2</v>
       </c>
       <c r="Q125" s="22" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -20008,7 +20008,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.21613572546466733</v>
+        <v>0.21802994295402547</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20522,14 +20522,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>6660.0340329499995</v>
+        <v>6629.5300602799998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.21613572546466733</v>
+        <v>0.21802994295402547</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20537,13 +20537,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20728,22 +20728,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20933,10 +20933,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20952,22 +20952,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.1927727306157055E-2</v>
+        <v>7.2258683106645516E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.1679389312977099E-2</v>
+        <v>2.1779141104294478E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -21102,22 +21102,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -21125,13 +21125,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21280,33 +21280,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21369,23 +21369,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21429,13 +21429,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21599,13 +21599,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r=